--- a/04-Vulnerability-Remediation/DC01-Vulnerability-Tracker.xlsx
+++ b/04-Vulnerability-Remediation/DC01-Vulnerability-Tracker.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rd5540972b03a44ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="2" r:id="Rde50eb295a794796"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remediation" sheetId="3" r:id="Rb353591a0c0c4aaf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="4" r:id="Rae306c03c9e24811"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scan Review" sheetId="5" r:id="Rb8de43d4914b4874"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="6" r:id="R74cb1e8d64aa4cbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R57fbd255c8e14c5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="2" r:id="R270113e637b740b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remediation" sheetId="3" r:id="R33befa548b3447e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="4" r:id="R9f20c14e0fcf423b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scan Review" sheetId="5" r:id="Redab9b2c603c4a33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="6" r:id="Rdebf4ef885914173"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -23,7 +23,7 @@
     <x:numFmt numFmtId="201" formatCode="0.00%"/>
     <x:numFmt numFmtId="202" formatCode="0.0"/>
   </x:numFmts>
-  <x:fonts count="6">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -57,8 +57,60 @@
       <x:color rgb="FF243247"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF243247"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF243247"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color rgb="FF17354D"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:u val="single"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF1767A3"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="17"/>
+      <x:color rgb="FF17354D"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF526B80"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF17354D"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF6F531B"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -68,6 +120,31 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF18354D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17354D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF0F5F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF1F6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF4D8"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -83,7 +160,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="85">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -114,13 +191,223 @@
     <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="1">
+  <x:dxfs count="2">
     <x:dxf>
       <x:font>
+        <x:color rgb="FF24583E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE3EFE8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
         <x:color rgb="FF24583E"/>
       </x:font>
       <x:fill>
@@ -414,326 +701,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
-    <x:tabColor rgb="FF18354D"/>
+    <x:tabColor rgb="FF17354D"/>
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="31" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="4" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="78" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="38" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="1"/>
-      <x:c r="B1" s="1"/>
-      <x:c r="C1" s="1"/>
-      <x:c r="D1" s="1"/>
-      <x:c r="E1" s="1"/>
-      <x:c r="F1" s="1"/>
-      <x:c r="G1" s="1"/>
-      <x:c r="H1" s="1"/>
-    </x:row>
-    <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="14" t="str">
+    <x:row r="1" ht="25" customHeight="1">
+      <x:c r="A1" s="56"/>
+      <x:c r="B1" s="56"/>
+      <x:c r="C1" s="56"/>
+      <x:c r="D1" s="56"/>
+      <x:c r="E1" s="56"/>
+      <x:c r="F1" s="56"/>
+      <x:c r="G1" s="56"/>
+      <x:c r="H1" s="56"/>
+    </x:row>
+    <x:row r="2" ht="34" customHeight="1">
+      <x:c r="A2" s="57" t="str">
         <x:v>DC01 | Vulnerability management</x:v>
       </x:c>
-      <x:c r="B2" s="1"/>
-      <x:c r="C2" s="1"/>
-      <x:c r="D2" s="1"/>
-      <x:c r="E2" s="1"/>
-      <x:c r="F2" s="1"/>
-      <x:c r="G2" s="1"/>
-      <x:c r="H2" s="1"/>
-    </x:row>
-    <x:row r="3" ht="24" customHeight="1">
-      <x:c r="A3" s="1"/>
-      <x:c r="B3" s="1"/>
-      <x:c r="C3" s="1"/>
-      <x:c r="D3" s="1"/>
-      <x:c r="E3" s="1"/>
-      <x:c r="F3" s="1"/>
-      <x:c r="G3" s="1"/>
-      <x:c r="H3" s="1"/>
-    </x:row>
-    <x:row r="4" ht="24" customHeight="1">
-      <x:c r="A4" s="1" t="str">
-        <x:v>As of</x:v>
-      </x:c>
-      <x:c r="B4" s="15" t="d">
+      <x:c r="B2" s="56"/>
+      <x:c r="C2" s="56"/>
+      <x:c r="D2" s="56"/>
+      <x:c r="E2" s="56"/>
+      <x:c r="F2" s="56"/>
+      <x:c r="G2" s="56"/>
+      <x:c r="H2" s="56"/>
+    </x:row>
+    <x:row r="3" ht="25" customHeight="1">
+      <x:c r="A3" s="56" t="str">
+        <x:v>Windows Server security lab • Evidence review as of October 23, 2026</x:v>
+      </x:c>
+      <x:c r="B3" s="56"/>
+      <x:c r="C3" s="56"/>
+      <x:c r="D3" s="56"/>
+      <x:c r="E3" s="56"/>
+      <x:c r="F3" s="56"/>
+      <x:c r="G3" s="56"/>
+      <x:c r="H3" s="56"/>
+    </x:row>
+    <x:row r="4" ht="25" customHeight="1">
+      <x:c r="A4" s="56" t="str">
+        <x:v>Reporting date</x:v>
+      </x:c>
+      <x:c r="B4" s="58" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="C4" s="1"/>
-      <x:c r="D4" s="1"/>
-      <x:c r="E4" s="1"/>
-      <x:c r="F4" s="1"/>
-      <x:c r="G4" s="1"/>
-      <x:c r="H4" s="1"/>
-    </x:row>
-    <x:row r="5" ht="24" customHeight="1">
-      <x:c r="A5" s="1"/>
-      <x:c r="B5" s="1"/>
-      <x:c r="C5" s="1"/>
-      <x:c r="D5" s="1"/>
-      <x:c r="E5" s="1"/>
-      <x:c r="F5" s="1"/>
-      <x:c r="G5" s="1"/>
-      <x:c r="H5" s="1"/>
-    </x:row>
-    <x:row r="6" ht="24" customHeight="1">
-      <x:c r="A6" s="4" t="str">
-        <x:v>Tracked finding status</x:v>
-      </x:c>
-      <x:c r="B6" s="4" t="str">
-        <x:v>Count</x:v>
-      </x:c>
-      <x:c r="C6" s="1"/>
-      <x:c r="D6" s="1" t="str">
-        <x:v>Closure scope</x:v>
-      </x:c>
-      <x:c r="E6" s="1"/>
-      <x:c r="F6" s="1"/>
-      <x:c r="G6" s="1"/>
-      <x:c r="H6" s="1"/>
-    </x:row>
-    <x:row r="7" ht="24" customHeight="1">
-      <x:c r="A7" s="1" t="str">
-        <x:v>Total findings</x:v>
-      </x:c>
-      <x:c r="B7" s="1" t="n">
+      <x:c r="C4" s="56"/>
+      <x:c r="D4" s="56"/>
+      <x:c r="E4" s="56"/>
+      <x:c r="F4" s="56"/>
+      <x:c r="G4" s="56"/>
+      <x:c r="H4" s="56"/>
+    </x:row>
+    <x:row r="5" ht="25" customHeight="1">
+      <x:c r="A5" s="56"/>
+      <x:c r="B5" s="56"/>
+      <x:c r="C5" s="56"/>
+      <x:c r="D5" s="56"/>
+      <x:c r="E5" s="56"/>
+      <x:c r="F5" s="56"/>
+      <x:c r="G5" s="56"/>
+      <x:c r="H5" s="56"/>
+    </x:row>
+    <x:row r="6" ht="25" customHeight="1">
+      <x:c r="A6" s="61" t="str">
+        <x:v>TRACKED FINDINGS</x:v>
+      </x:c>
+      <x:c r="B6" s="61" t="str">
+        <x:v>VERIFIED CLOSED</x:v>
+      </x:c>
+      <x:c r="C6" s="62"/>
+      <x:c r="D6" s="61" t="str">
+        <x:v>NOT CLOSED</x:v>
+      </x:c>
+      <x:c r="E6" s="61" t="str">
+        <x:v>OVERDUE</x:v>
+      </x:c>
+      <x:c r="F6" s="62"/>
+      <x:c r="G6" s="61" t="str">
+        <x:v>AUTHENTICATED SCAN</x:v>
+      </x:c>
+      <x:c r="H6" s="61"/>
+    </x:row>
+    <x:row r="7" ht="33" customHeight="1">
+      <x:c r="A7" s="60" t="n">
         <x:f>COUNTA(Findings!A6:A205)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="1"/>
-      <x:c r="D7" s="1" t="str">
-        <x:v>Two tracked DC01 findings verified remediated.</x:v>
-      </x:c>
-      <x:c r="E7" s="1"/>
-      <x:c r="F7" s="1"/>
-      <x:c r="G7" s="1"/>
-      <x:c r="H7" s="1"/>
-    </x:row>
-    <x:row r="8" ht="24" customHeight="1">
-      <x:c r="A8" s="1" t="str">
-        <x:v>Closed</x:v>
-      </x:c>
-      <x:c r="B8" s="1" t="n">
+      <x:c r="B7" s="60" t="n">
         <x:f>COUNTIFS(Findings!L6:L205,"Closed")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C8" s="1"/>
-      <x:c r="D8" s="1"/>
-      <x:c r="E8" s="1"/>
-      <x:c r="F8" s="1"/>
-      <x:c r="G8" s="1"/>
-      <x:c r="H8" s="1"/>
-    </x:row>
-    <x:row r="9" ht="24" customHeight="1">
-      <x:c r="A9" s="1" t="str">
-        <x:v>Not closed</x:v>
-      </x:c>
-      <x:c r="B9" s="1" t="n">
-        <x:f>B7-B8</x:f>
+      <x:c r="C7" s="56"/>
+      <x:c r="D7" s="60" t="n">
+        <x:f>A7-B7</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C9" s="1"/>
-      <x:c r="D9" s="1" t="str">
-        <x:v>Administrator credential removal: operator confirmed.</x:v>
-      </x:c>
-      <x:c r="E9" s="1"/>
-      <x:c r="F9" s="1"/>
-      <x:c r="G9" s="1"/>
-      <x:c r="H9" s="1"/>
-    </x:row>
-    <x:row r="10" ht="24" customHeight="1">
-      <x:c r="A10" s="1" t="str">
-        <x:v>Overdue</x:v>
-      </x:c>
-      <x:c r="B10" s="1" t="n">
+      <x:c r="E7" s="60" t="n">
         <x:f>COUNTIFS(Findings!U6:U205,"Overdue")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C10" s="1"/>
-      <x:c r="D10" s="1"/>
-      <x:c r="E10" s="1"/>
-      <x:c r="F10" s="1"/>
-      <x:c r="G10" s="1"/>
-      <x:c r="H10" s="1"/>
-    </x:row>
-    <x:row r="11" ht="24" customHeight="1">
-      <x:c r="A11" s="1" t="str">
-        <x:v>Missing target: not closed</x:v>
-      </x:c>
-      <x:c r="B11" s="1" t="n">
-        <x:f>COUNTIFS(Findings!U6:U205,"No target set")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C11" s="1"/>
-      <x:c r="D11" s="1" t="str">
-        <x:v>50 screenshots retained; evidence links use repository layout.</x:v>
-      </x:c>
-      <x:c r="E11" s="1"/>
-      <x:c r="F11" s="1"/>
-      <x:c r="G11" s="1"/>
-      <x:c r="H11" s="1"/>
-    </x:row>
-    <x:row r="12" ht="24" customHeight="1">
-      <x:c r="A12" s="1"/>
-      <x:c r="B12" s="1"/>
-      <x:c r="C12" s="1"/>
-      <x:c r="D12" s="1"/>
-      <x:c r="E12" s="1"/>
-      <x:c r="F12" s="1"/>
-      <x:c r="G12" s="1"/>
-      <x:c r="H12" s="1"/>
-    </x:row>
-    <x:row r="13" ht="24" customHeight="1">
-      <x:c r="A13" s="1"/>
-      <x:c r="B13" s="1"/>
-      <x:c r="C13" s="1"/>
-      <x:c r="D13" s="1"/>
-      <x:c r="E13" s="1"/>
-      <x:c r="F13" s="1"/>
-      <x:c r="G13" s="1"/>
-      <x:c r="H13" s="1"/>
-    </x:row>
-    <x:row r="14" ht="24" customHeight="1">
-      <x:c r="A14" s="4" t="str">
-        <x:v>Final scan</x:v>
-      </x:c>
-      <x:c r="B14" s="4" t="str">
-        <x:v>Observed result</x:v>
-      </x:c>
-      <x:c r="C14" s="1"/>
-      <x:c r="D14" s="1" t="str">
-        <x:v>Physical Hyper-V host protection was not assessed.</x:v>
-      </x:c>
-      <x:c r="E14" s="1"/>
-      <x:c r="F14" s="1"/>
-      <x:c r="G14" s="1"/>
-      <x:c r="H14" s="1"/>
-    </x:row>
-    <x:row r="15" ht="24" customHeight="1">
-      <x:c r="A15" s="1" t="str">
-        <x:v>Displayed groups</x:v>
-      </x:c>
-      <x:c r="B15" s="1" t="n">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C15" s="1"/>
-      <x:c r="D15" s="1"/>
-      <x:c r="E15" s="1"/>
-      <x:c r="F15" s="1"/>
-      <x:c r="G15" s="1"/>
-      <x:c r="H15" s="1"/>
-    </x:row>
-    <x:row r="16" ht="24" customHeight="1">
-      <x:c r="A16" s="1" t="str">
-        <x:v>Informational instances</x:v>
-      </x:c>
-      <x:c r="B16" s="1" t="n">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="C16" s="1"/>
-      <x:c r="D16" s="1" t="str">
-        <x:v>Lab evidence; no independent approval or compliance claim.</x:v>
-      </x:c>
-      <x:c r="E16" s="1"/>
-      <x:c r="F16" s="1"/>
-      <x:c r="G16" s="1"/>
-      <x:c r="H16" s="1"/>
-    </x:row>
-    <x:row r="17" ht="24" customHeight="1">
-      <x:c r="A17" s="1" t="str">
+      <x:c r="F7" s="56"/>
+      <x:c r="G7" s="60" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="H7" s="59"/>
+    </x:row>
+    <x:row r="8" ht="25" customHeight="1">
+      <x:c r="A8" s="56"/>
+      <x:c r="B8" s="56"/>
+      <x:c r="C8" s="56"/>
+      <x:c r="D8" s="56"/>
+      <x:c r="E8" s="56"/>
+      <x:c r="F8" s="56"/>
+      <x:c r="G8" s="56"/>
+      <x:c r="H8" s="56"/>
+    </x:row>
+    <x:row r="9" ht="25" customHeight="1">
+      <x:c r="A9" s="56"/>
+      <x:c r="B9" s="56"/>
+      <x:c r="C9" s="56"/>
+      <x:c r="D9" s="56"/>
+      <x:c r="E9" s="56"/>
+      <x:c r="F9" s="56"/>
+      <x:c r="G9" s="56"/>
+      <x:c r="H9" s="56"/>
+    </x:row>
+    <x:row r="10" ht="35" customHeight="1">
+      <x:c r="A10" s="33" t="str">
+        <x:v>Finding ID</x:v>
+      </x:c>
+      <x:c r="B10" s="33" t="str">
+        <x:v>Finding</x:v>
+      </x:c>
+      <x:c r="C10" s="33" t="str">
+        <x:v>Nessus severity</x:v>
+      </x:c>
+      <x:c r="D10" s="33" t="str">
+        <x:v>CVSS v3.0</x:v>
+      </x:c>
+      <x:c r="E10" s="33" t="str">
+        <x:v>VPR</x:v>
+      </x:c>
+      <x:c r="F10" s="33" t="str">
+        <x:v>EPSS</x:v>
+      </x:c>
+      <x:c r="G10" s="33" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="H10" s="33" t="str">
+        <x:v>Change ID</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="58" customHeight="1">
+      <x:c r="A11" s="67" t="str">
+        <x:f>Findings!A6</x:f>
+        <x:v>DC01-VULN-001</x:v>
+      </x:c>
+      <x:c r="B11" s="67" t="str">
+        <x:f>Findings!C6</x:f>
+        <x:v>WinVerifyTrust / CVE-2013-3900</x:v>
+      </x:c>
+      <x:c r="C11" s="74" t="str">
+        <x:f>Findings!E6</x:f>
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="D11" s="75" t="n">
+        <x:f>Findings!G6</x:f>
+        <x:v>8.8</x:v>
+      </x:c>
+      <x:c r="E11" s="75" t="n">
+        <x:f>Findings!H6</x:f>
+        <x:v>9.5</x:v>
+      </x:c>
+      <x:c r="F11" s="76" t="n">
+        <x:f>Findings!I6</x:f>
+        <x:v>0.4465</x:v>
+      </x:c>
+      <x:c r="G11" s="74" t="str">
+        <x:f>Findings!L6</x:f>
+        <x:v>Closed</x:v>
+      </x:c>
+      <x:c r="H11" s="74" t="str">
+        <x:f>Findings!Q6</x:f>
+        <x:v>LAB-CHG-012</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="58" customHeight="1">
+      <x:c r="A12" s="69" t="str">
+        <x:f>Findings!A7</x:f>
+        <x:v>DC01-VULN-002</x:v>
+      </x:c>
+      <x:c r="B12" s="69" t="str">
+        <x:f>Findings!C7</x:f>
+        <x:v>Intel BHI / CVE-2022-0001</x:v>
+      </x:c>
+      <x:c r="C12" s="77" t="str">
+        <x:f>Findings!E7</x:f>
+        <x:v>Low</x:v>
+      </x:c>
+      <x:c r="D12" s="78" t="n">
+        <x:f>Findings!G7</x:f>
+        <x:v>6.5</x:v>
+      </x:c>
+      <x:c r="E12" s="78" t="n">
+        <x:f>Findings!H7</x:f>
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="F12" s="79" t="n">
+        <x:f>Findings!I7</x:f>
+        <x:v>0.0046</x:v>
+      </x:c>
+      <x:c r="G12" s="77" t="str">
+        <x:f>Findings!L7</x:f>
+        <x:v>Closed</x:v>
+      </x:c>
+      <x:c r="H12" s="77" t="str">
+        <x:f>Findings!Q7</x:f>
+        <x:v>LAB-CHG-013</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="25" customHeight="1">
+      <x:c r="A13" s="56"/>
+      <x:c r="B13" s="56"/>
+      <x:c r="C13" s="56"/>
+      <x:c r="D13" s="56"/>
+      <x:c r="E13" s="56"/>
+      <x:c r="F13" s="56"/>
+      <x:c r="G13" s="56"/>
+      <x:c r="H13" s="56"/>
+    </x:row>
+    <x:row r="14" ht="25" customHeight="1">
+      <x:c r="A14" s="56"/>
+      <x:c r="B14" s="56"/>
+      <x:c r="C14" s="56"/>
+      <x:c r="D14" s="56"/>
+      <x:c r="E14" s="56"/>
+      <x:c r="F14" s="56"/>
+      <x:c r="G14" s="56"/>
+      <x:c r="H14" s="56"/>
+    </x:row>
+    <x:row r="15" ht="28" customHeight="1">
+      <x:c r="A15" s="80" t="str">
+        <x:v>VERIFICATION RECORD</x:v>
+      </x:c>
+      <x:c r="B15" s="80"/>
+      <x:c r="C15" s="80"/>
+      <x:c r="D15" s="80"/>
+      <x:c r="E15" s="80"/>
+      <x:c r="F15" s="80"/>
+      <x:c r="G15" s="80"/>
+      <x:c r="H15" s="80"/>
+    </x:row>
+    <x:row r="16" ht="25" customHeight="1">
+      <x:c r="A16" s="56" t="str">
         <x:v>Credentialed checks</x:v>
       </x:c>
-      <x:c r="B17" s="1" t="str">
-        <x:v>Yes / Administrator</x:v>
-      </x:c>
-      <x:c r="C17" s="1"/>
-      <x:c r="D17" s="1"/>
-      <x:c r="E17" s="1"/>
-      <x:c r="F17" s="1"/>
-      <x:c r="G17" s="1"/>
-      <x:c r="H17" s="1"/>
-    </x:row>
-    <x:row r="18" ht="24" customHeight="1">
-      <x:c r="A18" s="1"/>
-      <x:c r="B18" s="1"/>
-      <x:c r="C18" s="1"/>
-      <x:c r="D18" s="1"/>
-      <x:c r="E18" s="1"/>
-      <x:c r="F18" s="1"/>
-      <x:c r="G18" s="1"/>
-      <x:c r="H18" s="1"/>
-    </x:row>
-    <x:row r="19" ht="24" customHeight="1">
-      <x:c r="A19" s="1"/>
-      <x:c r="B19" s="1"/>
-      <x:c r="C19" s="1"/>
-      <x:c r="D19" s="1"/>
-      <x:c r="E19" s="1"/>
-      <x:c r="F19" s="1"/>
-      <x:c r="G19" s="1"/>
-      <x:c r="H19" s="1"/>
-    </x:row>
-    <x:row r="20" ht="24" customHeight="1">
-      <x:c r="A20" s="1"/>
-      <x:c r="B20" s="1"/>
-      <x:c r="C20" s="1"/>
-      <x:c r="D20" s="1"/>
-      <x:c r="E20" s="1"/>
-      <x:c r="F20" s="1"/>
-      <x:c r="G20" s="1"/>
-      <x:c r="H20" s="1"/>
-    </x:row>
-    <x:row r="21" ht="24" customHeight="1">
-      <x:c r="A21" s="1"/>
-      <x:c r="B21" s="1"/>
-      <x:c r="C21" s="1"/>
-      <x:c r="D21" s="1"/>
-      <x:c r="E21" s="1"/>
-      <x:c r="F21" s="1"/>
-      <x:c r="G21" s="1"/>
-      <x:c r="H21" s="1"/>
-    </x:row>
-    <x:row r="22" ht="24" customHeight="1">
-      <x:c r="A22" s="1"/>
-      <x:c r="B22" s="1"/>
-      <x:c r="C22" s="1"/>
-      <x:c r="D22" s="1"/>
-      <x:c r="E22" s="1"/>
-      <x:c r="F22" s="1"/>
-      <x:c r="G22" s="1"/>
-      <x:c r="H22" s="1"/>
-    </x:row>
-    <x:row r="23" ht="24" customHeight="1">
-      <x:c r="A23" s="1"/>
-      <x:c r="B23" s="1"/>
-      <x:c r="C23" s="1"/>
-      <x:c r="D23" s="1"/>
-      <x:c r="E23" s="1"/>
-      <x:c r="F23" s="1"/>
-      <x:c r="G23" s="1"/>
-      <x:c r="H23" s="1"/>
-    </x:row>
-    <x:row r="24" ht="24" customHeight="1">
-      <x:c r="A24" s="1"/>
-      <x:c r="B24" s="1"/>
-      <x:c r="C24" s="1"/>
-      <x:c r="D24" s="1"/>
-      <x:c r="E24" s="1"/>
-      <x:c r="F24" s="1"/>
-      <x:c r="G24" s="1"/>
-      <x:c r="H24" s="1"/>
+      <x:c r="B16" s="56" t="str">
+        <x:v>Yes, via SMB</x:v>
+      </x:c>
+      <x:c r="C16" s="56"/>
+      <x:c r="D16" s="56" t="str">
+        <x:v>Closure evidence</x:v>
+      </x:c>
+      <x:c r="E16" s="56"/>
+      <x:c r="F16" s="56"/>
+      <x:c r="G16" s="56"/>
+      <x:c r="H16" s="56"/>
+    </x:row>
+    <x:row r="17" ht="25" customHeight="1">
+      <x:c r="A17" s="56" t="str">
+        <x:v>Final scan results</x:v>
+      </x:c>
+      <x:c r="B17" s="56" t="str">
+        <x:v>51 groups / 235 Info instances</x:v>
+      </x:c>
+      <x:c r="C17" s="56"/>
+      <x:c r="D17" s="81" t="str">
+        <x:v>Baseline → scoped GPO → verified registry → restart checks → authenticated rescan</x:v>
+      </x:c>
+      <x:c r="E17" s="81"/>
+      <x:c r="F17" s="81"/>
+      <x:c r="G17" s="81"/>
+      <x:c r="H17" s="81"/>
+    </x:row>
+    <x:row r="18" ht="25" customHeight="1">
+      <x:c r="A18" s="56" t="str">
+        <x:v>Retained screenshots</x:v>
+      </x:c>
+      <x:c r="B18" s="56" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C18" s="56"/>
+      <x:c r="D18" s="81"/>
+      <x:c r="E18" s="81"/>
+      <x:c r="F18" s="81"/>
+      <x:c r="G18" s="81"/>
+      <x:c r="H18" s="81"/>
+    </x:row>
+    <x:row r="19" ht="25" customHeight="1">
+      <x:c r="A19" s="56" t="str">
+        <x:v>Privileged credential</x:v>
+      </x:c>
+      <x:c r="B19" s="56" t="str">
+        <x:v>Removed; operator confirmed</x:v>
+      </x:c>
+      <x:c r="C19" s="56"/>
+      <x:c r="D19" s="56" t="str">
+        <x:v>Service and AD console checks: operator reported.</x:v>
+      </x:c>
+      <x:c r="E19" s="56"/>
+      <x:c r="F19" s="56"/>
+      <x:c r="G19" s="56"/>
+      <x:c r="H19" s="56"/>
+    </x:row>
+    <x:row r="20" ht="25" customHeight="1">
+      <x:c r="A20" s="56"/>
+      <x:c r="B20" s="56"/>
+      <x:c r="C20" s="56"/>
+      <x:c r="D20" s="56"/>
+      <x:c r="E20" s="56"/>
+      <x:c r="F20" s="56"/>
+      <x:c r="G20" s="56"/>
+      <x:c r="H20" s="56"/>
+    </x:row>
+    <x:row r="21" ht="25" customHeight="1">
+      <x:c r="A21" s="56"/>
+      <x:c r="B21" s="56"/>
+      <x:c r="C21" s="56"/>
+      <x:c r="D21" s="56"/>
+      <x:c r="E21" s="56"/>
+      <x:c r="F21" s="56"/>
+      <x:c r="G21" s="56"/>
+      <x:c r="H21" s="56"/>
+    </x:row>
+    <x:row r="22" ht="25" customHeight="1">
+      <x:c r="A22" s="84" t="str">
+        <x:v>Scope: two selected DC01 configuration findings. Original scores retained. Physical Hyper-V host protection, independent approval, and full compliance were not established.</x:v>
+      </x:c>
+      <x:c r="B22" s="84"/>
+      <x:c r="C22" s="84"/>
+      <x:c r="D22" s="84"/>
+      <x:c r="E22" s="84"/>
+      <x:c r="F22" s="84"/>
+      <x:c r="G22" s="84"/>
+      <x:c r="H22" s="84"/>
+    </x:row>
+    <x:row r="23" ht="25" customHeight="1">
+      <x:c r="A23" s="84"/>
+      <x:c r="B23" s="84"/>
+      <x:c r="C23" s="84"/>
+      <x:c r="D23" s="84"/>
+      <x:c r="E23" s="84"/>
+      <x:c r="F23" s="84"/>
+      <x:c r="G23" s="84"/>
+      <x:c r="H23" s="84"/>
+    </x:row>
+    <x:row r="24" ht="25" customHeight="1">
+      <x:c r="A24" s="56"/>
+      <x:c r="B24" s="56"/>
+      <x:c r="C24" s="56"/>
+      <x:c r="D24" s="56"/>
+      <x:c r="E24" s="56"/>
+      <x:c r="F24" s="56"/>
+      <x:c r="G24" s="56"/>
+      <x:c r="H24" s="56"/>
+    </x:row>
+    <x:row r="25" ht="25" customHeight="1">
+      <x:c r="A25" s="81" t="str">
+        <x:v>Use Findings for the complete register, Remediation for changes, and Evidence for screenshot links. Download the repository together to preserve relative links. Target dates were not assigned retrospectively.</x:v>
+      </x:c>
+      <x:c r="B25" s="81"/>
+      <x:c r="C25" s="81"/>
+      <x:c r="D25" s="81"/>
+      <x:c r="E25" s="81"/>
+      <x:c r="F25" s="81"/>
+      <x:c r="G25" s="81"/>
+      <x:c r="H25" s="81"/>
+    </x:row>
+    <x:row r="26" ht="25" customHeight="1">
+      <x:c r="A26" s="81"/>
+      <x:c r="B26" s="81"/>
+      <x:c r="C26" s="81"/>
+      <x:c r="D26" s="81"/>
+      <x:c r="E26" s="81"/>
+      <x:c r="F26" s="81"/>
+      <x:c r="G26" s="81"/>
+      <x:c r="H26" s="81"/>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="D17:H18"/>
+    <x:mergeCell ref="A22:H23"/>
+    <x:mergeCell ref="A25:H26"/>
+    <x:mergeCell ref="A2:H2"/>
+    <x:mergeCell ref="A3:H3"/>
+    <x:mergeCell ref="G6:H6"/>
+    <x:mergeCell ref="A15:H15"/>
+    <x:mergeCell ref="D16:H16"/>
+    <x:mergeCell ref="D19:H19"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="G11:G12">
+    <x:cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Closed"/>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF5A7890"/>
+  </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="23" hidden="0" customWidth="1"/>
@@ -760,1283 +1149,5249 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="1"/>
-      <x:c r="B1" s="1"/>
-      <x:c r="C1" s="1"/>
-      <x:c r="D1" s="1"/>
-      <x:c r="E1" s="1"/>
-      <x:c r="F1" s="1"/>
-      <x:c r="G1" s="1"/>
-      <x:c r="H1" s="1"/>
-      <x:c r="I1" s="1"/>
-      <x:c r="J1" s="1"/>
-      <x:c r="K1" s="1"/>
-      <x:c r="L1" s="1"/>
-      <x:c r="M1" s="1"/>
-      <x:c r="N1" s="1"/>
-      <x:c r="O1" s="1"/>
-      <x:c r="P1" s="1"/>
-      <x:c r="Q1" s="1"/>
-      <x:c r="R1" s="1"/>
-      <x:c r="S1" s="1"/>
-      <x:c r="T1" s="1"/>
-      <x:c r="U1" s="1"/>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="2" t="str">
+      <x:c r="A1" s="20"/>
+      <x:c r="B1" s="20"/>
+      <x:c r="C1" s="20"/>
+      <x:c r="D1" s="20"/>
+      <x:c r="E1" s="20"/>
+      <x:c r="F1" s="20"/>
+      <x:c r="G1" s="20"/>
+      <x:c r="H1" s="20"/>
+      <x:c r="I1" s="20"/>
+      <x:c r="J1" s="20"/>
+      <x:c r="K1" s="20"/>
+      <x:c r="L1" s="20"/>
+      <x:c r="M1" s="20"/>
+      <x:c r="N1" s="20"/>
+      <x:c r="O1" s="20"/>
+      <x:c r="P1" s="20"/>
+      <x:c r="Q1" s="20"/>
+      <x:c r="R1" s="20"/>
+      <x:c r="S1" s="20"/>
+      <x:c r="T1" s="20"/>
+      <x:c r="U1" s="20"/>
+    </x:row>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="24" t="str">
         <x:v>DC01 | Vulnerability register</x:v>
       </x:c>
-      <x:c r="B2" s="1"/>
-      <x:c r="C2" s="1"/>
-      <x:c r="D2" s="1"/>
-      <x:c r="E2" s="1"/>
-      <x:c r="F2" s="1"/>
-      <x:c r="G2" s="1"/>
-      <x:c r="H2" s="1"/>
-      <x:c r="I2" s="1"/>
-      <x:c r="J2" s="1"/>
-      <x:c r="K2" s="1"/>
-      <x:c r="L2" s="1"/>
-      <x:c r="M2" s="1"/>
-      <x:c r="N2" s="1"/>
-      <x:c r="O2" s="1"/>
-      <x:c r="P2" s="1"/>
-      <x:c r="Q2" s="1"/>
-      <x:c r="R2" s="1"/>
-      <x:c r="S2" s="1"/>
-      <x:c r="T2" s="1"/>
-      <x:c r="U2" s="1"/>
+      <x:c r="B2" s="20"/>
+      <x:c r="C2" s="20"/>
+      <x:c r="D2" s="20"/>
+      <x:c r="E2" s="20"/>
+      <x:c r="F2" s="20"/>
+      <x:c r="G2" s="20"/>
+      <x:c r="H2" s="20"/>
+      <x:c r="I2" s="20"/>
+      <x:c r="J2" s="20"/>
+      <x:c r="K2" s="20"/>
+      <x:c r="L2" s="20"/>
+      <x:c r="M2" s="20"/>
+      <x:c r="N2" s="20"/>
+      <x:c r="O2" s="20"/>
+      <x:c r="P2" s="20"/>
+      <x:c r="Q2" s="20"/>
+      <x:c r="R2" s="20"/>
+      <x:c r="S2" s="20"/>
+      <x:c r="T2" s="20"/>
+      <x:c r="U2" s="20"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="1"/>
-      <x:c r="B3" s="1"/>
-      <x:c r="C3" s="1"/>
-      <x:c r="D3" s="1"/>
-      <x:c r="E3" s="1"/>
-      <x:c r="F3" s="1"/>
-      <x:c r="G3" s="1"/>
-      <x:c r="H3" s="1"/>
-      <x:c r="I3" s="1"/>
-      <x:c r="J3" s="1"/>
-      <x:c r="K3" s="1"/>
-      <x:c r="L3" s="1"/>
-      <x:c r="M3" s="1"/>
-      <x:c r="N3" s="1"/>
-      <x:c r="O3" s="1"/>
-      <x:c r="P3" s="1"/>
-      <x:c r="Q3" s="1"/>
-      <x:c r="R3" s="1"/>
-      <x:c r="S3" s="1"/>
-      <x:c r="T3" s="1"/>
-      <x:c r="U3" s="1"/>
+      <x:c r="A3" s="20" t="str">
+        <x:v>Baseline scores are historical. Status changes require verification evidence. Scroll right for ownership, change, and evidence fields.</x:v>
+      </x:c>
+      <x:c r="B3" s="20"/>
+      <x:c r="C3" s="20"/>
+      <x:c r="D3" s="20"/>
+      <x:c r="E3" s="20"/>
+      <x:c r="F3" s="20"/>
+      <x:c r="G3" s="20"/>
+      <x:c r="H3" s="20"/>
+      <x:c r="I3" s="20"/>
+      <x:c r="J3" s="20"/>
+      <x:c r="K3" s="20"/>
+      <x:c r="L3" s="20"/>
+      <x:c r="M3" s="20"/>
+      <x:c r="N3" s="20"/>
+      <x:c r="O3" s="20"/>
+      <x:c r="P3" s="20"/>
+      <x:c r="Q3" s="20"/>
+      <x:c r="R3" s="20"/>
+      <x:c r="S3" s="20"/>
+      <x:c r="T3" s="20"/>
+      <x:c r="U3" s="20"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="1"/>
-      <x:c r="B4" s="1"/>
-      <x:c r="C4" s="1"/>
-      <x:c r="D4" s="1"/>
-      <x:c r="E4" s="1"/>
-      <x:c r="F4" s="1"/>
-      <x:c r="G4" s="1"/>
-      <x:c r="H4" s="1"/>
-      <x:c r="I4" s="1"/>
-      <x:c r="J4" s="1"/>
-      <x:c r="K4" s="1"/>
-      <x:c r="L4" s="1"/>
-      <x:c r="M4" s="1"/>
-      <x:c r="N4" s="1"/>
-      <x:c r="O4" s="1"/>
-      <x:c r="P4" s="1"/>
-      <x:c r="Q4" s="1"/>
-      <x:c r="R4" s="1"/>
-      <x:c r="S4" s="1"/>
-      <x:c r="T4" s="1"/>
-      <x:c r="U4" s="1"/>
-    </x:row>
-    <x:row r="5" ht="34" customHeight="1">
-      <x:c r="A5" s="7" t="str">
+      <x:c r="A4" s="20"/>
+      <x:c r="B4" s="20"/>
+      <x:c r="C4" s="20"/>
+      <x:c r="D4" s="20"/>
+      <x:c r="E4" s="20"/>
+      <x:c r="F4" s="20"/>
+      <x:c r="G4" s="20"/>
+      <x:c r="H4" s="20"/>
+      <x:c r="I4" s="20"/>
+      <x:c r="J4" s="20"/>
+      <x:c r="K4" s="20"/>
+      <x:c r="L4" s="20"/>
+      <x:c r="M4" s="20"/>
+      <x:c r="N4" s="20"/>
+      <x:c r="O4" s="20"/>
+      <x:c r="P4" s="20"/>
+      <x:c r="Q4" s="20"/>
+      <x:c r="R4" s="20"/>
+      <x:c r="S4" s="20"/>
+      <x:c r="T4" s="20"/>
+      <x:c r="U4" s="20"/>
+    </x:row>
+    <x:row r="5" ht="42" customHeight="1">
+      <x:c r="A5" s="33" t="str">
         <x:v>Finding ID</x:v>
       </x:c>
-      <x:c r="B5" s="7" t="str">
+      <x:c r="B5" s="33" t="str">
         <x:v>Asset / IP</x:v>
       </x:c>
-      <x:c r="C5" s="7" t="str">
+      <x:c r="C5" s="33" t="str">
         <x:v>Finding / CVE</x:v>
       </x:c>
-      <x:c r="D5" s="7" t="str">
+      <x:c r="D5" s="33" t="str">
         <x:v>Plugin ID</x:v>
       </x:c>
-      <x:c r="E5" s="7" t="str">
+      <x:c r="E5" s="33" t="str">
         <x:v>Nessus severity</x:v>
       </x:c>
-      <x:c r="F5" s="7" t="str">
+      <x:c r="F5" s="33" t="str">
         <x:v>CVSS version</x:v>
       </x:c>
-      <x:c r="G5" s="7" t="str">
+      <x:c r="G5" s="33" t="str">
         <x:v>Base score</x:v>
       </x:c>
-      <x:c r="H5" s="7" t="str">
+      <x:c r="H5" s="33" t="str">
         <x:v>VPR at baseline</x:v>
       </x:c>
-      <x:c r="I5" s="7" t="str">
+      <x:c r="I5" s="33" t="str">
         <x:v>EPSS at baseline</x:v>
       </x:c>
-      <x:c r="J5" s="7" t="str">
+      <x:c r="J5" s="33" t="str">
         <x:v>Score date</x:v>
       </x:c>
-      <x:c r="K5" s="7" t="str">
+      <x:c r="K5" s="33" t="str">
         <x:v>Lab priority / rationale</x:v>
       </x:c>
-      <x:c r="L5" s="7" t="str">
+      <x:c r="L5" s="33" t="str">
         <x:v>Status</x:v>
       </x:c>
-      <x:c r="M5" s="7" t="str">
+      <x:c r="M5" s="33" t="str">
         <x:v>Detected date</x:v>
       </x:c>
-      <x:c r="N5" s="7" t="str">
+      <x:c r="N5" s="33" t="str">
         <x:v>Target date</x:v>
       </x:c>
-      <x:c r="O5" s="7" t="str">
+      <x:c r="O5" s="33" t="str">
         <x:v>Closed date</x:v>
       </x:c>
-      <x:c r="P5" s="7" t="str">
+      <x:c r="P5" s="33" t="str">
         <x:v>Owner role</x:v>
       </x:c>
-      <x:c r="Q5" s="7" t="str">
+      <x:c r="Q5" s="33" t="str">
         <x:v>Change ID</x:v>
       </x:c>
-      <x:c r="R5" s="7" t="str">
+      <x:c r="R5" s="33" t="str">
         <x:v>Baseline condition</x:v>
       </x:c>
-      <x:c r="S5" s="7" t="str">
+      <x:c r="S5" s="33" t="str">
         <x:v>Verification / limits</x:v>
       </x:c>
-      <x:c r="T5" s="7" t="str">
+      <x:c r="T5" s="33" t="str">
         <x:v>Evidence IDs</x:v>
       </x:c>
-      <x:c r="U5" s="7" t="str">
+      <x:c r="U5" s="33" t="str">
         <x:v>Overdue</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="110" customHeight="1">
-      <x:c r="A6" s="8" t="str">
+    <x:row r="6" ht="125" customHeight="1">
+      <x:c r="A6" s="34" t="str">
         <x:v>DC01-VULN-001</x:v>
       </x:c>
-      <x:c r="B6" s="8" t="str">
+      <x:c r="B6" s="34" t="str">
         <x:v>DC01 / 192.168.77.10</x:v>
       </x:c>
-      <x:c r="C6" s="8" t="str">
+      <x:c r="C6" s="34" t="str">
         <x:v>WinVerifyTrust / CVE-2013-3900</x:v>
       </x:c>
-      <x:c r="D6" s="8" t="n">
+      <x:c r="D6" s="46" t="n">
         <x:v>166555</x:v>
       </x:c>
-      <x:c r="E6" s="8" t="str">
+      <x:c r="E6" s="46" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F6" s="8" t="str">
+      <x:c r="F6" s="46" t="str">
         <x:v>3.0</x:v>
       </x:c>
-      <x:c r="G6" s="11" t="n">
+      <x:c r="G6" s="47" t="n">
         <x:v>8.8</x:v>
       </x:c>
-      <x:c r="H6" s="11" t="n">
+      <x:c r="H6" s="47" t="n">
         <x:v>9.5</x:v>
       </x:c>
-      <x:c r="I6" s="10" t="n">
+      <x:c r="I6" s="48" t="n">
         <x:v>0.4465</x:v>
       </x:c>
-      <x:c r="J6" s="9" t="d">
+      <x:c r="J6" s="49" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="K6" s="8" t="str">
+      <x:c r="K6" s="34" t="str">
         <x:v>High: domain-controller role; high technical severity and threat prioritization. Lab judgment.</x:v>
       </x:c>
-      <x:c r="L6" s="8" t="str">
+      <x:c r="L6" s="46" t="str">
         <x:v>Closed</x:v>
       </x:c>
-      <x:c r="M6" s="9" t="d">
+      <x:c r="M6" s="49" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="N6" s="9"/>
-      <x:c r="O6" s="9" t="d">
+      <x:c r="N6" s="49"/>
+      <x:c r="O6" s="49" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="P6" s="8" t="str">
+      <x:c r="P6" s="34" t="str">
         <x:v>Lab operator (administrator + analyst)</x:v>
       </x:c>
-      <x:c r="Q6" s="8" t="str">
+      <x:c r="Q6" s="34" t="str">
         <x:v>LAB-CHG-012</x:v>
       </x:c>
-      <x:c r="R6" s="8" t="str">
+      <x:c r="R6" s="34" t="str">
         <x:v>EnableCertPaddingCheck absent in native and WOW6432Node paths.</x:v>
       </x:c>
-      <x:c r="S6" s="8" t="str">
+      <x:c r="S6" s="34" t="str">
         <x:v>Both DWORDs = 1; restart; operator-reported services/AD console pass; authenticated rescan and no WinVerifyTrust result. Scoped scanner closure, not proof of zero risk.</x:v>
       </x:c>
-      <x:c r="T6" s="8" t="str">
+      <x:c r="T6" s="34" t="str">
         <x:v>EV-003; EV-005; EV-006; EV-007; EV-008</x:v>
       </x:c>
-      <x:c r="U6" s="8" t="str">
+      <x:c r="U6" s="34" t="str">
         <x:f>IF(A6="","",IF(OR(L6="Closed",L6="False positive"),"No",IF(N6="","No target set",IF(N6&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
         <x:v>No</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="110" customHeight="1">
-      <x:c r="A7" s="8" t="str">
+    <x:row r="7" ht="125" customHeight="1">
+      <x:c r="A7" s="38" t="str">
         <x:v>DC01-VULN-002</x:v>
       </x:c>
-      <x:c r="B7" s="8" t="str">
+      <x:c r="B7" s="38" t="str">
         <x:v>DC01 / 192.168.77.10</x:v>
       </x:c>
-      <x:c r="C7" s="8" t="str">
+      <x:c r="C7" s="38" t="str">
         <x:v>Intel BHI / CVE-2022-0001</x:v>
       </x:c>
-      <x:c r="D7" s="8" t="n">
+      <x:c r="D7" s="50" t="n">
         <x:v>302873</x:v>
       </x:c>
-      <x:c r="E7" s="8" t="str">
+      <x:c r="E7" s="50" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="F7" s="8" t="str">
+      <x:c r="F7" s="50" t="str">
         <x:v>3.0</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="n">
+      <x:c r="G7" s="51" t="n">
         <x:v>6.5</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="n">
+      <x:c r="H7" s="51" t="n">
         <x:v>3.3</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="n">
+      <x:c r="I7" s="52" t="n">
         <x:v>0.0046</x:v>
       </x:c>
-      <x:c r="J7" s="9" t="d">
+      <x:c r="J7" s="53" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="K7" s="8" t="str">
+      <x:c r="K7" s="38" t="str">
         <x:v>Medium: lab judgment due to DC role; local attack conditions and lower threat scores. Nessus label retained separately.</x:v>
       </x:c>
-      <x:c r="L7" s="8" t="str">
+      <x:c r="L7" s="50" t="str">
         <x:v>Closed</x:v>
       </x:c>
-      <x:c r="M7" s="9" t="d">
+      <x:c r="M7" s="53" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="N7" s="9"/>
-      <x:c r="O7" s="9" t="d">
+      <x:c r="N7" s="53"/>
+      <x:c r="O7" s="53" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="P7" s="8" t="str">
+      <x:c r="P7" s="38" t="str">
         <x:v>Lab operator (administrator + analyst)</x:v>
       </x:c>
-      <x:c r="Q7" s="8" t="str">
+      <x:c r="Q7" s="38" t="str">
         <x:v>LAB-CHG-013</x:v>
       </x:c>
-      <x:c r="R7" s="8" t="str">
+      <x:c r="R7" s="38" t="str">
         <x:v>FeatureSettingsOverride and mask absent.</x:v>
       </x:c>
-      <x:c r="S7" s="8" t="str">
+      <x:c r="S7" s="38" t="str">
         <x:v>Override 8388608, mask 3; restart; operator-reported checks pass; authenticated all-Info scan and Windows group Info. Guest configuration only; physical host protection unverified.</x:v>
       </x:c>
-      <x:c r="T7" s="8" t="str">
+      <x:c r="T7" s="38" t="str">
         <x:v>EV-004; EV-009; EV-010; EV-011; EV-012; EV-013</x:v>
       </x:c>
-      <x:c r="U7" s="8" t="str">
+      <x:c r="U7" s="38" t="str">
         <x:f>IF(A7="","",IF(OR(L7="Closed",L7="False positive"),"No",IF(N7="","No target set",IF(N7&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
         <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="U8" t="str">
+      <x:c r="A8" s="20"/>
+      <x:c r="B8" s="20"/>
+      <x:c r="C8" s="20"/>
+      <x:c r="D8" s="20"/>
+      <x:c r="E8" s="20"/>
+      <x:c r="F8" s="20"/>
+      <x:c r="G8" s="20"/>
+      <x:c r="H8" s="20"/>
+      <x:c r="I8" s="20"/>
+      <x:c r="J8" s="20"/>
+      <x:c r="K8" s="20"/>
+      <x:c r="L8" s="20"/>
+      <x:c r="M8" s="20"/>
+      <x:c r="N8" s="20"/>
+      <x:c r="O8" s="20"/>
+      <x:c r="P8" s="20"/>
+      <x:c r="Q8" s="20"/>
+      <x:c r="R8" s="20"/>
+      <x:c r="S8" s="20"/>
+      <x:c r="T8" s="20"/>
+      <x:c r="U8" s="20" t="str">
         <x:f>IF(A8="","",IF(OR(L8="Closed",L8="False positive"),"No",IF(N8="","No target set",IF(N8&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="U9" t="str">
+      <x:c r="A9" s="20"/>
+      <x:c r="B9" s="20"/>
+      <x:c r="C9" s="20"/>
+      <x:c r="D9" s="20"/>
+      <x:c r="E9" s="20"/>
+      <x:c r="F9" s="20"/>
+      <x:c r="G9" s="20"/>
+      <x:c r="H9" s="20"/>
+      <x:c r="I9" s="20"/>
+      <x:c r="J9" s="20"/>
+      <x:c r="K9" s="20"/>
+      <x:c r="L9" s="20"/>
+      <x:c r="M9" s="20"/>
+      <x:c r="N9" s="20"/>
+      <x:c r="O9" s="20"/>
+      <x:c r="P9" s="20"/>
+      <x:c r="Q9" s="20"/>
+      <x:c r="R9" s="20"/>
+      <x:c r="S9" s="20"/>
+      <x:c r="T9" s="20"/>
+      <x:c r="U9" s="20" t="str">
         <x:f>IF(A9="","",IF(OR(L9="Closed",L9="False positive"),"No",IF(N9="","No target set",IF(N9&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="U10" t="str">
+      <x:c r="A10" s="20"/>
+      <x:c r="B10" s="20"/>
+      <x:c r="C10" s="20"/>
+      <x:c r="D10" s="20"/>
+      <x:c r="E10" s="20"/>
+      <x:c r="F10" s="20"/>
+      <x:c r="G10" s="20"/>
+      <x:c r="H10" s="20"/>
+      <x:c r="I10" s="20"/>
+      <x:c r="J10" s="20"/>
+      <x:c r="K10" s="20"/>
+      <x:c r="L10" s="20"/>
+      <x:c r="M10" s="20"/>
+      <x:c r="N10" s="20"/>
+      <x:c r="O10" s="20"/>
+      <x:c r="P10" s="20"/>
+      <x:c r="Q10" s="20"/>
+      <x:c r="R10" s="20"/>
+      <x:c r="S10" s="20"/>
+      <x:c r="T10" s="20"/>
+      <x:c r="U10" s="20" t="str">
         <x:f>IF(A10="","",IF(OR(L10="Closed",L10="False positive"),"No",IF(N10="","No target set",IF(N10&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="U11" t="str">
+      <x:c r="A11" s="20"/>
+      <x:c r="B11" s="20"/>
+      <x:c r="C11" s="20"/>
+      <x:c r="D11" s="20"/>
+      <x:c r="E11" s="20"/>
+      <x:c r="F11" s="20"/>
+      <x:c r="G11" s="20"/>
+      <x:c r="H11" s="20"/>
+      <x:c r="I11" s="20"/>
+      <x:c r="J11" s="20"/>
+      <x:c r="K11" s="20"/>
+      <x:c r="L11" s="20"/>
+      <x:c r="M11" s="20"/>
+      <x:c r="N11" s="20"/>
+      <x:c r="O11" s="20"/>
+      <x:c r="P11" s="20"/>
+      <x:c r="Q11" s="20"/>
+      <x:c r="R11" s="20"/>
+      <x:c r="S11" s="20"/>
+      <x:c r="T11" s="20"/>
+      <x:c r="U11" s="20" t="str">
         <x:f>IF(A11="","",IF(OR(L11="Closed",L11="False positive"),"No",IF(N11="","No target set",IF(N11&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="U12" t="str">
+      <x:c r="A12" s="20"/>
+      <x:c r="B12" s="20"/>
+      <x:c r="C12" s="20"/>
+      <x:c r="D12" s="20"/>
+      <x:c r="E12" s="20"/>
+      <x:c r="F12" s="20"/>
+      <x:c r="G12" s="20"/>
+      <x:c r="H12" s="20"/>
+      <x:c r="I12" s="20"/>
+      <x:c r="J12" s="20"/>
+      <x:c r="K12" s="20"/>
+      <x:c r="L12" s="20"/>
+      <x:c r="M12" s="20"/>
+      <x:c r="N12" s="20"/>
+      <x:c r="O12" s="20"/>
+      <x:c r="P12" s="20"/>
+      <x:c r="Q12" s="20"/>
+      <x:c r="R12" s="20"/>
+      <x:c r="S12" s="20"/>
+      <x:c r="T12" s="20"/>
+      <x:c r="U12" s="20" t="str">
         <x:f>IF(A12="","",IF(OR(L12="Closed",L12="False positive"),"No",IF(N12="","No target set",IF(N12&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="U13" t="str">
+      <x:c r="A13" s="20"/>
+      <x:c r="B13" s="20"/>
+      <x:c r="C13" s="20"/>
+      <x:c r="D13" s="20"/>
+      <x:c r="E13" s="20"/>
+      <x:c r="F13" s="20"/>
+      <x:c r="G13" s="20"/>
+      <x:c r="H13" s="20"/>
+      <x:c r="I13" s="20"/>
+      <x:c r="J13" s="20"/>
+      <x:c r="K13" s="20"/>
+      <x:c r="L13" s="20"/>
+      <x:c r="M13" s="20"/>
+      <x:c r="N13" s="20"/>
+      <x:c r="O13" s="20"/>
+      <x:c r="P13" s="20"/>
+      <x:c r="Q13" s="20"/>
+      <x:c r="R13" s="20"/>
+      <x:c r="S13" s="20"/>
+      <x:c r="T13" s="20"/>
+      <x:c r="U13" s="20" t="str">
         <x:f>IF(A13="","",IF(OR(L13="Closed",L13="False positive"),"No",IF(N13="","No target set",IF(N13&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="U14" t="str">
+      <x:c r="A14" s="20"/>
+      <x:c r="B14" s="20"/>
+      <x:c r="C14" s="20"/>
+      <x:c r="D14" s="20"/>
+      <x:c r="E14" s="20"/>
+      <x:c r="F14" s="20"/>
+      <x:c r="G14" s="20"/>
+      <x:c r="H14" s="20"/>
+      <x:c r="I14" s="20"/>
+      <x:c r="J14" s="20"/>
+      <x:c r="K14" s="20"/>
+      <x:c r="L14" s="20"/>
+      <x:c r="M14" s="20"/>
+      <x:c r="N14" s="20"/>
+      <x:c r="O14" s="20"/>
+      <x:c r="P14" s="20"/>
+      <x:c r="Q14" s="20"/>
+      <x:c r="R14" s="20"/>
+      <x:c r="S14" s="20"/>
+      <x:c r="T14" s="20"/>
+      <x:c r="U14" s="20" t="str">
         <x:f>IF(A14="","",IF(OR(L14="Closed",L14="False positive"),"No",IF(N14="","No target set",IF(N14&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="U15" t="str">
+      <x:c r="A15" s="20"/>
+      <x:c r="B15" s="20"/>
+      <x:c r="C15" s="20"/>
+      <x:c r="D15" s="20"/>
+      <x:c r="E15" s="20"/>
+      <x:c r="F15" s="20"/>
+      <x:c r="G15" s="20"/>
+      <x:c r="H15" s="20"/>
+      <x:c r="I15" s="20"/>
+      <x:c r="J15" s="20"/>
+      <x:c r="K15" s="20"/>
+      <x:c r="L15" s="20"/>
+      <x:c r="M15" s="20"/>
+      <x:c r="N15" s="20"/>
+      <x:c r="O15" s="20"/>
+      <x:c r="P15" s="20"/>
+      <x:c r="Q15" s="20"/>
+      <x:c r="R15" s="20"/>
+      <x:c r="S15" s="20"/>
+      <x:c r="T15" s="20"/>
+      <x:c r="U15" s="20" t="str">
         <x:f>IF(A15="","",IF(OR(L15="Closed",L15="False positive"),"No",IF(N15="","No target set",IF(N15&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="U16" t="str">
+      <x:c r="A16" s="20"/>
+      <x:c r="B16" s="20"/>
+      <x:c r="C16" s="20"/>
+      <x:c r="D16" s="20"/>
+      <x:c r="E16" s="20"/>
+      <x:c r="F16" s="20"/>
+      <x:c r="G16" s="20"/>
+      <x:c r="H16" s="20"/>
+      <x:c r="I16" s="20"/>
+      <x:c r="J16" s="20"/>
+      <x:c r="K16" s="20"/>
+      <x:c r="L16" s="20"/>
+      <x:c r="M16" s="20"/>
+      <x:c r="N16" s="20"/>
+      <x:c r="O16" s="20"/>
+      <x:c r="P16" s="20"/>
+      <x:c r="Q16" s="20"/>
+      <x:c r="R16" s="20"/>
+      <x:c r="S16" s="20"/>
+      <x:c r="T16" s="20"/>
+      <x:c r="U16" s="20" t="str">
         <x:f>IF(A16="","",IF(OR(L16="Closed",L16="False positive"),"No",IF(N16="","No target set",IF(N16&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="U17" t="str">
+      <x:c r="A17" s="20"/>
+      <x:c r="B17" s="20"/>
+      <x:c r="C17" s="20"/>
+      <x:c r="D17" s="20"/>
+      <x:c r="E17" s="20"/>
+      <x:c r="F17" s="20"/>
+      <x:c r="G17" s="20"/>
+      <x:c r="H17" s="20"/>
+      <x:c r="I17" s="20"/>
+      <x:c r="J17" s="20"/>
+      <x:c r="K17" s="20"/>
+      <x:c r="L17" s="20"/>
+      <x:c r="M17" s="20"/>
+      <x:c r="N17" s="20"/>
+      <x:c r="O17" s="20"/>
+      <x:c r="P17" s="20"/>
+      <x:c r="Q17" s="20"/>
+      <x:c r="R17" s="20"/>
+      <x:c r="S17" s="20"/>
+      <x:c r="T17" s="20"/>
+      <x:c r="U17" s="20" t="str">
         <x:f>IF(A17="","",IF(OR(L17="Closed",L17="False positive"),"No",IF(N17="","No target set",IF(N17&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="U18" t="str">
+      <x:c r="A18" s="20"/>
+      <x:c r="B18" s="20"/>
+      <x:c r="C18" s="20"/>
+      <x:c r="D18" s="20"/>
+      <x:c r="E18" s="20"/>
+      <x:c r="F18" s="20"/>
+      <x:c r="G18" s="20"/>
+      <x:c r="H18" s="20"/>
+      <x:c r="I18" s="20"/>
+      <x:c r="J18" s="20"/>
+      <x:c r="K18" s="20"/>
+      <x:c r="L18" s="20"/>
+      <x:c r="M18" s="20"/>
+      <x:c r="N18" s="20"/>
+      <x:c r="O18" s="20"/>
+      <x:c r="P18" s="20"/>
+      <x:c r="Q18" s="20"/>
+      <x:c r="R18" s="20"/>
+      <x:c r="S18" s="20"/>
+      <x:c r="T18" s="20"/>
+      <x:c r="U18" s="20" t="str">
         <x:f>IF(A18="","",IF(OR(L18="Closed",L18="False positive"),"No",IF(N18="","No target set",IF(N18&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="U19" t="str">
+      <x:c r="A19" s="20"/>
+      <x:c r="B19" s="20"/>
+      <x:c r="C19" s="20"/>
+      <x:c r="D19" s="20"/>
+      <x:c r="E19" s="20"/>
+      <x:c r="F19" s="20"/>
+      <x:c r="G19" s="20"/>
+      <x:c r="H19" s="20"/>
+      <x:c r="I19" s="20"/>
+      <x:c r="J19" s="20"/>
+      <x:c r="K19" s="20"/>
+      <x:c r="L19" s="20"/>
+      <x:c r="M19" s="20"/>
+      <x:c r="N19" s="20"/>
+      <x:c r="O19" s="20"/>
+      <x:c r="P19" s="20"/>
+      <x:c r="Q19" s="20"/>
+      <x:c r="R19" s="20"/>
+      <x:c r="S19" s="20"/>
+      <x:c r="T19" s="20"/>
+      <x:c r="U19" s="20" t="str">
         <x:f>IF(A19="","",IF(OR(L19="Closed",L19="False positive"),"No",IF(N19="","No target set",IF(N19&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="U20" t="str">
+      <x:c r="A20" s="20"/>
+      <x:c r="B20" s="20"/>
+      <x:c r="C20" s="20"/>
+      <x:c r="D20" s="20"/>
+      <x:c r="E20" s="20"/>
+      <x:c r="F20" s="20"/>
+      <x:c r="G20" s="20"/>
+      <x:c r="H20" s="20"/>
+      <x:c r="I20" s="20"/>
+      <x:c r="J20" s="20"/>
+      <x:c r="K20" s="20"/>
+      <x:c r="L20" s="20"/>
+      <x:c r="M20" s="20"/>
+      <x:c r="N20" s="20"/>
+      <x:c r="O20" s="20"/>
+      <x:c r="P20" s="20"/>
+      <x:c r="Q20" s="20"/>
+      <x:c r="R20" s="20"/>
+      <x:c r="S20" s="20"/>
+      <x:c r="T20" s="20"/>
+      <x:c r="U20" s="20" t="str">
         <x:f>IF(A20="","",IF(OR(L20="Closed",L20="False positive"),"No",IF(N20="","No target set",IF(N20&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="U21" t="str">
+      <x:c r="A21" s="20"/>
+      <x:c r="B21" s="20"/>
+      <x:c r="C21" s="20"/>
+      <x:c r="D21" s="20"/>
+      <x:c r="E21" s="20"/>
+      <x:c r="F21" s="20"/>
+      <x:c r="G21" s="20"/>
+      <x:c r="H21" s="20"/>
+      <x:c r="I21" s="20"/>
+      <x:c r="J21" s="20"/>
+      <x:c r="K21" s="20"/>
+      <x:c r="L21" s="20"/>
+      <x:c r="M21" s="20"/>
+      <x:c r="N21" s="20"/>
+      <x:c r="O21" s="20"/>
+      <x:c r="P21" s="20"/>
+      <x:c r="Q21" s="20"/>
+      <x:c r="R21" s="20"/>
+      <x:c r="S21" s="20"/>
+      <x:c r="T21" s="20"/>
+      <x:c r="U21" s="20" t="str">
         <x:f>IF(A21="","",IF(OR(L21="Closed",L21="False positive"),"No",IF(N21="","No target set",IF(N21&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="U22" t="str">
+      <x:c r="A22" s="20"/>
+      <x:c r="B22" s="20"/>
+      <x:c r="C22" s="20"/>
+      <x:c r="D22" s="20"/>
+      <x:c r="E22" s="20"/>
+      <x:c r="F22" s="20"/>
+      <x:c r="G22" s="20"/>
+      <x:c r="H22" s="20"/>
+      <x:c r="I22" s="20"/>
+      <x:c r="J22" s="20"/>
+      <x:c r="K22" s="20"/>
+      <x:c r="L22" s="20"/>
+      <x:c r="M22" s="20"/>
+      <x:c r="N22" s="20"/>
+      <x:c r="O22" s="20"/>
+      <x:c r="P22" s="20"/>
+      <x:c r="Q22" s="20"/>
+      <x:c r="R22" s="20"/>
+      <x:c r="S22" s="20"/>
+      <x:c r="T22" s="20"/>
+      <x:c r="U22" s="20" t="str">
         <x:f>IF(A22="","",IF(OR(L22="Closed",L22="False positive"),"No",IF(N22="","No target set",IF(N22&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="U23" t="str">
+      <x:c r="A23" s="20"/>
+      <x:c r="B23" s="20"/>
+      <x:c r="C23" s="20"/>
+      <x:c r="D23" s="20"/>
+      <x:c r="E23" s="20"/>
+      <x:c r="F23" s="20"/>
+      <x:c r="G23" s="20"/>
+      <x:c r="H23" s="20"/>
+      <x:c r="I23" s="20"/>
+      <x:c r="J23" s="20"/>
+      <x:c r="K23" s="20"/>
+      <x:c r="L23" s="20"/>
+      <x:c r="M23" s="20"/>
+      <x:c r="N23" s="20"/>
+      <x:c r="O23" s="20"/>
+      <x:c r="P23" s="20"/>
+      <x:c r="Q23" s="20"/>
+      <x:c r="R23" s="20"/>
+      <x:c r="S23" s="20"/>
+      <x:c r="T23" s="20"/>
+      <x:c r="U23" s="20" t="str">
         <x:f>IF(A23="","",IF(OR(L23="Closed",L23="False positive"),"No",IF(N23="","No target set",IF(N23&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="U24" t="str">
+      <x:c r="A24" s="20"/>
+      <x:c r="B24" s="20"/>
+      <x:c r="C24" s="20"/>
+      <x:c r="D24" s="20"/>
+      <x:c r="E24" s="20"/>
+      <x:c r="F24" s="20"/>
+      <x:c r="G24" s="20"/>
+      <x:c r="H24" s="20"/>
+      <x:c r="I24" s="20"/>
+      <x:c r="J24" s="20"/>
+      <x:c r="K24" s="20"/>
+      <x:c r="L24" s="20"/>
+      <x:c r="M24" s="20"/>
+      <x:c r="N24" s="20"/>
+      <x:c r="O24" s="20"/>
+      <x:c r="P24" s="20"/>
+      <x:c r="Q24" s="20"/>
+      <x:c r="R24" s="20"/>
+      <x:c r="S24" s="20"/>
+      <x:c r="T24" s="20"/>
+      <x:c r="U24" s="20" t="str">
         <x:f>IF(A24="","",IF(OR(L24="Closed",L24="False positive"),"No",IF(N24="","No target set",IF(N24&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="U25" t="str">
+      <x:c r="A25" s="20"/>
+      <x:c r="B25" s="20"/>
+      <x:c r="C25" s="20"/>
+      <x:c r="D25" s="20"/>
+      <x:c r="E25" s="20"/>
+      <x:c r="F25" s="20"/>
+      <x:c r="G25" s="20"/>
+      <x:c r="H25" s="20"/>
+      <x:c r="I25" s="20"/>
+      <x:c r="J25" s="20"/>
+      <x:c r="K25" s="20"/>
+      <x:c r="L25" s="20"/>
+      <x:c r="M25" s="20"/>
+      <x:c r="N25" s="20"/>
+      <x:c r="O25" s="20"/>
+      <x:c r="P25" s="20"/>
+      <x:c r="Q25" s="20"/>
+      <x:c r="R25" s="20"/>
+      <x:c r="S25" s="20"/>
+      <x:c r="T25" s="20"/>
+      <x:c r="U25" s="20" t="str">
         <x:f>IF(A25="","",IF(OR(L25="Closed",L25="False positive"),"No",IF(N25="","No target set",IF(N25&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="U26" t="str">
+      <x:c r="A26" s="20"/>
+      <x:c r="B26" s="20"/>
+      <x:c r="C26" s="20"/>
+      <x:c r="D26" s="20"/>
+      <x:c r="E26" s="20"/>
+      <x:c r="F26" s="20"/>
+      <x:c r="G26" s="20"/>
+      <x:c r="H26" s="20"/>
+      <x:c r="I26" s="20"/>
+      <x:c r="J26" s="20"/>
+      <x:c r="K26" s="20"/>
+      <x:c r="L26" s="20"/>
+      <x:c r="M26" s="20"/>
+      <x:c r="N26" s="20"/>
+      <x:c r="O26" s="20"/>
+      <x:c r="P26" s="20"/>
+      <x:c r="Q26" s="20"/>
+      <x:c r="R26" s="20"/>
+      <x:c r="S26" s="20"/>
+      <x:c r="T26" s="20"/>
+      <x:c r="U26" s="20" t="str">
         <x:f>IF(A26="","",IF(OR(L26="Closed",L26="False positive"),"No",IF(N26="","No target set",IF(N26&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="27">
-      <x:c r="U27" t="str">
+      <x:c r="A27" s="20"/>
+      <x:c r="B27" s="20"/>
+      <x:c r="C27" s="20"/>
+      <x:c r="D27" s="20"/>
+      <x:c r="E27" s="20"/>
+      <x:c r="F27" s="20"/>
+      <x:c r="G27" s="20"/>
+      <x:c r="H27" s="20"/>
+      <x:c r="I27" s="20"/>
+      <x:c r="J27" s="20"/>
+      <x:c r="K27" s="20"/>
+      <x:c r="L27" s="20"/>
+      <x:c r="M27" s="20"/>
+      <x:c r="N27" s="20"/>
+      <x:c r="O27" s="20"/>
+      <x:c r="P27" s="20"/>
+      <x:c r="Q27" s="20"/>
+      <x:c r="R27" s="20"/>
+      <x:c r="S27" s="20"/>
+      <x:c r="T27" s="20"/>
+      <x:c r="U27" s="20" t="str">
         <x:f>IF(A27="","",IF(OR(L27="Closed",L27="False positive"),"No",IF(N27="","No target set",IF(N27&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="28">
-      <x:c r="U28" t="str">
+      <x:c r="A28" s="20"/>
+      <x:c r="B28" s="20"/>
+      <x:c r="C28" s="20"/>
+      <x:c r="D28" s="20"/>
+      <x:c r="E28" s="20"/>
+      <x:c r="F28" s="20"/>
+      <x:c r="G28" s="20"/>
+      <x:c r="H28" s="20"/>
+      <x:c r="I28" s="20"/>
+      <x:c r="J28" s="20"/>
+      <x:c r="K28" s="20"/>
+      <x:c r="L28" s="20"/>
+      <x:c r="M28" s="20"/>
+      <x:c r="N28" s="20"/>
+      <x:c r="O28" s="20"/>
+      <x:c r="P28" s="20"/>
+      <x:c r="Q28" s="20"/>
+      <x:c r="R28" s="20"/>
+      <x:c r="S28" s="20"/>
+      <x:c r="T28" s="20"/>
+      <x:c r="U28" s="20" t="str">
         <x:f>IF(A28="","",IF(OR(L28="Closed",L28="False positive"),"No",IF(N28="","No target set",IF(N28&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="29">
-      <x:c r="U29" t="str">
+      <x:c r="A29" s="20"/>
+      <x:c r="B29" s="20"/>
+      <x:c r="C29" s="20"/>
+      <x:c r="D29" s="20"/>
+      <x:c r="E29" s="20"/>
+      <x:c r="F29" s="20"/>
+      <x:c r="G29" s="20"/>
+      <x:c r="H29" s="20"/>
+      <x:c r="I29" s="20"/>
+      <x:c r="J29" s="20"/>
+      <x:c r="K29" s="20"/>
+      <x:c r="L29" s="20"/>
+      <x:c r="M29" s="20"/>
+      <x:c r="N29" s="20"/>
+      <x:c r="O29" s="20"/>
+      <x:c r="P29" s="20"/>
+      <x:c r="Q29" s="20"/>
+      <x:c r="R29" s="20"/>
+      <x:c r="S29" s="20"/>
+      <x:c r="T29" s="20"/>
+      <x:c r="U29" s="20" t="str">
         <x:f>IF(A29="","",IF(OR(L29="Closed",L29="False positive"),"No",IF(N29="","No target set",IF(N29&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="30">
-      <x:c r="U30" t="str">
+      <x:c r="A30" s="20"/>
+      <x:c r="B30" s="20"/>
+      <x:c r="C30" s="20"/>
+      <x:c r="D30" s="20"/>
+      <x:c r="E30" s="20"/>
+      <x:c r="F30" s="20"/>
+      <x:c r="G30" s="20"/>
+      <x:c r="H30" s="20"/>
+      <x:c r="I30" s="20"/>
+      <x:c r="J30" s="20"/>
+      <x:c r="K30" s="20"/>
+      <x:c r="L30" s="20"/>
+      <x:c r="M30" s="20"/>
+      <x:c r="N30" s="20"/>
+      <x:c r="O30" s="20"/>
+      <x:c r="P30" s="20"/>
+      <x:c r="Q30" s="20"/>
+      <x:c r="R30" s="20"/>
+      <x:c r="S30" s="20"/>
+      <x:c r="T30" s="20"/>
+      <x:c r="U30" s="20" t="str">
         <x:f>IF(A30="","",IF(OR(L30="Closed",L30="False positive"),"No",IF(N30="","No target set",IF(N30&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="31">
-      <x:c r="U31" t="str">
+      <x:c r="A31" s="20"/>
+      <x:c r="B31" s="20"/>
+      <x:c r="C31" s="20"/>
+      <x:c r="D31" s="20"/>
+      <x:c r="E31" s="20"/>
+      <x:c r="F31" s="20"/>
+      <x:c r="G31" s="20"/>
+      <x:c r="H31" s="20"/>
+      <x:c r="I31" s="20"/>
+      <x:c r="J31" s="20"/>
+      <x:c r="K31" s="20"/>
+      <x:c r="L31" s="20"/>
+      <x:c r="M31" s="20"/>
+      <x:c r="N31" s="20"/>
+      <x:c r="O31" s="20"/>
+      <x:c r="P31" s="20"/>
+      <x:c r="Q31" s="20"/>
+      <x:c r="R31" s="20"/>
+      <x:c r="S31" s="20"/>
+      <x:c r="T31" s="20"/>
+      <x:c r="U31" s="20" t="str">
         <x:f>IF(A31="","",IF(OR(L31="Closed",L31="False positive"),"No",IF(N31="","No target set",IF(N31&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="32">
-      <x:c r="U32" t="str">
+      <x:c r="A32" s="20"/>
+      <x:c r="B32" s="20"/>
+      <x:c r="C32" s="20"/>
+      <x:c r="D32" s="20"/>
+      <x:c r="E32" s="20"/>
+      <x:c r="F32" s="20"/>
+      <x:c r="G32" s="20"/>
+      <x:c r="H32" s="20"/>
+      <x:c r="I32" s="20"/>
+      <x:c r="J32" s="20"/>
+      <x:c r="K32" s="20"/>
+      <x:c r="L32" s="20"/>
+      <x:c r="M32" s="20"/>
+      <x:c r="N32" s="20"/>
+      <x:c r="O32" s="20"/>
+      <x:c r="P32" s="20"/>
+      <x:c r="Q32" s="20"/>
+      <x:c r="R32" s="20"/>
+      <x:c r="S32" s="20"/>
+      <x:c r="T32" s="20"/>
+      <x:c r="U32" s="20" t="str">
         <x:f>IF(A32="","",IF(OR(L32="Closed",L32="False positive"),"No",IF(N32="","No target set",IF(N32&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="33">
-      <x:c r="U33" t="str">
+      <x:c r="A33" s="20"/>
+      <x:c r="B33" s="20"/>
+      <x:c r="C33" s="20"/>
+      <x:c r="D33" s="20"/>
+      <x:c r="E33" s="20"/>
+      <x:c r="F33" s="20"/>
+      <x:c r="G33" s="20"/>
+      <x:c r="H33" s="20"/>
+      <x:c r="I33" s="20"/>
+      <x:c r="J33" s="20"/>
+      <x:c r="K33" s="20"/>
+      <x:c r="L33" s="20"/>
+      <x:c r="M33" s="20"/>
+      <x:c r="N33" s="20"/>
+      <x:c r="O33" s="20"/>
+      <x:c r="P33" s="20"/>
+      <x:c r="Q33" s="20"/>
+      <x:c r="R33" s="20"/>
+      <x:c r="S33" s="20"/>
+      <x:c r="T33" s="20"/>
+      <x:c r="U33" s="20" t="str">
         <x:f>IF(A33="","",IF(OR(L33="Closed",L33="False positive"),"No",IF(N33="","No target set",IF(N33&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="34">
-      <x:c r="U34" t="str">
+      <x:c r="A34" s="20"/>
+      <x:c r="B34" s="20"/>
+      <x:c r="C34" s="20"/>
+      <x:c r="D34" s="20"/>
+      <x:c r="E34" s="20"/>
+      <x:c r="F34" s="20"/>
+      <x:c r="G34" s="20"/>
+      <x:c r="H34" s="20"/>
+      <x:c r="I34" s="20"/>
+      <x:c r="J34" s="20"/>
+      <x:c r="K34" s="20"/>
+      <x:c r="L34" s="20"/>
+      <x:c r="M34" s="20"/>
+      <x:c r="N34" s="20"/>
+      <x:c r="O34" s="20"/>
+      <x:c r="P34" s="20"/>
+      <x:c r="Q34" s="20"/>
+      <x:c r="R34" s="20"/>
+      <x:c r="S34" s="20"/>
+      <x:c r="T34" s="20"/>
+      <x:c r="U34" s="20" t="str">
         <x:f>IF(A34="","",IF(OR(L34="Closed",L34="False positive"),"No",IF(N34="","No target set",IF(N34&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="35">
-      <x:c r="U35" t="str">
+      <x:c r="A35" s="20"/>
+      <x:c r="B35" s="20"/>
+      <x:c r="C35" s="20"/>
+      <x:c r="D35" s="20"/>
+      <x:c r="E35" s="20"/>
+      <x:c r="F35" s="20"/>
+      <x:c r="G35" s="20"/>
+      <x:c r="H35" s="20"/>
+      <x:c r="I35" s="20"/>
+      <x:c r="J35" s="20"/>
+      <x:c r="K35" s="20"/>
+      <x:c r="L35" s="20"/>
+      <x:c r="M35" s="20"/>
+      <x:c r="N35" s="20"/>
+      <x:c r="O35" s="20"/>
+      <x:c r="P35" s="20"/>
+      <x:c r="Q35" s="20"/>
+      <x:c r="R35" s="20"/>
+      <x:c r="S35" s="20"/>
+      <x:c r="T35" s="20"/>
+      <x:c r="U35" s="20" t="str">
         <x:f>IF(A35="","",IF(OR(L35="Closed",L35="False positive"),"No",IF(N35="","No target set",IF(N35&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="36">
-      <x:c r="U36" t="str">
+      <x:c r="A36" s="20"/>
+      <x:c r="B36" s="20"/>
+      <x:c r="C36" s="20"/>
+      <x:c r="D36" s="20"/>
+      <x:c r="E36" s="20"/>
+      <x:c r="F36" s="20"/>
+      <x:c r="G36" s="20"/>
+      <x:c r="H36" s="20"/>
+      <x:c r="I36" s="20"/>
+      <x:c r="J36" s="20"/>
+      <x:c r="K36" s="20"/>
+      <x:c r="L36" s="20"/>
+      <x:c r="M36" s="20"/>
+      <x:c r="N36" s="20"/>
+      <x:c r="O36" s="20"/>
+      <x:c r="P36" s="20"/>
+      <x:c r="Q36" s="20"/>
+      <x:c r="R36" s="20"/>
+      <x:c r="S36" s="20"/>
+      <x:c r="T36" s="20"/>
+      <x:c r="U36" s="20" t="str">
         <x:f>IF(A36="","",IF(OR(L36="Closed",L36="False positive"),"No",IF(N36="","No target set",IF(N36&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="37">
-      <x:c r="U37" t="str">
+      <x:c r="A37" s="20"/>
+      <x:c r="B37" s="20"/>
+      <x:c r="C37" s="20"/>
+      <x:c r="D37" s="20"/>
+      <x:c r="E37" s="20"/>
+      <x:c r="F37" s="20"/>
+      <x:c r="G37" s="20"/>
+      <x:c r="H37" s="20"/>
+      <x:c r="I37" s="20"/>
+      <x:c r="J37" s="20"/>
+      <x:c r="K37" s="20"/>
+      <x:c r="L37" s="20"/>
+      <x:c r="M37" s="20"/>
+      <x:c r="N37" s="20"/>
+      <x:c r="O37" s="20"/>
+      <x:c r="P37" s="20"/>
+      <x:c r="Q37" s="20"/>
+      <x:c r="R37" s="20"/>
+      <x:c r="S37" s="20"/>
+      <x:c r="T37" s="20"/>
+      <x:c r="U37" s="20" t="str">
         <x:f>IF(A37="","",IF(OR(L37="Closed",L37="False positive"),"No",IF(N37="","No target set",IF(N37&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="U38" t="str">
+      <x:c r="A38" s="20"/>
+      <x:c r="B38" s="20"/>
+      <x:c r="C38" s="20"/>
+      <x:c r="D38" s="20"/>
+      <x:c r="E38" s="20"/>
+      <x:c r="F38" s="20"/>
+      <x:c r="G38" s="20"/>
+      <x:c r="H38" s="20"/>
+      <x:c r="I38" s="20"/>
+      <x:c r="J38" s="20"/>
+      <x:c r="K38" s="20"/>
+      <x:c r="L38" s="20"/>
+      <x:c r="M38" s="20"/>
+      <x:c r="N38" s="20"/>
+      <x:c r="O38" s="20"/>
+      <x:c r="P38" s="20"/>
+      <x:c r="Q38" s="20"/>
+      <x:c r="R38" s="20"/>
+      <x:c r="S38" s="20"/>
+      <x:c r="T38" s="20"/>
+      <x:c r="U38" s="20" t="str">
         <x:f>IF(A38="","",IF(OR(L38="Closed",L38="False positive"),"No",IF(N38="","No target set",IF(N38&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="39">
-      <x:c r="U39" t="str">
+      <x:c r="A39" s="20"/>
+      <x:c r="B39" s="20"/>
+      <x:c r="C39" s="20"/>
+      <x:c r="D39" s="20"/>
+      <x:c r="E39" s="20"/>
+      <x:c r="F39" s="20"/>
+      <x:c r="G39" s="20"/>
+      <x:c r="H39" s="20"/>
+      <x:c r="I39" s="20"/>
+      <x:c r="J39" s="20"/>
+      <x:c r="K39" s="20"/>
+      <x:c r="L39" s="20"/>
+      <x:c r="M39" s="20"/>
+      <x:c r="N39" s="20"/>
+      <x:c r="O39" s="20"/>
+      <x:c r="P39" s="20"/>
+      <x:c r="Q39" s="20"/>
+      <x:c r="R39" s="20"/>
+      <x:c r="S39" s="20"/>
+      <x:c r="T39" s="20"/>
+      <x:c r="U39" s="20" t="str">
         <x:f>IF(A39="","",IF(OR(L39="Closed",L39="False positive"),"No",IF(N39="","No target set",IF(N39&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="40">
-      <x:c r="U40" t="str">
+      <x:c r="A40" s="20"/>
+      <x:c r="B40" s="20"/>
+      <x:c r="C40" s="20"/>
+      <x:c r="D40" s="20"/>
+      <x:c r="E40" s="20"/>
+      <x:c r="F40" s="20"/>
+      <x:c r="G40" s="20"/>
+      <x:c r="H40" s="20"/>
+      <x:c r="I40" s="20"/>
+      <x:c r="J40" s="20"/>
+      <x:c r="K40" s="20"/>
+      <x:c r="L40" s="20"/>
+      <x:c r="M40" s="20"/>
+      <x:c r="N40" s="20"/>
+      <x:c r="O40" s="20"/>
+      <x:c r="P40" s="20"/>
+      <x:c r="Q40" s="20"/>
+      <x:c r="R40" s="20"/>
+      <x:c r="S40" s="20"/>
+      <x:c r="T40" s="20"/>
+      <x:c r="U40" s="20" t="str">
         <x:f>IF(A40="","",IF(OR(L40="Closed",L40="False positive"),"No",IF(N40="","No target set",IF(N40&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="41">
-      <x:c r="U41" t="str">
+      <x:c r="A41" s="20"/>
+      <x:c r="B41" s="20"/>
+      <x:c r="C41" s="20"/>
+      <x:c r="D41" s="20"/>
+      <x:c r="E41" s="20"/>
+      <x:c r="F41" s="20"/>
+      <x:c r="G41" s="20"/>
+      <x:c r="H41" s="20"/>
+      <x:c r="I41" s="20"/>
+      <x:c r="J41" s="20"/>
+      <x:c r="K41" s="20"/>
+      <x:c r="L41" s="20"/>
+      <x:c r="M41" s="20"/>
+      <x:c r="N41" s="20"/>
+      <x:c r="O41" s="20"/>
+      <x:c r="P41" s="20"/>
+      <x:c r="Q41" s="20"/>
+      <x:c r="R41" s="20"/>
+      <x:c r="S41" s="20"/>
+      <x:c r="T41" s="20"/>
+      <x:c r="U41" s="20" t="str">
         <x:f>IF(A41="","",IF(OR(L41="Closed",L41="False positive"),"No",IF(N41="","No target set",IF(N41&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="42">
-      <x:c r="U42" t="str">
+      <x:c r="A42" s="20"/>
+      <x:c r="B42" s="20"/>
+      <x:c r="C42" s="20"/>
+      <x:c r="D42" s="20"/>
+      <x:c r="E42" s="20"/>
+      <x:c r="F42" s="20"/>
+      <x:c r="G42" s="20"/>
+      <x:c r="H42" s="20"/>
+      <x:c r="I42" s="20"/>
+      <x:c r="J42" s="20"/>
+      <x:c r="K42" s="20"/>
+      <x:c r="L42" s="20"/>
+      <x:c r="M42" s="20"/>
+      <x:c r="N42" s="20"/>
+      <x:c r="O42" s="20"/>
+      <x:c r="P42" s="20"/>
+      <x:c r="Q42" s="20"/>
+      <x:c r="R42" s="20"/>
+      <x:c r="S42" s="20"/>
+      <x:c r="T42" s="20"/>
+      <x:c r="U42" s="20" t="str">
         <x:f>IF(A42="","",IF(OR(L42="Closed",L42="False positive"),"No",IF(N42="","No target set",IF(N42&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="43">
-      <x:c r="U43" t="str">
+      <x:c r="A43" s="20"/>
+      <x:c r="B43" s="20"/>
+      <x:c r="C43" s="20"/>
+      <x:c r="D43" s="20"/>
+      <x:c r="E43" s="20"/>
+      <x:c r="F43" s="20"/>
+      <x:c r="G43" s="20"/>
+      <x:c r="H43" s="20"/>
+      <x:c r="I43" s="20"/>
+      <x:c r="J43" s="20"/>
+      <x:c r="K43" s="20"/>
+      <x:c r="L43" s="20"/>
+      <x:c r="M43" s="20"/>
+      <x:c r="N43" s="20"/>
+      <x:c r="O43" s="20"/>
+      <x:c r="P43" s="20"/>
+      <x:c r="Q43" s="20"/>
+      <x:c r="R43" s="20"/>
+      <x:c r="S43" s="20"/>
+      <x:c r="T43" s="20"/>
+      <x:c r="U43" s="20" t="str">
         <x:f>IF(A43="","",IF(OR(L43="Closed",L43="False positive"),"No",IF(N43="","No target set",IF(N43&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="44">
-      <x:c r="U44" t="str">
+      <x:c r="A44" s="20"/>
+      <x:c r="B44" s="20"/>
+      <x:c r="C44" s="20"/>
+      <x:c r="D44" s="20"/>
+      <x:c r="E44" s="20"/>
+      <x:c r="F44" s="20"/>
+      <x:c r="G44" s="20"/>
+      <x:c r="H44" s="20"/>
+      <x:c r="I44" s="20"/>
+      <x:c r="J44" s="20"/>
+      <x:c r="K44" s="20"/>
+      <x:c r="L44" s="20"/>
+      <x:c r="M44" s="20"/>
+      <x:c r="N44" s="20"/>
+      <x:c r="O44" s="20"/>
+      <x:c r="P44" s="20"/>
+      <x:c r="Q44" s="20"/>
+      <x:c r="R44" s="20"/>
+      <x:c r="S44" s="20"/>
+      <x:c r="T44" s="20"/>
+      <x:c r="U44" s="20" t="str">
         <x:f>IF(A44="","",IF(OR(L44="Closed",L44="False positive"),"No",IF(N44="","No target set",IF(N44&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="45">
-      <x:c r="U45" t="str">
+      <x:c r="A45" s="20"/>
+      <x:c r="B45" s="20"/>
+      <x:c r="C45" s="20"/>
+      <x:c r="D45" s="20"/>
+      <x:c r="E45" s="20"/>
+      <x:c r="F45" s="20"/>
+      <x:c r="G45" s="20"/>
+      <x:c r="H45" s="20"/>
+      <x:c r="I45" s="20"/>
+      <x:c r="J45" s="20"/>
+      <x:c r="K45" s="20"/>
+      <x:c r="L45" s="20"/>
+      <x:c r="M45" s="20"/>
+      <x:c r="N45" s="20"/>
+      <x:c r="O45" s="20"/>
+      <x:c r="P45" s="20"/>
+      <x:c r="Q45" s="20"/>
+      <x:c r="R45" s="20"/>
+      <x:c r="S45" s="20"/>
+      <x:c r="T45" s="20"/>
+      <x:c r="U45" s="20" t="str">
         <x:f>IF(A45="","",IF(OR(L45="Closed",L45="False positive"),"No",IF(N45="","No target set",IF(N45&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="46">
-      <x:c r="U46" t="str">
+      <x:c r="A46" s="20"/>
+      <x:c r="B46" s="20"/>
+      <x:c r="C46" s="20"/>
+      <x:c r="D46" s="20"/>
+      <x:c r="E46" s="20"/>
+      <x:c r="F46" s="20"/>
+      <x:c r="G46" s="20"/>
+      <x:c r="H46" s="20"/>
+      <x:c r="I46" s="20"/>
+      <x:c r="J46" s="20"/>
+      <x:c r="K46" s="20"/>
+      <x:c r="L46" s="20"/>
+      <x:c r="M46" s="20"/>
+      <x:c r="N46" s="20"/>
+      <x:c r="O46" s="20"/>
+      <x:c r="P46" s="20"/>
+      <x:c r="Q46" s="20"/>
+      <x:c r="R46" s="20"/>
+      <x:c r="S46" s="20"/>
+      <x:c r="T46" s="20"/>
+      <x:c r="U46" s="20" t="str">
         <x:f>IF(A46="","",IF(OR(L46="Closed",L46="False positive"),"No",IF(N46="","No target set",IF(N46&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="47">
-      <x:c r="U47" t="str">
+      <x:c r="A47" s="20"/>
+      <x:c r="B47" s="20"/>
+      <x:c r="C47" s="20"/>
+      <x:c r="D47" s="20"/>
+      <x:c r="E47" s="20"/>
+      <x:c r="F47" s="20"/>
+      <x:c r="G47" s="20"/>
+      <x:c r="H47" s="20"/>
+      <x:c r="I47" s="20"/>
+      <x:c r="J47" s="20"/>
+      <x:c r="K47" s="20"/>
+      <x:c r="L47" s="20"/>
+      <x:c r="M47" s="20"/>
+      <x:c r="N47" s="20"/>
+      <x:c r="O47" s="20"/>
+      <x:c r="P47" s="20"/>
+      <x:c r="Q47" s="20"/>
+      <x:c r="R47" s="20"/>
+      <x:c r="S47" s="20"/>
+      <x:c r="T47" s="20"/>
+      <x:c r="U47" s="20" t="str">
         <x:f>IF(A47="","",IF(OR(L47="Closed",L47="False positive"),"No",IF(N47="","No target set",IF(N47&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="48">
-      <x:c r="U48" t="str">
+      <x:c r="A48" s="20"/>
+      <x:c r="B48" s="20"/>
+      <x:c r="C48" s="20"/>
+      <x:c r="D48" s="20"/>
+      <x:c r="E48" s="20"/>
+      <x:c r="F48" s="20"/>
+      <x:c r="G48" s="20"/>
+      <x:c r="H48" s="20"/>
+      <x:c r="I48" s="20"/>
+      <x:c r="J48" s="20"/>
+      <x:c r="K48" s="20"/>
+      <x:c r="L48" s="20"/>
+      <x:c r="M48" s="20"/>
+      <x:c r="N48" s="20"/>
+      <x:c r="O48" s="20"/>
+      <x:c r="P48" s="20"/>
+      <x:c r="Q48" s="20"/>
+      <x:c r="R48" s="20"/>
+      <x:c r="S48" s="20"/>
+      <x:c r="T48" s="20"/>
+      <x:c r="U48" s="20" t="str">
         <x:f>IF(A48="","",IF(OR(L48="Closed",L48="False positive"),"No",IF(N48="","No target set",IF(N48&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="49">
-      <x:c r="U49" t="str">
+      <x:c r="A49" s="20"/>
+      <x:c r="B49" s="20"/>
+      <x:c r="C49" s="20"/>
+      <x:c r="D49" s="20"/>
+      <x:c r="E49" s="20"/>
+      <x:c r="F49" s="20"/>
+      <x:c r="G49" s="20"/>
+      <x:c r="H49" s="20"/>
+      <x:c r="I49" s="20"/>
+      <x:c r="J49" s="20"/>
+      <x:c r="K49" s="20"/>
+      <x:c r="L49" s="20"/>
+      <x:c r="M49" s="20"/>
+      <x:c r="N49" s="20"/>
+      <x:c r="O49" s="20"/>
+      <x:c r="P49" s="20"/>
+      <x:c r="Q49" s="20"/>
+      <x:c r="R49" s="20"/>
+      <x:c r="S49" s="20"/>
+      <x:c r="T49" s="20"/>
+      <x:c r="U49" s="20" t="str">
         <x:f>IF(A49="","",IF(OR(L49="Closed",L49="False positive"),"No",IF(N49="","No target set",IF(N49&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="50">
-      <x:c r="U50" t="str">
+      <x:c r="A50" s="20"/>
+      <x:c r="B50" s="20"/>
+      <x:c r="C50" s="20"/>
+      <x:c r="D50" s="20"/>
+      <x:c r="E50" s="20"/>
+      <x:c r="F50" s="20"/>
+      <x:c r="G50" s="20"/>
+      <x:c r="H50" s="20"/>
+      <x:c r="I50" s="20"/>
+      <x:c r="J50" s="20"/>
+      <x:c r="K50" s="20"/>
+      <x:c r="L50" s="20"/>
+      <x:c r="M50" s="20"/>
+      <x:c r="N50" s="20"/>
+      <x:c r="O50" s="20"/>
+      <x:c r="P50" s="20"/>
+      <x:c r="Q50" s="20"/>
+      <x:c r="R50" s="20"/>
+      <x:c r="S50" s="20"/>
+      <x:c r="T50" s="20"/>
+      <x:c r="U50" s="20" t="str">
         <x:f>IF(A50="","",IF(OR(L50="Closed",L50="False positive"),"No",IF(N50="","No target set",IF(N50&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="51">
-      <x:c r="U51" t="str">
+      <x:c r="A51" s="20"/>
+      <x:c r="B51" s="20"/>
+      <x:c r="C51" s="20"/>
+      <x:c r="D51" s="20"/>
+      <x:c r="E51" s="20"/>
+      <x:c r="F51" s="20"/>
+      <x:c r="G51" s="20"/>
+      <x:c r="H51" s="20"/>
+      <x:c r="I51" s="20"/>
+      <x:c r="J51" s="20"/>
+      <x:c r="K51" s="20"/>
+      <x:c r="L51" s="20"/>
+      <x:c r="M51" s="20"/>
+      <x:c r="N51" s="20"/>
+      <x:c r="O51" s="20"/>
+      <x:c r="P51" s="20"/>
+      <x:c r="Q51" s="20"/>
+      <x:c r="R51" s="20"/>
+      <x:c r="S51" s="20"/>
+      <x:c r="T51" s="20"/>
+      <x:c r="U51" s="20" t="str">
         <x:f>IF(A51="","",IF(OR(L51="Closed",L51="False positive"),"No",IF(N51="","No target set",IF(N51&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="52">
-      <x:c r="U52" t="str">
+      <x:c r="A52" s="20"/>
+      <x:c r="B52" s="20"/>
+      <x:c r="C52" s="20"/>
+      <x:c r="D52" s="20"/>
+      <x:c r="E52" s="20"/>
+      <x:c r="F52" s="20"/>
+      <x:c r="G52" s="20"/>
+      <x:c r="H52" s="20"/>
+      <x:c r="I52" s="20"/>
+      <x:c r="J52" s="20"/>
+      <x:c r="K52" s="20"/>
+      <x:c r="L52" s="20"/>
+      <x:c r="M52" s="20"/>
+      <x:c r="N52" s="20"/>
+      <x:c r="O52" s="20"/>
+      <x:c r="P52" s="20"/>
+      <x:c r="Q52" s="20"/>
+      <x:c r="R52" s="20"/>
+      <x:c r="S52" s="20"/>
+      <x:c r="T52" s="20"/>
+      <x:c r="U52" s="20" t="str">
         <x:f>IF(A52="","",IF(OR(L52="Closed",L52="False positive"),"No",IF(N52="","No target set",IF(N52&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="53">
-      <x:c r="U53" t="str">
+      <x:c r="A53" s="20"/>
+      <x:c r="B53" s="20"/>
+      <x:c r="C53" s="20"/>
+      <x:c r="D53" s="20"/>
+      <x:c r="E53" s="20"/>
+      <x:c r="F53" s="20"/>
+      <x:c r="G53" s="20"/>
+      <x:c r="H53" s="20"/>
+      <x:c r="I53" s="20"/>
+      <x:c r="J53" s="20"/>
+      <x:c r="K53" s="20"/>
+      <x:c r="L53" s="20"/>
+      <x:c r="M53" s="20"/>
+      <x:c r="N53" s="20"/>
+      <x:c r="O53" s="20"/>
+      <x:c r="P53" s="20"/>
+      <x:c r="Q53" s="20"/>
+      <x:c r="R53" s="20"/>
+      <x:c r="S53" s="20"/>
+      <x:c r="T53" s="20"/>
+      <x:c r="U53" s="20" t="str">
         <x:f>IF(A53="","",IF(OR(L53="Closed",L53="False positive"),"No",IF(N53="","No target set",IF(N53&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="54">
-      <x:c r="U54" t="str">
+      <x:c r="A54" s="20"/>
+      <x:c r="B54" s="20"/>
+      <x:c r="C54" s="20"/>
+      <x:c r="D54" s="20"/>
+      <x:c r="E54" s="20"/>
+      <x:c r="F54" s="20"/>
+      <x:c r="G54" s="20"/>
+      <x:c r="H54" s="20"/>
+      <x:c r="I54" s="20"/>
+      <x:c r="J54" s="20"/>
+      <x:c r="K54" s="20"/>
+      <x:c r="L54" s="20"/>
+      <x:c r="M54" s="20"/>
+      <x:c r="N54" s="20"/>
+      <x:c r="O54" s="20"/>
+      <x:c r="P54" s="20"/>
+      <x:c r="Q54" s="20"/>
+      <x:c r="R54" s="20"/>
+      <x:c r="S54" s="20"/>
+      <x:c r="T54" s="20"/>
+      <x:c r="U54" s="20" t="str">
         <x:f>IF(A54="","",IF(OR(L54="Closed",L54="False positive"),"No",IF(N54="","No target set",IF(N54&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="55">
-      <x:c r="U55" t="str">
+      <x:c r="A55" s="20"/>
+      <x:c r="B55" s="20"/>
+      <x:c r="C55" s="20"/>
+      <x:c r="D55" s="20"/>
+      <x:c r="E55" s="20"/>
+      <x:c r="F55" s="20"/>
+      <x:c r="G55" s="20"/>
+      <x:c r="H55" s="20"/>
+      <x:c r="I55" s="20"/>
+      <x:c r="J55" s="20"/>
+      <x:c r="K55" s="20"/>
+      <x:c r="L55" s="20"/>
+      <x:c r="M55" s="20"/>
+      <x:c r="N55" s="20"/>
+      <x:c r="O55" s="20"/>
+      <x:c r="P55" s="20"/>
+      <x:c r="Q55" s="20"/>
+      <x:c r="R55" s="20"/>
+      <x:c r="S55" s="20"/>
+      <x:c r="T55" s="20"/>
+      <x:c r="U55" s="20" t="str">
         <x:f>IF(A55="","",IF(OR(L55="Closed",L55="False positive"),"No",IF(N55="","No target set",IF(N55&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="56">
-      <x:c r="U56" t="str">
+      <x:c r="A56" s="20"/>
+      <x:c r="B56" s="20"/>
+      <x:c r="C56" s="20"/>
+      <x:c r="D56" s="20"/>
+      <x:c r="E56" s="20"/>
+      <x:c r="F56" s="20"/>
+      <x:c r="G56" s="20"/>
+      <x:c r="H56" s="20"/>
+      <x:c r="I56" s="20"/>
+      <x:c r="J56" s="20"/>
+      <x:c r="K56" s="20"/>
+      <x:c r="L56" s="20"/>
+      <x:c r="M56" s="20"/>
+      <x:c r="N56" s="20"/>
+      <x:c r="O56" s="20"/>
+      <x:c r="P56" s="20"/>
+      <x:c r="Q56" s="20"/>
+      <x:c r="R56" s="20"/>
+      <x:c r="S56" s="20"/>
+      <x:c r="T56" s="20"/>
+      <x:c r="U56" s="20" t="str">
         <x:f>IF(A56="","",IF(OR(L56="Closed",L56="False positive"),"No",IF(N56="","No target set",IF(N56&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="57">
-      <x:c r="U57" t="str">
+      <x:c r="A57" s="20"/>
+      <x:c r="B57" s="20"/>
+      <x:c r="C57" s="20"/>
+      <x:c r="D57" s="20"/>
+      <x:c r="E57" s="20"/>
+      <x:c r="F57" s="20"/>
+      <x:c r="G57" s="20"/>
+      <x:c r="H57" s="20"/>
+      <x:c r="I57" s="20"/>
+      <x:c r="J57" s="20"/>
+      <x:c r="K57" s="20"/>
+      <x:c r="L57" s="20"/>
+      <x:c r="M57" s="20"/>
+      <x:c r="N57" s="20"/>
+      <x:c r="O57" s="20"/>
+      <x:c r="P57" s="20"/>
+      <x:c r="Q57" s="20"/>
+      <x:c r="R57" s="20"/>
+      <x:c r="S57" s="20"/>
+      <x:c r="T57" s="20"/>
+      <x:c r="U57" s="20" t="str">
         <x:f>IF(A57="","",IF(OR(L57="Closed",L57="False positive"),"No",IF(N57="","No target set",IF(N57&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="58">
-      <x:c r="U58" t="str">
+      <x:c r="A58" s="20"/>
+      <x:c r="B58" s="20"/>
+      <x:c r="C58" s="20"/>
+      <x:c r="D58" s="20"/>
+      <x:c r="E58" s="20"/>
+      <x:c r="F58" s="20"/>
+      <x:c r="G58" s="20"/>
+      <x:c r="H58" s="20"/>
+      <x:c r="I58" s="20"/>
+      <x:c r="J58" s="20"/>
+      <x:c r="K58" s="20"/>
+      <x:c r="L58" s="20"/>
+      <x:c r="M58" s="20"/>
+      <x:c r="N58" s="20"/>
+      <x:c r="O58" s="20"/>
+      <x:c r="P58" s="20"/>
+      <x:c r="Q58" s="20"/>
+      <x:c r="R58" s="20"/>
+      <x:c r="S58" s="20"/>
+      <x:c r="T58" s="20"/>
+      <x:c r="U58" s="20" t="str">
         <x:f>IF(A58="","",IF(OR(L58="Closed",L58="False positive"),"No",IF(N58="","No target set",IF(N58&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="59">
-      <x:c r="U59" t="str">
+      <x:c r="A59" s="20"/>
+      <x:c r="B59" s="20"/>
+      <x:c r="C59" s="20"/>
+      <x:c r="D59" s="20"/>
+      <x:c r="E59" s="20"/>
+      <x:c r="F59" s="20"/>
+      <x:c r="G59" s="20"/>
+      <x:c r="H59" s="20"/>
+      <x:c r="I59" s="20"/>
+      <x:c r="J59" s="20"/>
+      <x:c r="K59" s="20"/>
+      <x:c r="L59" s="20"/>
+      <x:c r="M59" s="20"/>
+      <x:c r="N59" s="20"/>
+      <x:c r="O59" s="20"/>
+      <x:c r="P59" s="20"/>
+      <x:c r="Q59" s="20"/>
+      <x:c r="R59" s="20"/>
+      <x:c r="S59" s="20"/>
+      <x:c r="T59" s="20"/>
+      <x:c r="U59" s="20" t="str">
         <x:f>IF(A59="","",IF(OR(L59="Closed",L59="False positive"),"No",IF(N59="","No target set",IF(N59&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="60">
-      <x:c r="U60" t="str">
+      <x:c r="A60" s="20"/>
+      <x:c r="B60" s="20"/>
+      <x:c r="C60" s="20"/>
+      <x:c r="D60" s="20"/>
+      <x:c r="E60" s="20"/>
+      <x:c r="F60" s="20"/>
+      <x:c r="G60" s="20"/>
+      <x:c r="H60" s="20"/>
+      <x:c r="I60" s="20"/>
+      <x:c r="J60" s="20"/>
+      <x:c r="K60" s="20"/>
+      <x:c r="L60" s="20"/>
+      <x:c r="M60" s="20"/>
+      <x:c r="N60" s="20"/>
+      <x:c r="O60" s="20"/>
+      <x:c r="P60" s="20"/>
+      <x:c r="Q60" s="20"/>
+      <x:c r="R60" s="20"/>
+      <x:c r="S60" s="20"/>
+      <x:c r="T60" s="20"/>
+      <x:c r="U60" s="20" t="str">
         <x:f>IF(A60="","",IF(OR(L60="Closed",L60="False positive"),"No",IF(N60="","No target set",IF(N60&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="61">
-      <x:c r="U61" t="str">
+      <x:c r="A61" s="20"/>
+      <x:c r="B61" s="20"/>
+      <x:c r="C61" s="20"/>
+      <x:c r="D61" s="20"/>
+      <x:c r="E61" s="20"/>
+      <x:c r="F61" s="20"/>
+      <x:c r="G61" s="20"/>
+      <x:c r="H61" s="20"/>
+      <x:c r="I61" s="20"/>
+      <x:c r="J61" s="20"/>
+      <x:c r="K61" s="20"/>
+      <x:c r="L61" s="20"/>
+      <x:c r="M61" s="20"/>
+      <x:c r="N61" s="20"/>
+      <x:c r="O61" s="20"/>
+      <x:c r="P61" s="20"/>
+      <x:c r="Q61" s="20"/>
+      <x:c r="R61" s="20"/>
+      <x:c r="S61" s="20"/>
+      <x:c r="T61" s="20"/>
+      <x:c r="U61" s="20" t="str">
         <x:f>IF(A61="","",IF(OR(L61="Closed",L61="False positive"),"No",IF(N61="","No target set",IF(N61&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="62">
-      <x:c r="U62" t="str">
+      <x:c r="A62" s="20"/>
+      <x:c r="B62" s="20"/>
+      <x:c r="C62" s="20"/>
+      <x:c r="D62" s="20"/>
+      <x:c r="E62" s="20"/>
+      <x:c r="F62" s="20"/>
+      <x:c r="G62" s="20"/>
+      <x:c r="H62" s="20"/>
+      <x:c r="I62" s="20"/>
+      <x:c r="J62" s="20"/>
+      <x:c r="K62" s="20"/>
+      <x:c r="L62" s="20"/>
+      <x:c r="M62" s="20"/>
+      <x:c r="N62" s="20"/>
+      <x:c r="O62" s="20"/>
+      <x:c r="P62" s="20"/>
+      <x:c r="Q62" s="20"/>
+      <x:c r="R62" s="20"/>
+      <x:c r="S62" s="20"/>
+      <x:c r="T62" s="20"/>
+      <x:c r="U62" s="20" t="str">
         <x:f>IF(A62="","",IF(OR(L62="Closed",L62="False positive"),"No",IF(N62="","No target set",IF(N62&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="63">
-      <x:c r="U63" t="str">
+      <x:c r="A63" s="20"/>
+      <x:c r="B63" s="20"/>
+      <x:c r="C63" s="20"/>
+      <x:c r="D63" s="20"/>
+      <x:c r="E63" s="20"/>
+      <x:c r="F63" s="20"/>
+      <x:c r="G63" s="20"/>
+      <x:c r="H63" s="20"/>
+      <x:c r="I63" s="20"/>
+      <x:c r="J63" s="20"/>
+      <x:c r="K63" s="20"/>
+      <x:c r="L63" s="20"/>
+      <x:c r="M63" s="20"/>
+      <x:c r="N63" s="20"/>
+      <x:c r="O63" s="20"/>
+      <x:c r="P63" s="20"/>
+      <x:c r="Q63" s="20"/>
+      <x:c r="R63" s="20"/>
+      <x:c r="S63" s="20"/>
+      <x:c r="T63" s="20"/>
+      <x:c r="U63" s="20" t="str">
         <x:f>IF(A63="","",IF(OR(L63="Closed",L63="False positive"),"No",IF(N63="","No target set",IF(N63&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="64">
-      <x:c r="U64" t="str">
+      <x:c r="A64" s="20"/>
+      <x:c r="B64" s="20"/>
+      <x:c r="C64" s="20"/>
+      <x:c r="D64" s="20"/>
+      <x:c r="E64" s="20"/>
+      <x:c r="F64" s="20"/>
+      <x:c r="G64" s="20"/>
+      <x:c r="H64" s="20"/>
+      <x:c r="I64" s="20"/>
+      <x:c r="J64" s="20"/>
+      <x:c r="K64" s="20"/>
+      <x:c r="L64" s="20"/>
+      <x:c r="M64" s="20"/>
+      <x:c r="N64" s="20"/>
+      <x:c r="O64" s="20"/>
+      <x:c r="P64" s="20"/>
+      <x:c r="Q64" s="20"/>
+      <x:c r="R64" s="20"/>
+      <x:c r="S64" s="20"/>
+      <x:c r="T64" s="20"/>
+      <x:c r="U64" s="20" t="str">
         <x:f>IF(A64="","",IF(OR(L64="Closed",L64="False positive"),"No",IF(N64="","No target set",IF(N64&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="65">
-      <x:c r="U65" t="str">
+      <x:c r="A65" s="20"/>
+      <x:c r="B65" s="20"/>
+      <x:c r="C65" s="20"/>
+      <x:c r="D65" s="20"/>
+      <x:c r="E65" s="20"/>
+      <x:c r="F65" s="20"/>
+      <x:c r="G65" s="20"/>
+      <x:c r="H65" s="20"/>
+      <x:c r="I65" s="20"/>
+      <x:c r="J65" s="20"/>
+      <x:c r="K65" s="20"/>
+      <x:c r="L65" s="20"/>
+      <x:c r="M65" s="20"/>
+      <x:c r="N65" s="20"/>
+      <x:c r="O65" s="20"/>
+      <x:c r="P65" s="20"/>
+      <x:c r="Q65" s="20"/>
+      <x:c r="R65" s="20"/>
+      <x:c r="S65" s="20"/>
+      <x:c r="T65" s="20"/>
+      <x:c r="U65" s="20" t="str">
         <x:f>IF(A65="","",IF(OR(L65="Closed",L65="False positive"),"No",IF(N65="","No target set",IF(N65&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="66">
-      <x:c r="U66" t="str">
+      <x:c r="A66" s="20"/>
+      <x:c r="B66" s="20"/>
+      <x:c r="C66" s="20"/>
+      <x:c r="D66" s="20"/>
+      <x:c r="E66" s="20"/>
+      <x:c r="F66" s="20"/>
+      <x:c r="G66" s="20"/>
+      <x:c r="H66" s="20"/>
+      <x:c r="I66" s="20"/>
+      <x:c r="J66" s="20"/>
+      <x:c r="K66" s="20"/>
+      <x:c r="L66" s="20"/>
+      <x:c r="M66" s="20"/>
+      <x:c r="N66" s="20"/>
+      <x:c r="O66" s="20"/>
+      <x:c r="P66" s="20"/>
+      <x:c r="Q66" s="20"/>
+      <x:c r="R66" s="20"/>
+      <x:c r="S66" s="20"/>
+      <x:c r="T66" s="20"/>
+      <x:c r="U66" s="20" t="str">
         <x:f>IF(A66="","",IF(OR(L66="Closed",L66="False positive"),"No",IF(N66="","No target set",IF(N66&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="67">
-      <x:c r="U67" t="str">
+      <x:c r="A67" s="20"/>
+      <x:c r="B67" s="20"/>
+      <x:c r="C67" s="20"/>
+      <x:c r="D67" s="20"/>
+      <x:c r="E67" s="20"/>
+      <x:c r="F67" s="20"/>
+      <x:c r="G67" s="20"/>
+      <x:c r="H67" s="20"/>
+      <x:c r="I67" s="20"/>
+      <x:c r="J67" s="20"/>
+      <x:c r="K67" s="20"/>
+      <x:c r="L67" s="20"/>
+      <x:c r="M67" s="20"/>
+      <x:c r="N67" s="20"/>
+      <x:c r="O67" s="20"/>
+      <x:c r="P67" s="20"/>
+      <x:c r="Q67" s="20"/>
+      <x:c r="R67" s="20"/>
+      <x:c r="S67" s="20"/>
+      <x:c r="T67" s="20"/>
+      <x:c r="U67" s="20" t="str">
         <x:f>IF(A67="","",IF(OR(L67="Closed",L67="False positive"),"No",IF(N67="","No target set",IF(N67&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="68">
-      <x:c r="U68" t="str">
+      <x:c r="A68" s="20"/>
+      <x:c r="B68" s="20"/>
+      <x:c r="C68" s="20"/>
+      <x:c r="D68" s="20"/>
+      <x:c r="E68" s="20"/>
+      <x:c r="F68" s="20"/>
+      <x:c r="G68" s="20"/>
+      <x:c r="H68" s="20"/>
+      <x:c r="I68" s="20"/>
+      <x:c r="J68" s="20"/>
+      <x:c r="K68" s="20"/>
+      <x:c r="L68" s="20"/>
+      <x:c r="M68" s="20"/>
+      <x:c r="N68" s="20"/>
+      <x:c r="O68" s="20"/>
+      <x:c r="P68" s="20"/>
+      <x:c r="Q68" s="20"/>
+      <x:c r="R68" s="20"/>
+      <x:c r="S68" s="20"/>
+      <x:c r="T68" s="20"/>
+      <x:c r="U68" s="20" t="str">
         <x:f>IF(A68="","",IF(OR(L68="Closed",L68="False positive"),"No",IF(N68="","No target set",IF(N68&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="69">
-      <x:c r="U69" t="str">
+      <x:c r="A69" s="20"/>
+      <x:c r="B69" s="20"/>
+      <x:c r="C69" s="20"/>
+      <x:c r="D69" s="20"/>
+      <x:c r="E69" s="20"/>
+      <x:c r="F69" s="20"/>
+      <x:c r="G69" s="20"/>
+      <x:c r="H69" s="20"/>
+      <x:c r="I69" s="20"/>
+      <x:c r="J69" s="20"/>
+      <x:c r="K69" s="20"/>
+      <x:c r="L69" s="20"/>
+      <x:c r="M69" s="20"/>
+      <x:c r="N69" s="20"/>
+      <x:c r="O69" s="20"/>
+      <x:c r="P69" s="20"/>
+      <x:c r="Q69" s="20"/>
+      <x:c r="R69" s="20"/>
+      <x:c r="S69" s="20"/>
+      <x:c r="T69" s="20"/>
+      <x:c r="U69" s="20" t="str">
         <x:f>IF(A69="","",IF(OR(L69="Closed",L69="False positive"),"No",IF(N69="","No target set",IF(N69&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="70">
-      <x:c r="U70" t="str">
+      <x:c r="A70" s="20"/>
+      <x:c r="B70" s="20"/>
+      <x:c r="C70" s="20"/>
+      <x:c r="D70" s="20"/>
+      <x:c r="E70" s="20"/>
+      <x:c r="F70" s="20"/>
+      <x:c r="G70" s="20"/>
+      <x:c r="H70" s="20"/>
+      <x:c r="I70" s="20"/>
+      <x:c r="J70" s="20"/>
+      <x:c r="K70" s="20"/>
+      <x:c r="L70" s="20"/>
+      <x:c r="M70" s="20"/>
+      <x:c r="N70" s="20"/>
+      <x:c r="O70" s="20"/>
+      <x:c r="P70" s="20"/>
+      <x:c r="Q70" s="20"/>
+      <x:c r="R70" s="20"/>
+      <x:c r="S70" s="20"/>
+      <x:c r="T70" s="20"/>
+      <x:c r="U70" s="20" t="str">
         <x:f>IF(A70="","",IF(OR(L70="Closed",L70="False positive"),"No",IF(N70="","No target set",IF(N70&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="71">
-      <x:c r="U71" t="str">
+      <x:c r="A71" s="20"/>
+      <x:c r="B71" s="20"/>
+      <x:c r="C71" s="20"/>
+      <x:c r="D71" s="20"/>
+      <x:c r="E71" s="20"/>
+      <x:c r="F71" s="20"/>
+      <x:c r="G71" s="20"/>
+      <x:c r="H71" s="20"/>
+      <x:c r="I71" s="20"/>
+      <x:c r="J71" s="20"/>
+      <x:c r="K71" s="20"/>
+      <x:c r="L71" s="20"/>
+      <x:c r="M71" s="20"/>
+      <x:c r="N71" s="20"/>
+      <x:c r="O71" s="20"/>
+      <x:c r="P71" s="20"/>
+      <x:c r="Q71" s="20"/>
+      <x:c r="R71" s="20"/>
+      <x:c r="S71" s="20"/>
+      <x:c r="T71" s="20"/>
+      <x:c r="U71" s="20" t="str">
         <x:f>IF(A71="","",IF(OR(L71="Closed",L71="False positive"),"No",IF(N71="","No target set",IF(N71&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="72">
-      <x:c r="U72" t="str">
+      <x:c r="A72" s="20"/>
+      <x:c r="B72" s="20"/>
+      <x:c r="C72" s="20"/>
+      <x:c r="D72" s="20"/>
+      <x:c r="E72" s="20"/>
+      <x:c r="F72" s="20"/>
+      <x:c r="G72" s="20"/>
+      <x:c r="H72" s="20"/>
+      <x:c r="I72" s="20"/>
+      <x:c r="J72" s="20"/>
+      <x:c r="K72" s="20"/>
+      <x:c r="L72" s="20"/>
+      <x:c r="M72" s="20"/>
+      <x:c r="N72" s="20"/>
+      <x:c r="O72" s="20"/>
+      <x:c r="P72" s="20"/>
+      <x:c r="Q72" s="20"/>
+      <x:c r="R72" s="20"/>
+      <x:c r="S72" s="20"/>
+      <x:c r="T72" s="20"/>
+      <x:c r="U72" s="20" t="str">
         <x:f>IF(A72="","",IF(OR(L72="Closed",L72="False positive"),"No",IF(N72="","No target set",IF(N72&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="73">
-      <x:c r="U73" t="str">
+      <x:c r="A73" s="20"/>
+      <x:c r="B73" s="20"/>
+      <x:c r="C73" s="20"/>
+      <x:c r="D73" s="20"/>
+      <x:c r="E73" s="20"/>
+      <x:c r="F73" s="20"/>
+      <x:c r="G73" s="20"/>
+      <x:c r="H73" s="20"/>
+      <x:c r="I73" s="20"/>
+      <x:c r="J73" s="20"/>
+      <x:c r="K73" s="20"/>
+      <x:c r="L73" s="20"/>
+      <x:c r="M73" s="20"/>
+      <x:c r="N73" s="20"/>
+      <x:c r="O73" s="20"/>
+      <x:c r="P73" s="20"/>
+      <x:c r="Q73" s="20"/>
+      <x:c r="R73" s="20"/>
+      <x:c r="S73" s="20"/>
+      <x:c r="T73" s="20"/>
+      <x:c r="U73" s="20" t="str">
         <x:f>IF(A73="","",IF(OR(L73="Closed",L73="False positive"),"No",IF(N73="","No target set",IF(N73&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="74">
-      <x:c r="U74" t="str">
+      <x:c r="A74" s="20"/>
+      <x:c r="B74" s="20"/>
+      <x:c r="C74" s="20"/>
+      <x:c r="D74" s="20"/>
+      <x:c r="E74" s="20"/>
+      <x:c r="F74" s="20"/>
+      <x:c r="G74" s="20"/>
+      <x:c r="H74" s="20"/>
+      <x:c r="I74" s="20"/>
+      <x:c r="J74" s="20"/>
+      <x:c r="K74" s="20"/>
+      <x:c r="L74" s="20"/>
+      <x:c r="M74" s="20"/>
+      <x:c r="N74" s="20"/>
+      <x:c r="O74" s="20"/>
+      <x:c r="P74" s="20"/>
+      <x:c r="Q74" s="20"/>
+      <x:c r="R74" s="20"/>
+      <x:c r="S74" s="20"/>
+      <x:c r="T74" s="20"/>
+      <x:c r="U74" s="20" t="str">
         <x:f>IF(A74="","",IF(OR(L74="Closed",L74="False positive"),"No",IF(N74="","No target set",IF(N74&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="75">
-      <x:c r="U75" t="str">
+      <x:c r="A75" s="20"/>
+      <x:c r="B75" s="20"/>
+      <x:c r="C75" s="20"/>
+      <x:c r="D75" s="20"/>
+      <x:c r="E75" s="20"/>
+      <x:c r="F75" s="20"/>
+      <x:c r="G75" s="20"/>
+      <x:c r="H75" s="20"/>
+      <x:c r="I75" s="20"/>
+      <x:c r="J75" s="20"/>
+      <x:c r="K75" s="20"/>
+      <x:c r="L75" s="20"/>
+      <x:c r="M75" s="20"/>
+      <x:c r="N75" s="20"/>
+      <x:c r="O75" s="20"/>
+      <x:c r="P75" s="20"/>
+      <x:c r="Q75" s="20"/>
+      <x:c r="R75" s="20"/>
+      <x:c r="S75" s="20"/>
+      <x:c r="T75" s="20"/>
+      <x:c r="U75" s="20" t="str">
         <x:f>IF(A75="","",IF(OR(L75="Closed",L75="False positive"),"No",IF(N75="","No target set",IF(N75&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="76">
-      <x:c r="U76" t="str">
+      <x:c r="A76" s="20"/>
+      <x:c r="B76" s="20"/>
+      <x:c r="C76" s="20"/>
+      <x:c r="D76" s="20"/>
+      <x:c r="E76" s="20"/>
+      <x:c r="F76" s="20"/>
+      <x:c r="G76" s="20"/>
+      <x:c r="H76" s="20"/>
+      <x:c r="I76" s="20"/>
+      <x:c r="J76" s="20"/>
+      <x:c r="K76" s="20"/>
+      <x:c r="L76" s="20"/>
+      <x:c r="M76" s="20"/>
+      <x:c r="N76" s="20"/>
+      <x:c r="O76" s="20"/>
+      <x:c r="P76" s="20"/>
+      <x:c r="Q76" s="20"/>
+      <x:c r="R76" s="20"/>
+      <x:c r="S76" s="20"/>
+      <x:c r="T76" s="20"/>
+      <x:c r="U76" s="20" t="str">
         <x:f>IF(A76="","",IF(OR(L76="Closed",L76="False positive"),"No",IF(N76="","No target set",IF(N76&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="77">
-      <x:c r="U77" t="str">
+      <x:c r="A77" s="20"/>
+      <x:c r="B77" s="20"/>
+      <x:c r="C77" s="20"/>
+      <x:c r="D77" s="20"/>
+      <x:c r="E77" s="20"/>
+      <x:c r="F77" s="20"/>
+      <x:c r="G77" s="20"/>
+      <x:c r="H77" s="20"/>
+      <x:c r="I77" s="20"/>
+      <x:c r="J77" s="20"/>
+      <x:c r="K77" s="20"/>
+      <x:c r="L77" s="20"/>
+      <x:c r="M77" s="20"/>
+      <x:c r="N77" s="20"/>
+      <x:c r="O77" s="20"/>
+      <x:c r="P77" s="20"/>
+      <x:c r="Q77" s="20"/>
+      <x:c r="R77" s="20"/>
+      <x:c r="S77" s="20"/>
+      <x:c r="T77" s="20"/>
+      <x:c r="U77" s="20" t="str">
         <x:f>IF(A77="","",IF(OR(L77="Closed",L77="False positive"),"No",IF(N77="","No target set",IF(N77&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="78">
-      <x:c r="U78" t="str">
+      <x:c r="A78" s="20"/>
+      <x:c r="B78" s="20"/>
+      <x:c r="C78" s="20"/>
+      <x:c r="D78" s="20"/>
+      <x:c r="E78" s="20"/>
+      <x:c r="F78" s="20"/>
+      <x:c r="G78" s="20"/>
+      <x:c r="H78" s="20"/>
+      <x:c r="I78" s="20"/>
+      <x:c r="J78" s="20"/>
+      <x:c r="K78" s="20"/>
+      <x:c r="L78" s="20"/>
+      <x:c r="M78" s="20"/>
+      <x:c r="N78" s="20"/>
+      <x:c r="O78" s="20"/>
+      <x:c r="P78" s="20"/>
+      <x:c r="Q78" s="20"/>
+      <x:c r="R78" s="20"/>
+      <x:c r="S78" s="20"/>
+      <x:c r="T78" s="20"/>
+      <x:c r="U78" s="20" t="str">
         <x:f>IF(A78="","",IF(OR(L78="Closed",L78="False positive"),"No",IF(N78="","No target set",IF(N78&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="79">
-      <x:c r="U79" t="str">
+      <x:c r="A79" s="20"/>
+      <x:c r="B79" s="20"/>
+      <x:c r="C79" s="20"/>
+      <x:c r="D79" s="20"/>
+      <x:c r="E79" s="20"/>
+      <x:c r="F79" s="20"/>
+      <x:c r="G79" s="20"/>
+      <x:c r="H79" s="20"/>
+      <x:c r="I79" s="20"/>
+      <x:c r="J79" s="20"/>
+      <x:c r="K79" s="20"/>
+      <x:c r="L79" s="20"/>
+      <x:c r="M79" s="20"/>
+      <x:c r="N79" s="20"/>
+      <x:c r="O79" s="20"/>
+      <x:c r="P79" s="20"/>
+      <x:c r="Q79" s="20"/>
+      <x:c r="R79" s="20"/>
+      <x:c r="S79" s="20"/>
+      <x:c r="T79" s="20"/>
+      <x:c r="U79" s="20" t="str">
         <x:f>IF(A79="","",IF(OR(L79="Closed",L79="False positive"),"No",IF(N79="","No target set",IF(N79&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="80">
-      <x:c r="U80" t="str">
+      <x:c r="A80" s="20"/>
+      <x:c r="B80" s="20"/>
+      <x:c r="C80" s="20"/>
+      <x:c r="D80" s="20"/>
+      <x:c r="E80" s="20"/>
+      <x:c r="F80" s="20"/>
+      <x:c r="G80" s="20"/>
+      <x:c r="H80" s="20"/>
+      <x:c r="I80" s="20"/>
+      <x:c r="J80" s="20"/>
+      <x:c r="K80" s="20"/>
+      <x:c r="L80" s="20"/>
+      <x:c r="M80" s="20"/>
+      <x:c r="N80" s="20"/>
+      <x:c r="O80" s="20"/>
+      <x:c r="P80" s="20"/>
+      <x:c r="Q80" s="20"/>
+      <x:c r="R80" s="20"/>
+      <x:c r="S80" s="20"/>
+      <x:c r="T80" s="20"/>
+      <x:c r="U80" s="20" t="str">
         <x:f>IF(A80="","",IF(OR(L80="Closed",L80="False positive"),"No",IF(N80="","No target set",IF(N80&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="81">
-      <x:c r="U81" t="str">
+      <x:c r="A81" s="20"/>
+      <x:c r="B81" s="20"/>
+      <x:c r="C81" s="20"/>
+      <x:c r="D81" s="20"/>
+      <x:c r="E81" s="20"/>
+      <x:c r="F81" s="20"/>
+      <x:c r="G81" s="20"/>
+      <x:c r="H81" s="20"/>
+      <x:c r="I81" s="20"/>
+      <x:c r="J81" s="20"/>
+      <x:c r="K81" s="20"/>
+      <x:c r="L81" s="20"/>
+      <x:c r="M81" s="20"/>
+      <x:c r="N81" s="20"/>
+      <x:c r="O81" s="20"/>
+      <x:c r="P81" s="20"/>
+      <x:c r="Q81" s="20"/>
+      <x:c r="R81" s="20"/>
+      <x:c r="S81" s="20"/>
+      <x:c r="T81" s="20"/>
+      <x:c r="U81" s="20" t="str">
         <x:f>IF(A81="","",IF(OR(L81="Closed",L81="False positive"),"No",IF(N81="","No target set",IF(N81&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="82">
-      <x:c r="U82" t="str">
+      <x:c r="A82" s="20"/>
+      <x:c r="B82" s="20"/>
+      <x:c r="C82" s="20"/>
+      <x:c r="D82" s="20"/>
+      <x:c r="E82" s="20"/>
+      <x:c r="F82" s="20"/>
+      <x:c r="G82" s="20"/>
+      <x:c r="H82" s="20"/>
+      <x:c r="I82" s="20"/>
+      <x:c r="J82" s="20"/>
+      <x:c r="K82" s="20"/>
+      <x:c r="L82" s="20"/>
+      <x:c r="M82" s="20"/>
+      <x:c r="N82" s="20"/>
+      <x:c r="O82" s="20"/>
+      <x:c r="P82" s="20"/>
+      <x:c r="Q82" s="20"/>
+      <x:c r="R82" s="20"/>
+      <x:c r="S82" s="20"/>
+      <x:c r="T82" s="20"/>
+      <x:c r="U82" s="20" t="str">
         <x:f>IF(A82="","",IF(OR(L82="Closed",L82="False positive"),"No",IF(N82="","No target set",IF(N82&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="83">
-      <x:c r="U83" t="str">
+      <x:c r="A83" s="20"/>
+      <x:c r="B83" s="20"/>
+      <x:c r="C83" s="20"/>
+      <x:c r="D83" s="20"/>
+      <x:c r="E83" s="20"/>
+      <x:c r="F83" s="20"/>
+      <x:c r="G83" s="20"/>
+      <x:c r="H83" s="20"/>
+      <x:c r="I83" s="20"/>
+      <x:c r="J83" s="20"/>
+      <x:c r="K83" s="20"/>
+      <x:c r="L83" s="20"/>
+      <x:c r="M83" s="20"/>
+      <x:c r="N83" s="20"/>
+      <x:c r="O83" s="20"/>
+      <x:c r="P83" s="20"/>
+      <x:c r="Q83" s="20"/>
+      <x:c r="R83" s="20"/>
+      <x:c r="S83" s="20"/>
+      <x:c r="T83" s="20"/>
+      <x:c r="U83" s="20" t="str">
         <x:f>IF(A83="","",IF(OR(L83="Closed",L83="False positive"),"No",IF(N83="","No target set",IF(N83&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="84">
-      <x:c r="U84" t="str">
+      <x:c r="A84" s="20"/>
+      <x:c r="B84" s="20"/>
+      <x:c r="C84" s="20"/>
+      <x:c r="D84" s="20"/>
+      <x:c r="E84" s="20"/>
+      <x:c r="F84" s="20"/>
+      <x:c r="G84" s="20"/>
+      <x:c r="H84" s="20"/>
+      <x:c r="I84" s="20"/>
+      <x:c r="J84" s="20"/>
+      <x:c r="K84" s="20"/>
+      <x:c r="L84" s="20"/>
+      <x:c r="M84" s="20"/>
+      <x:c r="N84" s="20"/>
+      <x:c r="O84" s="20"/>
+      <x:c r="P84" s="20"/>
+      <x:c r="Q84" s="20"/>
+      <x:c r="R84" s="20"/>
+      <x:c r="S84" s="20"/>
+      <x:c r="T84" s="20"/>
+      <x:c r="U84" s="20" t="str">
         <x:f>IF(A84="","",IF(OR(L84="Closed",L84="False positive"),"No",IF(N84="","No target set",IF(N84&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="85">
-      <x:c r="U85" t="str">
+      <x:c r="A85" s="20"/>
+      <x:c r="B85" s="20"/>
+      <x:c r="C85" s="20"/>
+      <x:c r="D85" s="20"/>
+      <x:c r="E85" s="20"/>
+      <x:c r="F85" s="20"/>
+      <x:c r="G85" s="20"/>
+      <x:c r="H85" s="20"/>
+      <x:c r="I85" s="20"/>
+      <x:c r="J85" s="20"/>
+      <x:c r="K85" s="20"/>
+      <x:c r="L85" s="20"/>
+      <x:c r="M85" s="20"/>
+      <x:c r="N85" s="20"/>
+      <x:c r="O85" s="20"/>
+      <x:c r="P85" s="20"/>
+      <x:c r="Q85" s="20"/>
+      <x:c r="R85" s="20"/>
+      <x:c r="S85" s="20"/>
+      <x:c r="T85" s="20"/>
+      <x:c r="U85" s="20" t="str">
         <x:f>IF(A85="","",IF(OR(L85="Closed",L85="False positive"),"No",IF(N85="","No target set",IF(N85&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="86">
-      <x:c r="U86" t="str">
+      <x:c r="A86" s="20"/>
+      <x:c r="B86" s="20"/>
+      <x:c r="C86" s="20"/>
+      <x:c r="D86" s="20"/>
+      <x:c r="E86" s="20"/>
+      <x:c r="F86" s="20"/>
+      <x:c r="G86" s="20"/>
+      <x:c r="H86" s="20"/>
+      <x:c r="I86" s="20"/>
+      <x:c r="J86" s="20"/>
+      <x:c r="K86" s="20"/>
+      <x:c r="L86" s="20"/>
+      <x:c r="M86" s="20"/>
+      <x:c r="N86" s="20"/>
+      <x:c r="O86" s="20"/>
+      <x:c r="P86" s="20"/>
+      <x:c r="Q86" s="20"/>
+      <x:c r="R86" s="20"/>
+      <x:c r="S86" s="20"/>
+      <x:c r="T86" s="20"/>
+      <x:c r="U86" s="20" t="str">
         <x:f>IF(A86="","",IF(OR(L86="Closed",L86="False positive"),"No",IF(N86="","No target set",IF(N86&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="87">
-      <x:c r="U87" t="str">
+      <x:c r="A87" s="20"/>
+      <x:c r="B87" s="20"/>
+      <x:c r="C87" s="20"/>
+      <x:c r="D87" s="20"/>
+      <x:c r="E87" s="20"/>
+      <x:c r="F87" s="20"/>
+      <x:c r="G87" s="20"/>
+      <x:c r="H87" s="20"/>
+      <x:c r="I87" s="20"/>
+      <x:c r="J87" s="20"/>
+      <x:c r="K87" s="20"/>
+      <x:c r="L87" s="20"/>
+      <x:c r="M87" s="20"/>
+      <x:c r="N87" s="20"/>
+      <x:c r="O87" s="20"/>
+      <x:c r="P87" s="20"/>
+      <x:c r="Q87" s="20"/>
+      <x:c r="R87" s="20"/>
+      <x:c r="S87" s="20"/>
+      <x:c r="T87" s="20"/>
+      <x:c r="U87" s="20" t="str">
         <x:f>IF(A87="","",IF(OR(L87="Closed",L87="False positive"),"No",IF(N87="","No target set",IF(N87&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="88">
-      <x:c r="U88" t="str">
+      <x:c r="A88" s="20"/>
+      <x:c r="B88" s="20"/>
+      <x:c r="C88" s="20"/>
+      <x:c r="D88" s="20"/>
+      <x:c r="E88" s="20"/>
+      <x:c r="F88" s="20"/>
+      <x:c r="G88" s="20"/>
+      <x:c r="H88" s="20"/>
+      <x:c r="I88" s="20"/>
+      <x:c r="J88" s="20"/>
+      <x:c r="K88" s="20"/>
+      <x:c r="L88" s="20"/>
+      <x:c r="M88" s="20"/>
+      <x:c r="N88" s="20"/>
+      <x:c r="O88" s="20"/>
+      <x:c r="P88" s="20"/>
+      <x:c r="Q88" s="20"/>
+      <x:c r="R88" s="20"/>
+      <x:c r="S88" s="20"/>
+      <x:c r="T88" s="20"/>
+      <x:c r="U88" s="20" t="str">
         <x:f>IF(A88="","",IF(OR(L88="Closed",L88="False positive"),"No",IF(N88="","No target set",IF(N88&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="89">
-      <x:c r="U89" t="str">
+      <x:c r="A89" s="20"/>
+      <x:c r="B89" s="20"/>
+      <x:c r="C89" s="20"/>
+      <x:c r="D89" s="20"/>
+      <x:c r="E89" s="20"/>
+      <x:c r="F89" s="20"/>
+      <x:c r="G89" s="20"/>
+      <x:c r="H89" s="20"/>
+      <x:c r="I89" s="20"/>
+      <x:c r="J89" s="20"/>
+      <x:c r="K89" s="20"/>
+      <x:c r="L89" s="20"/>
+      <x:c r="M89" s="20"/>
+      <x:c r="N89" s="20"/>
+      <x:c r="O89" s="20"/>
+      <x:c r="P89" s="20"/>
+      <x:c r="Q89" s="20"/>
+      <x:c r="R89" s="20"/>
+      <x:c r="S89" s="20"/>
+      <x:c r="T89" s="20"/>
+      <x:c r="U89" s="20" t="str">
         <x:f>IF(A89="","",IF(OR(L89="Closed",L89="False positive"),"No",IF(N89="","No target set",IF(N89&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="90">
-      <x:c r="U90" t="str">
+      <x:c r="A90" s="20"/>
+      <x:c r="B90" s="20"/>
+      <x:c r="C90" s="20"/>
+      <x:c r="D90" s="20"/>
+      <x:c r="E90" s="20"/>
+      <x:c r="F90" s="20"/>
+      <x:c r="G90" s="20"/>
+      <x:c r="H90" s="20"/>
+      <x:c r="I90" s="20"/>
+      <x:c r="J90" s="20"/>
+      <x:c r="K90" s="20"/>
+      <x:c r="L90" s="20"/>
+      <x:c r="M90" s="20"/>
+      <x:c r="N90" s="20"/>
+      <x:c r="O90" s="20"/>
+      <x:c r="P90" s="20"/>
+      <x:c r="Q90" s="20"/>
+      <x:c r="R90" s="20"/>
+      <x:c r="S90" s="20"/>
+      <x:c r="T90" s="20"/>
+      <x:c r="U90" s="20" t="str">
         <x:f>IF(A90="","",IF(OR(L90="Closed",L90="False positive"),"No",IF(N90="","No target set",IF(N90&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="91">
-      <x:c r="U91" t="str">
+      <x:c r="A91" s="20"/>
+      <x:c r="B91" s="20"/>
+      <x:c r="C91" s="20"/>
+      <x:c r="D91" s="20"/>
+      <x:c r="E91" s="20"/>
+      <x:c r="F91" s="20"/>
+      <x:c r="G91" s="20"/>
+      <x:c r="H91" s="20"/>
+      <x:c r="I91" s="20"/>
+      <x:c r="J91" s="20"/>
+      <x:c r="K91" s="20"/>
+      <x:c r="L91" s="20"/>
+      <x:c r="M91" s="20"/>
+      <x:c r="N91" s="20"/>
+      <x:c r="O91" s="20"/>
+      <x:c r="P91" s="20"/>
+      <x:c r="Q91" s="20"/>
+      <x:c r="R91" s="20"/>
+      <x:c r="S91" s="20"/>
+      <x:c r="T91" s="20"/>
+      <x:c r="U91" s="20" t="str">
         <x:f>IF(A91="","",IF(OR(L91="Closed",L91="False positive"),"No",IF(N91="","No target set",IF(N91&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="92">
-      <x:c r="U92" t="str">
+      <x:c r="A92" s="20"/>
+      <x:c r="B92" s="20"/>
+      <x:c r="C92" s="20"/>
+      <x:c r="D92" s="20"/>
+      <x:c r="E92" s="20"/>
+      <x:c r="F92" s="20"/>
+      <x:c r="G92" s="20"/>
+      <x:c r="H92" s="20"/>
+      <x:c r="I92" s="20"/>
+      <x:c r="J92" s="20"/>
+      <x:c r="K92" s="20"/>
+      <x:c r="L92" s="20"/>
+      <x:c r="M92" s="20"/>
+      <x:c r="N92" s="20"/>
+      <x:c r="O92" s="20"/>
+      <x:c r="P92" s="20"/>
+      <x:c r="Q92" s="20"/>
+      <x:c r="R92" s="20"/>
+      <x:c r="S92" s="20"/>
+      <x:c r="T92" s="20"/>
+      <x:c r="U92" s="20" t="str">
         <x:f>IF(A92="","",IF(OR(L92="Closed",L92="False positive"),"No",IF(N92="","No target set",IF(N92&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="93">
-      <x:c r="U93" t="str">
+      <x:c r="A93" s="20"/>
+      <x:c r="B93" s="20"/>
+      <x:c r="C93" s="20"/>
+      <x:c r="D93" s="20"/>
+      <x:c r="E93" s="20"/>
+      <x:c r="F93" s="20"/>
+      <x:c r="G93" s="20"/>
+      <x:c r="H93" s="20"/>
+      <x:c r="I93" s="20"/>
+      <x:c r="J93" s="20"/>
+      <x:c r="K93" s="20"/>
+      <x:c r="L93" s="20"/>
+      <x:c r="M93" s="20"/>
+      <x:c r="N93" s="20"/>
+      <x:c r="O93" s="20"/>
+      <x:c r="P93" s="20"/>
+      <x:c r="Q93" s="20"/>
+      <x:c r="R93" s="20"/>
+      <x:c r="S93" s="20"/>
+      <x:c r="T93" s="20"/>
+      <x:c r="U93" s="20" t="str">
         <x:f>IF(A93="","",IF(OR(L93="Closed",L93="False positive"),"No",IF(N93="","No target set",IF(N93&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="94">
-      <x:c r="U94" t="str">
+      <x:c r="A94" s="20"/>
+      <x:c r="B94" s="20"/>
+      <x:c r="C94" s="20"/>
+      <x:c r="D94" s="20"/>
+      <x:c r="E94" s="20"/>
+      <x:c r="F94" s="20"/>
+      <x:c r="G94" s="20"/>
+      <x:c r="H94" s="20"/>
+      <x:c r="I94" s="20"/>
+      <x:c r="J94" s="20"/>
+      <x:c r="K94" s="20"/>
+      <x:c r="L94" s="20"/>
+      <x:c r="M94" s="20"/>
+      <x:c r="N94" s="20"/>
+      <x:c r="O94" s="20"/>
+      <x:c r="P94" s="20"/>
+      <x:c r="Q94" s="20"/>
+      <x:c r="R94" s="20"/>
+      <x:c r="S94" s="20"/>
+      <x:c r="T94" s="20"/>
+      <x:c r="U94" s="20" t="str">
         <x:f>IF(A94="","",IF(OR(L94="Closed",L94="False positive"),"No",IF(N94="","No target set",IF(N94&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="95">
-      <x:c r="U95" t="str">
+      <x:c r="A95" s="20"/>
+      <x:c r="B95" s="20"/>
+      <x:c r="C95" s="20"/>
+      <x:c r="D95" s="20"/>
+      <x:c r="E95" s="20"/>
+      <x:c r="F95" s="20"/>
+      <x:c r="G95" s="20"/>
+      <x:c r="H95" s="20"/>
+      <x:c r="I95" s="20"/>
+      <x:c r="J95" s="20"/>
+      <x:c r="K95" s="20"/>
+      <x:c r="L95" s="20"/>
+      <x:c r="M95" s="20"/>
+      <x:c r="N95" s="20"/>
+      <x:c r="O95" s="20"/>
+      <x:c r="P95" s="20"/>
+      <x:c r="Q95" s="20"/>
+      <x:c r="R95" s="20"/>
+      <x:c r="S95" s="20"/>
+      <x:c r="T95" s="20"/>
+      <x:c r="U95" s="20" t="str">
         <x:f>IF(A95="","",IF(OR(L95="Closed",L95="False positive"),"No",IF(N95="","No target set",IF(N95&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="96">
-      <x:c r="U96" t="str">
+      <x:c r="A96" s="20"/>
+      <x:c r="B96" s="20"/>
+      <x:c r="C96" s="20"/>
+      <x:c r="D96" s="20"/>
+      <x:c r="E96" s="20"/>
+      <x:c r="F96" s="20"/>
+      <x:c r="G96" s="20"/>
+      <x:c r="H96" s="20"/>
+      <x:c r="I96" s="20"/>
+      <x:c r="J96" s="20"/>
+      <x:c r="K96" s="20"/>
+      <x:c r="L96" s="20"/>
+      <x:c r="M96" s="20"/>
+      <x:c r="N96" s="20"/>
+      <x:c r="O96" s="20"/>
+      <x:c r="P96" s="20"/>
+      <x:c r="Q96" s="20"/>
+      <x:c r="R96" s="20"/>
+      <x:c r="S96" s="20"/>
+      <x:c r="T96" s="20"/>
+      <x:c r="U96" s="20" t="str">
         <x:f>IF(A96="","",IF(OR(L96="Closed",L96="False positive"),"No",IF(N96="","No target set",IF(N96&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="97">
-      <x:c r="U97" t="str">
+      <x:c r="A97" s="20"/>
+      <x:c r="B97" s="20"/>
+      <x:c r="C97" s="20"/>
+      <x:c r="D97" s="20"/>
+      <x:c r="E97" s="20"/>
+      <x:c r="F97" s="20"/>
+      <x:c r="G97" s="20"/>
+      <x:c r="H97" s="20"/>
+      <x:c r="I97" s="20"/>
+      <x:c r="J97" s="20"/>
+      <x:c r="K97" s="20"/>
+      <x:c r="L97" s="20"/>
+      <x:c r="M97" s="20"/>
+      <x:c r="N97" s="20"/>
+      <x:c r="O97" s="20"/>
+      <x:c r="P97" s="20"/>
+      <x:c r="Q97" s="20"/>
+      <x:c r="R97" s="20"/>
+      <x:c r="S97" s="20"/>
+      <x:c r="T97" s="20"/>
+      <x:c r="U97" s="20" t="str">
         <x:f>IF(A97="","",IF(OR(L97="Closed",L97="False positive"),"No",IF(N97="","No target set",IF(N97&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="98">
-      <x:c r="U98" t="str">
+      <x:c r="A98" s="20"/>
+      <x:c r="B98" s="20"/>
+      <x:c r="C98" s="20"/>
+      <x:c r="D98" s="20"/>
+      <x:c r="E98" s="20"/>
+      <x:c r="F98" s="20"/>
+      <x:c r="G98" s="20"/>
+      <x:c r="H98" s="20"/>
+      <x:c r="I98" s="20"/>
+      <x:c r="J98" s="20"/>
+      <x:c r="K98" s="20"/>
+      <x:c r="L98" s="20"/>
+      <x:c r="M98" s="20"/>
+      <x:c r="N98" s="20"/>
+      <x:c r="O98" s="20"/>
+      <x:c r="P98" s="20"/>
+      <x:c r="Q98" s="20"/>
+      <x:c r="R98" s="20"/>
+      <x:c r="S98" s="20"/>
+      <x:c r="T98" s="20"/>
+      <x:c r="U98" s="20" t="str">
         <x:f>IF(A98="","",IF(OR(L98="Closed",L98="False positive"),"No",IF(N98="","No target set",IF(N98&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="99">
-      <x:c r="U99" t="str">
+      <x:c r="A99" s="20"/>
+      <x:c r="B99" s="20"/>
+      <x:c r="C99" s="20"/>
+      <x:c r="D99" s="20"/>
+      <x:c r="E99" s="20"/>
+      <x:c r="F99" s="20"/>
+      <x:c r="G99" s="20"/>
+      <x:c r="H99" s="20"/>
+      <x:c r="I99" s="20"/>
+      <x:c r="J99" s="20"/>
+      <x:c r="K99" s="20"/>
+      <x:c r="L99" s="20"/>
+      <x:c r="M99" s="20"/>
+      <x:c r="N99" s="20"/>
+      <x:c r="O99" s="20"/>
+      <x:c r="P99" s="20"/>
+      <x:c r="Q99" s="20"/>
+      <x:c r="R99" s="20"/>
+      <x:c r="S99" s="20"/>
+      <x:c r="T99" s="20"/>
+      <x:c r="U99" s="20" t="str">
         <x:f>IF(A99="","",IF(OR(L99="Closed",L99="False positive"),"No",IF(N99="","No target set",IF(N99&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="100">
-      <x:c r="U100" t="str">
+      <x:c r="A100" s="20"/>
+      <x:c r="B100" s="20"/>
+      <x:c r="C100" s="20"/>
+      <x:c r="D100" s="20"/>
+      <x:c r="E100" s="20"/>
+      <x:c r="F100" s="20"/>
+      <x:c r="G100" s="20"/>
+      <x:c r="H100" s="20"/>
+      <x:c r="I100" s="20"/>
+      <x:c r="J100" s="20"/>
+      <x:c r="K100" s="20"/>
+      <x:c r="L100" s="20"/>
+      <x:c r="M100" s="20"/>
+      <x:c r="N100" s="20"/>
+      <x:c r="O100" s="20"/>
+      <x:c r="P100" s="20"/>
+      <x:c r="Q100" s="20"/>
+      <x:c r="R100" s="20"/>
+      <x:c r="S100" s="20"/>
+      <x:c r="T100" s="20"/>
+      <x:c r="U100" s="20" t="str">
         <x:f>IF(A100="","",IF(OR(L100="Closed",L100="False positive"),"No",IF(N100="","No target set",IF(N100&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="101">
-      <x:c r="U101" t="str">
+      <x:c r="A101" s="20"/>
+      <x:c r="B101" s="20"/>
+      <x:c r="C101" s="20"/>
+      <x:c r="D101" s="20"/>
+      <x:c r="E101" s="20"/>
+      <x:c r="F101" s="20"/>
+      <x:c r="G101" s="20"/>
+      <x:c r="H101" s="20"/>
+      <x:c r="I101" s="20"/>
+      <x:c r="J101" s="20"/>
+      <x:c r="K101" s="20"/>
+      <x:c r="L101" s="20"/>
+      <x:c r="M101" s="20"/>
+      <x:c r="N101" s="20"/>
+      <x:c r="O101" s="20"/>
+      <x:c r="P101" s="20"/>
+      <x:c r="Q101" s="20"/>
+      <x:c r="R101" s="20"/>
+      <x:c r="S101" s="20"/>
+      <x:c r="T101" s="20"/>
+      <x:c r="U101" s="20" t="str">
         <x:f>IF(A101="","",IF(OR(L101="Closed",L101="False positive"),"No",IF(N101="","No target set",IF(N101&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="102">
-      <x:c r="U102" t="str">
+      <x:c r="A102" s="20"/>
+      <x:c r="B102" s="20"/>
+      <x:c r="C102" s="20"/>
+      <x:c r="D102" s="20"/>
+      <x:c r="E102" s="20"/>
+      <x:c r="F102" s="20"/>
+      <x:c r="G102" s="20"/>
+      <x:c r="H102" s="20"/>
+      <x:c r="I102" s="20"/>
+      <x:c r="J102" s="20"/>
+      <x:c r="K102" s="20"/>
+      <x:c r="L102" s="20"/>
+      <x:c r="M102" s="20"/>
+      <x:c r="N102" s="20"/>
+      <x:c r="O102" s="20"/>
+      <x:c r="P102" s="20"/>
+      <x:c r="Q102" s="20"/>
+      <x:c r="R102" s="20"/>
+      <x:c r="S102" s="20"/>
+      <x:c r="T102" s="20"/>
+      <x:c r="U102" s="20" t="str">
         <x:f>IF(A102="","",IF(OR(L102="Closed",L102="False positive"),"No",IF(N102="","No target set",IF(N102&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="103">
-      <x:c r="U103" t="str">
+      <x:c r="A103" s="20"/>
+      <x:c r="B103" s="20"/>
+      <x:c r="C103" s="20"/>
+      <x:c r="D103" s="20"/>
+      <x:c r="E103" s="20"/>
+      <x:c r="F103" s="20"/>
+      <x:c r="G103" s="20"/>
+      <x:c r="H103" s="20"/>
+      <x:c r="I103" s="20"/>
+      <x:c r="J103" s="20"/>
+      <x:c r="K103" s="20"/>
+      <x:c r="L103" s="20"/>
+      <x:c r="M103" s="20"/>
+      <x:c r="N103" s="20"/>
+      <x:c r="O103" s="20"/>
+      <x:c r="P103" s="20"/>
+      <x:c r="Q103" s="20"/>
+      <x:c r="R103" s="20"/>
+      <x:c r="S103" s="20"/>
+      <x:c r="T103" s="20"/>
+      <x:c r="U103" s="20" t="str">
         <x:f>IF(A103="","",IF(OR(L103="Closed",L103="False positive"),"No",IF(N103="","No target set",IF(N103&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="104">
-      <x:c r="U104" t="str">
+      <x:c r="A104" s="20"/>
+      <x:c r="B104" s="20"/>
+      <x:c r="C104" s="20"/>
+      <x:c r="D104" s="20"/>
+      <x:c r="E104" s="20"/>
+      <x:c r="F104" s="20"/>
+      <x:c r="G104" s="20"/>
+      <x:c r="H104" s="20"/>
+      <x:c r="I104" s="20"/>
+      <x:c r="J104" s="20"/>
+      <x:c r="K104" s="20"/>
+      <x:c r="L104" s="20"/>
+      <x:c r="M104" s="20"/>
+      <x:c r="N104" s="20"/>
+      <x:c r="O104" s="20"/>
+      <x:c r="P104" s="20"/>
+      <x:c r="Q104" s="20"/>
+      <x:c r="R104" s="20"/>
+      <x:c r="S104" s="20"/>
+      <x:c r="T104" s="20"/>
+      <x:c r="U104" s="20" t="str">
         <x:f>IF(A104="","",IF(OR(L104="Closed",L104="False positive"),"No",IF(N104="","No target set",IF(N104&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="105">
-      <x:c r="U105" t="str">
+      <x:c r="A105" s="20"/>
+      <x:c r="B105" s="20"/>
+      <x:c r="C105" s="20"/>
+      <x:c r="D105" s="20"/>
+      <x:c r="E105" s="20"/>
+      <x:c r="F105" s="20"/>
+      <x:c r="G105" s="20"/>
+      <x:c r="H105" s="20"/>
+      <x:c r="I105" s="20"/>
+      <x:c r="J105" s="20"/>
+      <x:c r="K105" s="20"/>
+      <x:c r="L105" s="20"/>
+      <x:c r="M105" s="20"/>
+      <x:c r="N105" s="20"/>
+      <x:c r="O105" s="20"/>
+      <x:c r="P105" s="20"/>
+      <x:c r="Q105" s="20"/>
+      <x:c r="R105" s="20"/>
+      <x:c r="S105" s="20"/>
+      <x:c r="T105" s="20"/>
+      <x:c r="U105" s="20" t="str">
         <x:f>IF(A105="","",IF(OR(L105="Closed",L105="False positive"),"No",IF(N105="","No target set",IF(N105&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="106">
-      <x:c r="U106" t="str">
+      <x:c r="A106" s="20"/>
+      <x:c r="B106" s="20"/>
+      <x:c r="C106" s="20"/>
+      <x:c r="D106" s="20"/>
+      <x:c r="E106" s="20"/>
+      <x:c r="F106" s="20"/>
+      <x:c r="G106" s="20"/>
+      <x:c r="H106" s="20"/>
+      <x:c r="I106" s="20"/>
+      <x:c r="J106" s="20"/>
+      <x:c r="K106" s="20"/>
+      <x:c r="L106" s="20"/>
+      <x:c r="M106" s="20"/>
+      <x:c r="N106" s="20"/>
+      <x:c r="O106" s="20"/>
+      <x:c r="P106" s="20"/>
+      <x:c r="Q106" s="20"/>
+      <x:c r="R106" s="20"/>
+      <x:c r="S106" s="20"/>
+      <x:c r="T106" s="20"/>
+      <x:c r="U106" s="20" t="str">
         <x:f>IF(A106="","",IF(OR(L106="Closed",L106="False positive"),"No",IF(N106="","No target set",IF(N106&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="107">
-      <x:c r="U107" t="str">
+      <x:c r="A107" s="20"/>
+      <x:c r="B107" s="20"/>
+      <x:c r="C107" s="20"/>
+      <x:c r="D107" s="20"/>
+      <x:c r="E107" s="20"/>
+      <x:c r="F107" s="20"/>
+      <x:c r="G107" s="20"/>
+      <x:c r="H107" s="20"/>
+      <x:c r="I107" s="20"/>
+      <x:c r="J107" s="20"/>
+      <x:c r="K107" s="20"/>
+      <x:c r="L107" s="20"/>
+      <x:c r="M107" s="20"/>
+      <x:c r="N107" s="20"/>
+      <x:c r="O107" s="20"/>
+      <x:c r="P107" s="20"/>
+      <x:c r="Q107" s="20"/>
+      <x:c r="R107" s="20"/>
+      <x:c r="S107" s="20"/>
+      <x:c r="T107" s="20"/>
+      <x:c r="U107" s="20" t="str">
         <x:f>IF(A107="","",IF(OR(L107="Closed",L107="False positive"),"No",IF(N107="","No target set",IF(N107&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="108">
-      <x:c r="U108" t="str">
+      <x:c r="A108" s="20"/>
+      <x:c r="B108" s="20"/>
+      <x:c r="C108" s="20"/>
+      <x:c r="D108" s="20"/>
+      <x:c r="E108" s="20"/>
+      <x:c r="F108" s="20"/>
+      <x:c r="G108" s="20"/>
+      <x:c r="H108" s="20"/>
+      <x:c r="I108" s="20"/>
+      <x:c r="J108" s="20"/>
+      <x:c r="K108" s="20"/>
+      <x:c r="L108" s="20"/>
+      <x:c r="M108" s="20"/>
+      <x:c r="N108" s="20"/>
+      <x:c r="O108" s="20"/>
+      <x:c r="P108" s="20"/>
+      <x:c r="Q108" s="20"/>
+      <x:c r="R108" s="20"/>
+      <x:c r="S108" s="20"/>
+      <x:c r="T108" s="20"/>
+      <x:c r="U108" s="20" t="str">
         <x:f>IF(A108="","",IF(OR(L108="Closed",L108="False positive"),"No",IF(N108="","No target set",IF(N108&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="109">
-      <x:c r="U109" t="str">
+      <x:c r="A109" s="20"/>
+      <x:c r="B109" s="20"/>
+      <x:c r="C109" s="20"/>
+      <x:c r="D109" s="20"/>
+      <x:c r="E109" s="20"/>
+      <x:c r="F109" s="20"/>
+      <x:c r="G109" s="20"/>
+      <x:c r="H109" s="20"/>
+      <x:c r="I109" s="20"/>
+      <x:c r="J109" s="20"/>
+      <x:c r="K109" s="20"/>
+      <x:c r="L109" s="20"/>
+      <x:c r="M109" s="20"/>
+      <x:c r="N109" s="20"/>
+      <x:c r="O109" s="20"/>
+      <x:c r="P109" s="20"/>
+      <x:c r="Q109" s="20"/>
+      <x:c r="R109" s="20"/>
+      <x:c r="S109" s="20"/>
+      <x:c r="T109" s="20"/>
+      <x:c r="U109" s="20" t="str">
         <x:f>IF(A109="","",IF(OR(L109="Closed",L109="False positive"),"No",IF(N109="","No target set",IF(N109&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="110">
-      <x:c r="U110" t="str">
+      <x:c r="A110" s="20"/>
+      <x:c r="B110" s="20"/>
+      <x:c r="C110" s="20"/>
+      <x:c r="D110" s="20"/>
+      <x:c r="E110" s="20"/>
+      <x:c r="F110" s="20"/>
+      <x:c r="G110" s="20"/>
+      <x:c r="H110" s="20"/>
+      <x:c r="I110" s="20"/>
+      <x:c r="J110" s="20"/>
+      <x:c r="K110" s="20"/>
+      <x:c r="L110" s="20"/>
+      <x:c r="M110" s="20"/>
+      <x:c r="N110" s="20"/>
+      <x:c r="O110" s="20"/>
+      <x:c r="P110" s="20"/>
+      <x:c r="Q110" s="20"/>
+      <x:c r="R110" s="20"/>
+      <x:c r="S110" s="20"/>
+      <x:c r="T110" s="20"/>
+      <x:c r="U110" s="20" t="str">
         <x:f>IF(A110="","",IF(OR(L110="Closed",L110="False positive"),"No",IF(N110="","No target set",IF(N110&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="111">
-      <x:c r="U111" t="str">
+      <x:c r="A111" s="20"/>
+      <x:c r="B111" s="20"/>
+      <x:c r="C111" s="20"/>
+      <x:c r="D111" s="20"/>
+      <x:c r="E111" s="20"/>
+      <x:c r="F111" s="20"/>
+      <x:c r="G111" s="20"/>
+      <x:c r="H111" s="20"/>
+      <x:c r="I111" s="20"/>
+      <x:c r="J111" s="20"/>
+      <x:c r="K111" s="20"/>
+      <x:c r="L111" s="20"/>
+      <x:c r="M111" s="20"/>
+      <x:c r="N111" s="20"/>
+      <x:c r="O111" s="20"/>
+      <x:c r="P111" s="20"/>
+      <x:c r="Q111" s="20"/>
+      <x:c r="R111" s="20"/>
+      <x:c r="S111" s="20"/>
+      <x:c r="T111" s="20"/>
+      <x:c r="U111" s="20" t="str">
         <x:f>IF(A111="","",IF(OR(L111="Closed",L111="False positive"),"No",IF(N111="","No target set",IF(N111&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="112">
-      <x:c r="U112" t="str">
+      <x:c r="A112" s="20"/>
+      <x:c r="B112" s="20"/>
+      <x:c r="C112" s="20"/>
+      <x:c r="D112" s="20"/>
+      <x:c r="E112" s="20"/>
+      <x:c r="F112" s="20"/>
+      <x:c r="G112" s="20"/>
+      <x:c r="H112" s="20"/>
+      <x:c r="I112" s="20"/>
+      <x:c r="J112" s="20"/>
+      <x:c r="K112" s="20"/>
+      <x:c r="L112" s="20"/>
+      <x:c r="M112" s="20"/>
+      <x:c r="N112" s="20"/>
+      <x:c r="O112" s="20"/>
+      <x:c r="P112" s="20"/>
+      <x:c r="Q112" s="20"/>
+      <x:c r="R112" s="20"/>
+      <x:c r="S112" s="20"/>
+      <x:c r="T112" s="20"/>
+      <x:c r="U112" s="20" t="str">
         <x:f>IF(A112="","",IF(OR(L112="Closed",L112="False positive"),"No",IF(N112="","No target set",IF(N112&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="113">
-      <x:c r="U113" t="str">
+      <x:c r="A113" s="20"/>
+      <x:c r="B113" s="20"/>
+      <x:c r="C113" s="20"/>
+      <x:c r="D113" s="20"/>
+      <x:c r="E113" s="20"/>
+      <x:c r="F113" s="20"/>
+      <x:c r="G113" s="20"/>
+      <x:c r="H113" s="20"/>
+      <x:c r="I113" s="20"/>
+      <x:c r="J113" s="20"/>
+      <x:c r="K113" s="20"/>
+      <x:c r="L113" s="20"/>
+      <x:c r="M113" s="20"/>
+      <x:c r="N113" s="20"/>
+      <x:c r="O113" s="20"/>
+      <x:c r="P113" s="20"/>
+      <x:c r="Q113" s="20"/>
+      <x:c r="R113" s="20"/>
+      <x:c r="S113" s="20"/>
+      <x:c r="T113" s="20"/>
+      <x:c r="U113" s="20" t="str">
         <x:f>IF(A113="","",IF(OR(L113="Closed",L113="False positive"),"No",IF(N113="","No target set",IF(N113&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="114">
-      <x:c r="U114" t="str">
+      <x:c r="A114" s="20"/>
+      <x:c r="B114" s="20"/>
+      <x:c r="C114" s="20"/>
+      <x:c r="D114" s="20"/>
+      <x:c r="E114" s="20"/>
+      <x:c r="F114" s="20"/>
+      <x:c r="G114" s="20"/>
+      <x:c r="H114" s="20"/>
+      <x:c r="I114" s="20"/>
+      <x:c r="J114" s="20"/>
+      <x:c r="K114" s="20"/>
+      <x:c r="L114" s="20"/>
+      <x:c r="M114" s="20"/>
+      <x:c r="N114" s="20"/>
+      <x:c r="O114" s="20"/>
+      <x:c r="P114" s="20"/>
+      <x:c r="Q114" s="20"/>
+      <x:c r="R114" s="20"/>
+      <x:c r="S114" s="20"/>
+      <x:c r="T114" s="20"/>
+      <x:c r="U114" s="20" t="str">
         <x:f>IF(A114="","",IF(OR(L114="Closed",L114="False positive"),"No",IF(N114="","No target set",IF(N114&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="115">
-      <x:c r="U115" t="str">
+      <x:c r="A115" s="20"/>
+      <x:c r="B115" s="20"/>
+      <x:c r="C115" s="20"/>
+      <x:c r="D115" s="20"/>
+      <x:c r="E115" s="20"/>
+      <x:c r="F115" s="20"/>
+      <x:c r="G115" s="20"/>
+      <x:c r="H115" s="20"/>
+      <x:c r="I115" s="20"/>
+      <x:c r="J115" s="20"/>
+      <x:c r="K115" s="20"/>
+      <x:c r="L115" s="20"/>
+      <x:c r="M115" s="20"/>
+      <x:c r="N115" s="20"/>
+      <x:c r="O115" s="20"/>
+      <x:c r="P115" s="20"/>
+      <x:c r="Q115" s="20"/>
+      <x:c r="R115" s="20"/>
+      <x:c r="S115" s="20"/>
+      <x:c r="T115" s="20"/>
+      <x:c r="U115" s="20" t="str">
         <x:f>IF(A115="","",IF(OR(L115="Closed",L115="False positive"),"No",IF(N115="","No target set",IF(N115&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="116">
-      <x:c r="U116" t="str">
+      <x:c r="A116" s="20"/>
+      <x:c r="B116" s="20"/>
+      <x:c r="C116" s="20"/>
+      <x:c r="D116" s="20"/>
+      <x:c r="E116" s="20"/>
+      <x:c r="F116" s="20"/>
+      <x:c r="G116" s="20"/>
+      <x:c r="H116" s="20"/>
+      <x:c r="I116" s="20"/>
+      <x:c r="J116" s="20"/>
+      <x:c r="K116" s="20"/>
+      <x:c r="L116" s="20"/>
+      <x:c r="M116" s="20"/>
+      <x:c r="N116" s="20"/>
+      <x:c r="O116" s="20"/>
+      <x:c r="P116" s="20"/>
+      <x:c r="Q116" s="20"/>
+      <x:c r="R116" s="20"/>
+      <x:c r="S116" s="20"/>
+      <x:c r="T116" s="20"/>
+      <x:c r="U116" s="20" t="str">
         <x:f>IF(A116="","",IF(OR(L116="Closed",L116="False positive"),"No",IF(N116="","No target set",IF(N116&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="117">
-      <x:c r="U117" t="str">
+      <x:c r="A117" s="20"/>
+      <x:c r="B117" s="20"/>
+      <x:c r="C117" s="20"/>
+      <x:c r="D117" s="20"/>
+      <x:c r="E117" s="20"/>
+      <x:c r="F117" s="20"/>
+      <x:c r="G117" s="20"/>
+      <x:c r="H117" s="20"/>
+      <x:c r="I117" s="20"/>
+      <x:c r="J117" s="20"/>
+      <x:c r="K117" s="20"/>
+      <x:c r="L117" s="20"/>
+      <x:c r="M117" s="20"/>
+      <x:c r="N117" s="20"/>
+      <x:c r="O117" s="20"/>
+      <x:c r="P117" s="20"/>
+      <x:c r="Q117" s="20"/>
+      <x:c r="R117" s="20"/>
+      <x:c r="S117" s="20"/>
+      <x:c r="T117" s="20"/>
+      <x:c r="U117" s="20" t="str">
         <x:f>IF(A117="","",IF(OR(L117="Closed",L117="False positive"),"No",IF(N117="","No target set",IF(N117&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="118">
-      <x:c r="U118" t="str">
+      <x:c r="A118" s="20"/>
+      <x:c r="B118" s="20"/>
+      <x:c r="C118" s="20"/>
+      <x:c r="D118" s="20"/>
+      <x:c r="E118" s="20"/>
+      <x:c r="F118" s="20"/>
+      <x:c r="G118" s="20"/>
+      <x:c r="H118" s="20"/>
+      <x:c r="I118" s="20"/>
+      <x:c r="J118" s="20"/>
+      <x:c r="K118" s="20"/>
+      <x:c r="L118" s="20"/>
+      <x:c r="M118" s="20"/>
+      <x:c r="N118" s="20"/>
+      <x:c r="O118" s="20"/>
+      <x:c r="P118" s="20"/>
+      <x:c r="Q118" s="20"/>
+      <x:c r="R118" s="20"/>
+      <x:c r="S118" s="20"/>
+      <x:c r="T118" s="20"/>
+      <x:c r="U118" s="20" t="str">
         <x:f>IF(A118="","",IF(OR(L118="Closed",L118="False positive"),"No",IF(N118="","No target set",IF(N118&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="119">
-      <x:c r="U119" t="str">
+      <x:c r="A119" s="20"/>
+      <x:c r="B119" s="20"/>
+      <x:c r="C119" s="20"/>
+      <x:c r="D119" s="20"/>
+      <x:c r="E119" s="20"/>
+      <x:c r="F119" s="20"/>
+      <x:c r="G119" s="20"/>
+      <x:c r="H119" s="20"/>
+      <x:c r="I119" s="20"/>
+      <x:c r="J119" s="20"/>
+      <x:c r="K119" s="20"/>
+      <x:c r="L119" s="20"/>
+      <x:c r="M119" s="20"/>
+      <x:c r="N119" s="20"/>
+      <x:c r="O119" s="20"/>
+      <x:c r="P119" s="20"/>
+      <x:c r="Q119" s="20"/>
+      <x:c r="R119" s="20"/>
+      <x:c r="S119" s="20"/>
+      <x:c r="T119" s="20"/>
+      <x:c r="U119" s="20" t="str">
         <x:f>IF(A119="","",IF(OR(L119="Closed",L119="False positive"),"No",IF(N119="","No target set",IF(N119&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="120">
-      <x:c r="U120" t="str">
+      <x:c r="A120" s="20"/>
+      <x:c r="B120" s="20"/>
+      <x:c r="C120" s="20"/>
+      <x:c r="D120" s="20"/>
+      <x:c r="E120" s="20"/>
+      <x:c r="F120" s="20"/>
+      <x:c r="G120" s="20"/>
+      <x:c r="H120" s="20"/>
+      <x:c r="I120" s="20"/>
+      <x:c r="J120" s="20"/>
+      <x:c r="K120" s="20"/>
+      <x:c r="L120" s="20"/>
+      <x:c r="M120" s="20"/>
+      <x:c r="N120" s="20"/>
+      <x:c r="O120" s="20"/>
+      <x:c r="P120" s="20"/>
+      <x:c r="Q120" s="20"/>
+      <x:c r="R120" s="20"/>
+      <x:c r="S120" s="20"/>
+      <x:c r="T120" s="20"/>
+      <x:c r="U120" s="20" t="str">
         <x:f>IF(A120="","",IF(OR(L120="Closed",L120="False positive"),"No",IF(N120="","No target set",IF(N120&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="121">
-      <x:c r="U121" t="str">
+      <x:c r="A121" s="20"/>
+      <x:c r="B121" s="20"/>
+      <x:c r="C121" s="20"/>
+      <x:c r="D121" s="20"/>
+      <x:c r="E121" s="20"/>
+      <x:c r="F121" s="20"/>
+      <x:c r="G121" s="20"/>
+      <x:c r="H121" s="20"/>
+      <x:c r="I121" s="20"/>
+      <x:c r="J121" s="20"/>
+      <x:c r="K121" s="20"/>
+      <x:c r="L121" s="20"/>
+      <x:c r="M121" s="20"/>
+      <x:c r="N121" s="20"/>
+      <x:c r="O121" s="20"/>
+      <x:c r="P121" s="20"/>
+      <x:c r="Q121" s="20"/>
+      <x:c r="R121" s="20"/>
+      <x:c r="S121" s="20"/>
+      <x:c r="T121" s="20"/>
+      <x:c r="U121" s="20" t="str">
         <x:f>IF(A121="","",IF(OR(L121="Closed",L121="False positive"),"No",IF(N121="","No target set",IF(N121&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="122">
-      <x:c r="U122" t="str">
+      <x:c r="A122" s="20"/>
+      <x:c r="B122" s="20"/>
+      <x:c r="C122" s="20"/>
+      <x:c r="D122" s="20"/>
+      <x:c r="E122" s="20"/>
+      <x:c r="F122" s="20"/>
+      <x:c r="G122" s="20"/>
+      <x:c r="H122" s="20"/>
+      <x:c r="I122" s="20"/>
+      <x:c r="J122" s="20"/>
+      <x:c r="K122" s="20"/>
+      <x:c r="L122" s="20"/>
+      <x:c r="M122" s="20"/>
+      <x:c r="N122" s="20"/>
+      <x:c r="O122" s="20"/>
+      <x:c r="P122" s="20"/>
+      <x:c r="Q122" s="20"/>
+      <x:c r="R122" s="20"/>
+      <x:c r="S122" s="20"/>
+      <x:c r="T122" s="20"/>
+      <x:c r="U122" s="20" t="str">
         <x:f>IF(A122="","",IF(OR(L122="Closed",L122="False positive"),"No",IF(N122="","No target set",IF(N122&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="123">
-      <x:c r="U123" t="str">
+      <x:c r="A123" s="20"/>
+      <x:c r="B123" s="20"/>
+      <x:c r="C123" s="20"/>
+      <x:c r="D123" s="20"/>
+      <x:c r="E123" s="20"/>
+      <x:c r="F123" s="20"/>
+      <x:c r="G123" s="20"/>
+      <x:c r="H123" s="20"/>
+      <x:c r="I123" s="20"/>
+      <x:c r="J123" s="20"/>
+      <x:c r="K123" s="20"/>
+      <x:c r="L123" s="20"/>
+      <x:c r="M123" s="20"/>
+      <x:c r="N123" s="20"/>
+      <x:c r="O123" s="20"/>
+      <x:c r="P123" s="20"/>
+      <x:c r="Q123" s="20"/>
+      <x:c r="R123" s="20"/>
+      <x:c r="S123" s="20"/>
+      <x:c r="T123" s="20"/>
+      <x:c r="U123" s="20" t="str">
         <x:f>IF(A123="","",IF(OR(L123="Closed",L123="False positive"),"No",IF(N123="","No target set",IF(N123&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="124">
-      <x:c r="U124" t="str">
+      <x:c r="A124" s="20"/>
+      <x:c r="B124" s="20"/>
+      <x:c r="C124" s="20"/>
+      <x:c r="D124" s="20"/>
+      <x:c r="E124" s="20"/>
+      <x:c r="F124" s="20"/>
+      <x:c r="G124" s="20"/>
+      <x:c r="H124" s="20"/>
+      <x:c r="I124" s="20"/>
+      <x:c r="J124" s="20"/>
+      <x:c r="K124" s="20"/>
+      <x:c r="L124" s="20"/>
+      <x:c r="M124" s="20"/>
+      <x:c r="N124" s="20"/>
+      <x:c r="O124" s="20"/>
+      <x:c r="P124" s="20"/>
+      <x:c r="Q124" s="20"/>
+      <x:c r="R124" s="20"/>
+      <x:c r="S124" s="20"/>
+      <x:c r="T124" s="20"/>
+      <x:c r="U124" s="20" t="str">
         <x:f>IF(A124="","",IF(OR(L124="Closed",L124="False positive"),"No",IF(N124="","No target set",IF(N124&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="125">
-      <x:c r="U125" t="str">
+      <x:c r="A125" s="20"/>
+      <x:c r="B125" s="20"/>
+      <x:c r="C125" s="20"/>
+      <x:c r="D125" s="20"/>
+      <x:c r="E125" s="20"/>
+      <x:c r="F125" s="20"/>
+      <x:c r="G125" s="20"/>
+      <x:c r="H125" s="20"/>
+      <x:c r="I125" s="20"/>
+      <x:c r="J125" s="20"/>
+      <x:c r="K125" s="20"/>
+      <x:c r="L125" s="20"/>
+      <x:c r="M125" s="20"/>
+      <x:c r="N125" s="20"/>
+      <x:c r="O125" s="20"/>
+      <x:c r="P125" s="20"/>
+      <x:c r="Q125" s="20"/>
+      <x:c r="R125" s="20"/>
+      <x:c r="S125" s="20"/>
+      <x:c r="T125" s="20"/>
+      <x:c r="U125" s="20" t="str">
         <x:f>IF(A125="","",IF(OR(L125="Closed",L125="False positive"),"No",IF(N125="","No target set",IF(N125&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="126">
-      <x:c r="U126" t="str">
+      <x:c r="A126" s="20"/>
+      <x:c r="B126" s="20"/>
+      <x:c r="C126" s="20"/>
+      <x:c r="D126" s="20"/>
+      <x:c r="E126" s="20"/>
+      <x:c r="F126" s="20"/>
+      <x:c r="G126" s="20"/>
+      <x:c r="H126" s="20"/>
+      <x:c r="I126" s="20"/>
+      <x:c r="J126" s="20"/>
+      <x:c r="K126" s="20"/>
+      <x:c r="L126" s="20"/>
+      <x:c r="M126" s="20"/>
+      <x:c r="N126" s="20"/>
+      <x:c r="O126" s="20"/>
+      <x:c r="P126" s="20"/>
+      <x:c r="Q126" s="20"/>
+      <x:c r="R126" s="20"/>
+      <x:c r="S126" s="20"/>
+      <x:c r="T126" s="20"/>
+      <x:c r="U126" s="20" t="str">
         <x:f>IF(A126="","",IF(OR(L126="Closed",L126="False positive"),"No",IF(N126="","No target set",IF(N126&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="127">
-      <x:c r="U127" t="str">
+      <x:c r="A127" s="20"/>
+      <x:c r="B127" s="20"/>
+      <x:c r="C127" s="20"/>
+      <x:c r="D127" s="20"/>
+      <x:c r="E127" s="20"/>
+      <x:c r="F127" s="20"/>
+      <x:c r="G127" s="20"/>
+      <x:c r="H127" s="20"/>
+      <x:c r="I127" s="20"/>
+      <x:c r="J127" s="20"/>
+      <x:c r="K127" s="20"/>
+      <x:c r="L127" s="20"/>
+      <x:c r="M127" s="20"/>
+      <x:c r="N127" s="20"/>
+      <x:c r="O127" s="20"/>
+      <x:c r="P127" s="20"/>
+      <x:c r="Q127" s="20"/>
+      <x:c r="R127" s="20"/>
+      <x:c r="S127" s="20"/>
+      <x:c r="T127" s="20"/>
+      <x:c r="U127" s="20" t="str">
         <x:f>IF(A127="","",IF(OR(L127="Closed",L127="False positive"),"No",IF(N127="","No target set",IF(N127&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="128">
-      <x:c r="U128" t="str">
+      <x:c r="A128" s="20"/>
+      <x:c r="B128" s="20"/>
+      <x:c r="C128" s="20"/>
+      <x:c r="D128" s="20"/>
+      <x:c r="E128" s="20"/>
+      <x:c r="F128" s="20"/>
+      <x:c r="G128" s="20"/>
+      <x:c r="H128" s="20"/>
+      <x:c r="I128" s="20"/>
+      <x:c r="J128" s="20"/>
+      <x:c r="K128" s="20"/>
+      <x:c r="L128" s="20"/>
+      <x:c r="M128" s="20"/>
+      <x:c r="N128" s="20"/>
+      <x:c r="O128" s="20"/>
+      <x:c r="P128" s="20"/>
+      <x:c r="Q128" s="20"/>
+      <x:c r="R128" s="20"/>
+      <x:c r="S128" s="20"/>
+      <x:c r="T128" s="20"/>
+      <x:c r="U128" s="20" t="str">
         <x:f>IF(A128="","",IF(OR(L128="Closed",L128="False positive"),"No",IF(N128="","No target set",IF(N128&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="129">
-      <x:c r="U129" t="str">
+      <x:c r="A129" s="20"/>
+      <x:c r="B129" s="20"/>
+      <x:c r="C129" s="20"/>
+      <x:c r="D129" s="20"/>
+      <x:c r="E129" s="20"/>
+      <x:c r="F129" s="20"/>
+      <x:c r="G129" s="20"/>
+      <x:c r="H129" s="20"/>
+      <x:c r="I129" s="20"/>
+      <x:c r="J129" s="20"/>
+      <x:c r="K129" s="20"/>
+      <x:c r="L129" s="20"/>
+      <x:c r="M129" s="20"/>
+      <x:c r="N129" s="20"/>
+      <x:c r="O129" s="20"/>
+      <x:c r="P129" s="20"/>
+      <x:c r="Q129" s="20"/>
+      <x:c r="R129" s="20"/>
+      <x:c r="S129" s="20"/>
+      <x:c r="T129" s="20"/>
+      <x:c r="U129" s="20" t="str">
         <x:f>IF(A129="","",IF(OR(L129="Closed",L129="False positive"),"No",IF(N129="","No target set",IF(N129&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="130">
-      <x:c r="U130" t="str">
+      <x:c r="A130" s="20"/>
+      <x:c r="B130" s="20"/>
+      <x:c r="C130" s="20"/>
+      <x:c r="D130" s="20"/>
+      <x:c r="E130" s="20"/>
+      <x:c r="F130" s="20"/>
+      <x:c r="G130" s="20"/>
+      <x:c r="H130" s="20"/>
+      <x:c r="I130" s="20"/>
+      <x:c r="J130" s="20"/>
+      <x:c r="K130" s="20"/>
+      <x:c r="L130" s="20"/>
+      <x:c r="M130" s="20"/>
+      <x:c r="N130" s="20"/>
+      <x:c r="O130" s="20"/>
+      <x:c r="P130" s="20"/>
+      <x:c r="Q130" s="20"/>
+      <x:c r="R130" s="20"/>
+      <x:c r="S130" s="20"/>
+      <x:c r="T130" s="20"/>
+      <x:c r="U130" s="20" t="str">
         <x:f>IF(A130="","",IF(OR(L130="Closed",L130="False positive"),"No",IF(N130="","No target set",IF(N130&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="131">
-      <x:c r="U131" t="str">
+      <x:c r="A131" s="20"/>
+      <x:c r="B131" s="20"/>
+      <x:c r="C131" s="20"/>
+      <x:c r="D131" s="20"/>
+      <x:c r="E131" s="20"/>
+      <x:c r="F131" s="20"/>
+      <x:c r="G131" s="20"/>
+      <x:c r="H131" s="20"/>
+      <x:c r="I131" s="20"/>
+      <x:c r="J131" s="20"/>
+      <x:c r="K131" s="20"/>
+      <x:c r="L131" s="20"/>
+      <x:c r="M131" s="20"/>
+      <x:c r="N131" s="20"/>
+      <x:c r="O131" s="20"/>
+      <x:c r="P131" s="20"/>
+      <x:c r="Q131" s="20"/>
+      <x:c r="R131" s="20"/>
+      <x:c r="S131" s="20"/>
+      <x:c r="T131" s="20"/>
+      <x:c r="U131" s="20" t="str">
         <x:f>IF(A131="","",IF(OR(L131="Closed",L131="False positive"),"No",IF(N131="","No target set",IF(N131&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="132">
-      <x:c r="U132" t="str">
+      <x:c r="A132" s="20"/>
+      <x:c r="B132" s="20"/>
+      <x:c r="C132" s="20"/>
+      <x:c r="D132" s="20"/>
+      <x:c r="E132" s="20"/>
+      <x:c r="F132" s="20"/>
+      <x:c r="G132" s="20"/>
+      <x:c r="H132" s="20"/>
+      <x:c r="I132" s="20"/>
+      <x:c r="J132" s="20"/>
+      <x:c r="K132" s="20"/>
+      <x:c r="L132" s="20"/>
+      <x:c r="M132" s="20"/>
+      <x:c r="N132" s="20"/>
+      <x:c r="O132" s="20"/>
+      <x:c r="P132" s="20"/>
+      <x:c r="Q132" s="20"/>
+      <x:c r="R132" s="20"/>
+      <x:c r="S132" s="20"/>
+      <x:c r="T132" s="20"/>
+      <x:c r="U132" s="20" t="str">
         <x:f>IF(A132="","",IF(OR(L132="Closed",L132="False positive"),"No",IF(N132="","No target set",IF(N132&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="133">
-      <x:c r="U133" t="str">
+      <x:c r="A133" s="20"/>
+      <x:c r="B133" s="20"/>
+      <x:c r="C133" s="20"/>
+      <x:c r="D133" s="20"/>
+      <x:c r="E133" s="20"/>
+      <x:c r="F133" s="20"/>
+      <x:c r="G133" s="20"/>
+      <x:c r="H133" s="20"/>
+      <x:c r="I133" s="20"/>
+      <x:c r="J133" s="20"/>
+      <x:c r="K133" s="20"/>
+      <x:c r="L133" s="20"/>
+      <x:c r="M133" s="20"/>
+      <x:c r="N133" s="20"/>
+      <x:c r="O133" s="20"/>
+      <x:c r="P133" s="20"/>
+      <x:c r="Q133" s="20"/>
+      <x:c r="R133" s="20"/>
+      <x:c r="S133" s="20"/>
+      <x:c r="T133" s="20"/>
+      <x:c r="U133" s="20" t="str">
         <x:f>IF(A133="","",IF(OR(L133="Closed",L133="False positive"),"No",IF(N133="","No target set",IF(N133&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="134">
-      <x:c r="U134" t="str">
+      <x:c r="A134" s="20"/>
+      <x:c r="B134" s="20"/>
+      <x:c r="C134" s="20"/>
+      <x:c r="D134" s="20"/>
+      <x:c r="E134" s="20"/>
+      <x:c r="F134" s="20"/>
+      <x:c r="G134" s="20"/>
+      <x:c r="H134" s="20"/>
+      <x:c r="I134" s="20"/>
+      <x:c r="J134" s="20"/>
+      <x:c r="K134" s="20"/>
+      <x:c r="L134" s="20"/>
+      <x:c r="M134" s="20"/>
+      <x:c r="N134" s="20"/>
+      <x:c r="O134" s="20"/>
+      <x:c r="P134" s="20"/>
+      <x:c r="Q134" s="20"/>
+      <x:c r="R134" s="20"/>
+      <x:c r="S134" s="20"/>
+      <x:c r="T134" s="20"/>
+      <x:c r="U134" s="20" t="str">
         <x:f>IF(A134="","",IF(OR(L134="Closed",L134="False positive"),"No",IF(N134="","No target set",IF(N134&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="135">
-      <x:c r="U135" t="str">
+      <x:c r="A135" s="20"/>
+      <x:c r="B135" s="20"/>
+      <x:c r="C135" s="20"/>
+      <x:c r="D135" s="20"/>
+      <x:c r="E135" s="20"/>
+      <x:c r="F135" s="20"/>
+      <x:c r="G135" s="20"/>
+      <x:c r="H135" s="20"/>
+      <x:c r="I135" s="20"/>
+      <x:c r="J135" s="20"/>
+      <x:c r="K135" s="20"/>
+      <x:c r="L135" s="20"/>
+      <x:c r="M135" s="20"/>
+      <x:c r="N135" s="20"/>
+      <x:c r="O135" s="20"/>
+      <x:c r="P135" s="20"/>
+      <x:c r="Q135" s="20"/>
+      <x:c r="R135" s="20"/>
+      <x:c r="S135" s="20"/>
+      <x:c r="T135" s="20"/>
+      <x:c r="U135" s="20" t="str">
         <x:f>IF(A135="","",IF(OR(L135="Closed",L135="False positive"),"No",IF(N135="","No target set",IF(N135&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="136">
-      <x:c r="U136" t="str">
+      <x:c r="A136" s="20"/>
+      <x:c r="B136" s="20"/>
+      <x:c r="C136" s="20"/>
+      <x:c r="D136" s="20"/>
+      <x:c r="E136" s="20"/>
+      <x:c r="F136" s="20"/>
+      <x:c r="G136" s="20"/>
+      <x:c r="H136" s="20"/>
+      <x:c r="I136" s="20"/>
+      <x:c r="J136" s="20"/>
+      <x:c r="K136" s="20"/>
+      <x:c r="L136" s="20"/>
+      <x:c r="M136" s="20"/>
+      <x:c r="N136" s="20"/>
+      <x:c r="O136" s="20"/>
+      <x:c r="P136" s="20"/>
+      <x:c r="Q136" s="20"/>
+      <x:c r="R136" s="20"/>
+      <x:c r="S136" s="20"/>
+      <x:c r="T136" s="20"/>
+      <x:c r="U136" s="20" t="str">
         <x:f>IF(A136="","",IF(OR(L136="Closed",L136="False positive"),"No",IF(N136="","No target set",IF(N136&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="137">
-      <x:c r="U137" t="str">
+      <x:c r="A137" s="20"/>
+      <x:c r="B137" s="20"/>
+      <x:c r="C137" s="20"/>
+      <x:c r="D137" s="20"/>
+      <x:c r="E137" s="20"/>
+      <x:c r="F137" s="20"/>
+      <x:c r="G137" s="20"/>
+      <x:c r="H137" s="20"/>
+      <x:c r="I137" s="20"/>
+      <x:c r="J137" s="20"/>
+      <x:c r="K137" s="20"/>
+      <x:c r="L137" s="20"/>
+      <x:c r="M137" s="20"/>
+      <x:c r="N137" s="20"/>
+      <x:c r="O137" s="20"/>
+      <x:c r="P137" s="20"/>
+      <x:c r="Q137" s="20"/>
+      <x:c r="R137" s="20"/>
+      <x:c r="S137" s="20"/>
+      <x:c r="T137" s="20"/>
+      <x:c r="U137" s="20" t="str">
         <x:f>IF(A137="","",IF(OR(L137="Closed",L137="False positive"),"No",IF(N137="","No target set",IF(N137&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="138">
-      <x:c r="U138" t="str">
+      <x:c r="A138" s="20"/>
+      <x:c r="B138" s="20"/>
+      <x:c r="C138" s="20"/>
+      <x:c r="D138" s="20"/>
+      <x:c r="E138" s="20"/>
+      <x:c r="F138" s="20"/>
+      <x:c r="G138" s="20"/>
+      <x:c r="H138" s="20"/>
+      <x:c r="I138" s="20"/>
+      <x:c r="J138" s="20"/>
+      <x:c r="K138" s="20"/>
+      <x:c r="L138" s="20"/>
+      <x:c r="M138" s="20"/>
+      <x:c r="N138" s="20"/>
+      <x:c r="O138" s="20"/>
+      <x:c r="P138" s="20"/>
+      <x:c r="Q138" s="20"/>
+      <x:c r="R138" s="20"/>
+      <x:c r="S138" s="20"/>
+      <x:c r="T138" s="20"/>
+      <x:c r="U138" s="20" t="str">
         <x:f>IF(A138="","",IF(OR(L138="Closed",L138="False positive"),"No",IF(N138="","No target set",IF(N138&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="139">
-      <x:c r="U139" t="str">
+      <x:c r="A139" s="20"/>
+      <x:c r="B139" s="20"/>
+      <x:c r="C139" s="20"/>
+      <x:c r="D139" s="20"/>
+      <x:c r="E139" s="20"/>
+      <x:c r="F139" s="20"/>
+      <x:c r="G139" s="20"/>
+      <x:c r="H139" s="20"/>
+      <x:c r="I139" s="20"/>
+      <x:c r="J139" s="20"/>
+      <x:c r="K139" s="20"/>
+      <x:c r="L139" s="20"/>
+      <x:c r="M139" s="20"/>
+      <x:c r="N139" s="20"/>
+      <x:c r="O139" s="20"/>
+      <x:c r="P139" s="20"/>
+      <x:c r="Q139" s="20"/>
+      <x:c r="R139" s="20"/>
+      <x:c r="S139" s="20"/>
+      <x:c r="T139" s="20"/>
+      <x:c r="U139" s="20" t="str">
         <x:f>IF(A139="","",IF(OR(L139="Closed",L139="False positive"),"No",IF(N139="","No target set",IF(N139&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="140">
-      <x:c r="U140" t="str">
+      <x:c r="A140" s="20"/>
+      <x:c r="B140" s="20"/>
+      <x:c r="C140" s="20"/>
+      <x:c r="D140" s="20"/>
+      <x:c r="E140" s="20"/>
+      <x:c r="F140" s="20"/>
+      <x:c r="G140" s="20"/>
+      <x:c r="H140" s="20"/>
+      <x:c r="I140" s="20"/>
+      <x:c r="J140" s="20"/>
+      <x:c r="K140" s="20"/>
+      <x:c r="L140" s="20"/>
+      <x:c r="M140" s="20"/>
+      <x:c r="N140" s="20"/>
+      <x:c r="O140" s="20"/>
+      <x:c r="P140" s="20"/>
+      <x:c r="Q140" s="20"/>
+      <x:c r="R140" s="20"/>
+      <x:c r="S140" s="20"/>
+      <x:c r="T140" s="20"/>
+      <x:c r="U140" s="20" t="str">
         <x:f>IF(A140="","",IF(OR(L140="Closed",L140="False positive"),"No",IF(N140="","No target set",IF(N140&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="141">
-      <x:c r="U141" t="str">
+      <x:c r="A141" s="20"/>
+      <x:c r="B141" s="20"/>
+      <x:c r="C141" s="20"/>
+      <x:c r="D141" s="20"/>
+      <x:c r="E141" s="20"/>
+      <x:c r="F141" s="20"/>
+      <x:c r="G141" s="20"/>
+      <x:c r="H141" s="20"/>
+      <x:c r="I141" s="20"/>
+      <x:c r="J141" s="20"/>
+      <x:c r="K141" s="20"/>
+      <x:c r="L141" s="20"/>
+      <x:c r="M141" s="20"/>
+      <x:c r="N141" s="20"/>
+      <x:c r="O141" s="20"/>
+      <x:c r="P141" s="20"/>
+      <x:c r="Q141" s="20"/>
+      <x:c r="R141" s="20"/>
+      <x:c r="S141" s="20"/>
+      <x:c r="T141" s="20"/>
+      <x:c r="U141" s="20" t="str">
         <x:f>IF(A141="","",IF(OR(L141="Closed",L141="False positive"),"No",IF(N141="","No target set",IF(N141&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="142">
-      <x:c r="U142" t="str">
+      <x:c r="A142" s="20"/>
+      <x:c r="B142" s="20"/>
+      <x:c r="C142" s="20"/>
+      <x:c r="D142" s="20"/>
+      <x:c r="E142" s="20"/>
+      <x:c r="F142" s="20"/>
+      <x:c r="G142" s="20"/>
+      <x:c r="H142" s="20"/>
+      <x:c r="I142" s="20"/>
+      <x:c r="J142" s="20"/>
+      <x:c r="K142" s="20"/>
+      <x:c r="L142" s="20"/>
+      <x:c r="M142" s="20"/>
+      <x:c r="N142" s="20"/>
+      <x:c r="O142" s="20"/>
+      <x:c r="P142" s="20"/>
+      <x:c r="Q142" s="20"/>
+      <x:c r="R142" s="20"/>
+      <x:c r="S142" s="20"/>
+      <x:c r="T142" s="20"/>
+      <x:c r="U142" s="20" t="str">
         <x:f>IF(A142="","",IF(OR(L142="Closed",L142="False positive"),"No",IF(N142="","No target set",IF(N142&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="143">
-      <x:c r="U143" t="str">
+      <x:c r="A143" s="20"/>
+      <x:c r="B143" s="20"/>
+      <x:c r="C143" s="20"/>
+      <x:c r="D143" s="20"/>
+      <x:c r="E143" s="20"/>
+      <x:c r="F143" s="20"/>
+      <x:c r="G143" s="20"/>
+      <x:c r="H143" s="20"/>
+      <x:c r="I143" s="20"/>
+      <x:c r="J143" s="20"/>
+      <x:c r="K143" s="20"/>
+      <x:c r="L143" s="20"/>
+      <x:c r="M143" s="20"/>
+      <x:c r="N143" s="20"/>
+      <x:c r="O143" s="20"/>
+      <x:c r="P143" s="20"/>
+      <x:c r="Q143" s="20"/>
+      <x:c r="R143" s="20"/>
+      <x:c r="S143" s="20"/>
+      <x:c r="T143" s="20"/>
+      <x:c r="U143" s="20" t="str">
         <x:f>IF(A143="","",IF(OR(L143="Closed",L143="False positive"),"No",IF(N143="","No target set",IF(N143&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="144">
-      <x:c r="U144" t="str">
+      <x:c r="A144" s="20"/>
+      <x:c r="B144" s="20"/>
+      <x:c r="C144" s="20"/>
+      <x:c r="D144" s="20"/>
+      <x:c r="E144" s="20"/>
+      <x:c r="F144" s="20"/>
+      <x:c r="G144" s="20"/>
+      <x:c r="H144" s="20"/>
+      <x:c r="I144" s="20"/>
+      <x:c r="J144" s="20"/>
+      <x:c r="K144" s="20"/>
+      <x:c r="L144" s="20"/>
+      <x:c r="M144" s="20"/>
+      <x:c r="N144" s="20"/>
+      <x:c r="O144" s="20"/>
+      <x:c r="P144" s="20"/>
+      <x:c r="Q144" s="20"/>
+      <x:c r="R144" s="20"/>
+      <x:c r="S144" s="20"/>
+      <x:c r="T144" s="20"/>
+      <x:c r="U144" s="20" t="str">
         <x:f>IF(A144="","",IF(OR(L144="Closed",L144="False positive"),"No",IF(N144="","No target set",IF(N144&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="145">
-      <x:c r="U145" t="str">
+      <x:c r="A145" s="20"/>
+      <x:c r="B145" s="20"/>
+      <x:c r="C145" s="20"/>
+      <x:c r="D145" s="20"/>
+      <x:c r="E145" s="20"/>
+      <x:c r="F145" s="20"/>
+      <x:c r="G145" s="20"/>
+      <x:c r="H145" s="20"/>
+      <x:c r="I145" s="20"/>
+      <x:c r="J145" s="20"/>
+      <x:c r="K145" s="20"/>
+      <x:c r="L145" s="20"/>
+      <x:c r="M145" s="20"/>
+      <x:c r="N145" s="20"/>
+      <x:c r="O145" s="20"/>
+      <x:c r="P145" s="20"/>
+      <x:c r="Q145" s="20"/>
+      <x:c r="R145" s="20"/>
+      <x:c r="S145" s="20"/>
+      <x:c r="T145" s="20"/>
+      <x:c r="U145" s="20" t="str">
         <x:f>IF(A145="","",IF(OR(L145="Closed",L145="False positive"),"No",IF(N145="","No target set",IF(N145&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="146">
-      <x:c r="U146" t="str">
+      <x:c r="A146" s="20"/>
+      <x:c r="B146" s="20"/>
+      <x:c r="C146" s="20"/>
+      <x:c r="D146" s="20"/>
+      <x:c r="E146" s="20"/>
+      <x:c r="F146" s="20"/>
+      <x:c r="G146" s="20"/>
+      <x:c r="H146" s="20"/>
+      <x:c r="I146" s="20"/>
+      <x:c r="J146" s="20"/>
+      <x:c r="K146" s="20"/>
+      <x:c r="L146" s="20"/>
+      <x:c r="M146" s="20"/>
+      <x:c r="N146" s="20"/>
+      <x:c r="O146" s="20"/>
+      <x:c r="P146" s="20"/>
+      <x:c r="Q146" s="20"/>
+      <x:c r="R146" s="20"/>
+      <x:c r="S146" s="20"/>
+      <x:c r="T146" s="20"/>
+      <x:c r="U146" s="20" t="str">
         <x:f>IF(A146="","",IF(OR(L146="Closed",L146="False positive"),"No",IF(N146="","No target set",IF(N146&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="147">
-      <x:c r="U147" t="str">
+      <x:c r="A147" s="20"/>
+      <x:c r="B147" s="20"/>
+      <x:c r="C147" s="20"/>
+      <x:c r="D147" s="20"/>
+      <x:c r="E147" s="20"/>
+      <x:c r="F147" s="20"/>
+      <x:c r="G147" s="20"/>
+      <x:c r="H147" s="20"/>
+      <x:c r="I147" s="20"/>
+      <x:c r="J147" s="20"/>
+      <x:c r="K147" s="20"/>
+      <x:c r="L147" s="20"/>
+      <x:c r="M147" s="20"/>
+      <x:c r="N147" s="20"/>
+      <x:c r="O147" s="20"/>
+      <x:c r="P147" s="20"/>
+      <x:c r="Q147" s="20"/>
+      <x:c r="R147" s="20"/>
+      <x:c r="S147" s="20"/>
+      <x:c r="T147" s="20"/>
+      <x:c r="U147" s="20" t="str">
         <x:f>IF(A147="","",IF(OR(L147="Closed",L147="False positive"),"No",IF(N147="","No target set",IF(N147&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="148">
-      <x:c r="U148" t="str">
+      <x:c r="A148" s="20"/>
+      <x:c r="B148" s="20"/>
+      <x:c r="C148" s="20"/>
+      <x:c r="D148" s="20"/>
+      <x:c r="E148" s="20"/>
+      <x:c r="F148" s="20"/>
+      <x:c r="G148" s="20"/>
+      <x:c r="H148" s="20"/>
+      <x:c r="I148" s="20"/>
+      <x:c r="J148" s="20"/>
+      <x:c r="K148" s="20"/>
+      <x:c r="L148" s="20"/>
+      <x:c r="M148" s="20"/>
+      <x:c r="N148" s="20"/>
+      <x:c r="O148" s="20"/>
+      <x:c r="P148" s="20"/>
+      <x:c r="Q148" s="20"/>
+      <x:c r="R148" s="20"/>
+      <x:c r="S148" s="20"/>
+      <x:c r="T148" s="20"/>
+      <x:c r="U148" s="20" t="str">
         <x:f>IF(A148="","",IF(OR(L148="Closed",L148="False positive"),"No",IF(N148="","No target set",IF(N148&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="149">
-      <x:c r="U149" t="str">
+      <x:c r="A149" s="20"/>
+      <x:c r="B149" s="20"/>
+      <x:c r="C149" s="20"/>
+      <x:c r="D149" s="20"/>
+      <x:c r="E149" s="20"/>
+      <x:c r="F149" s="20"/>
+      <x:c r="G149" s="20"/>
+      <x:c r="H149" s="20"/>
+      <x:c r="I149" s="20"/>
+      <x:c r="J149" s="20"/>
+      <x:c r="K149" s="20"/>
+      <x:c r="L149" s="20"/>
+      <x:c r="M149" s="20"/>
+      <x:c r="N149" s="20"/>
+      <x:c r="O149" s="20"/>
+      <x:c r="P149" s="20"/>
+      <x:c r="Q149" s="20"/>
+      <x:c r="R149" s="20"/>
+      <x:c r="S149" s="20"/>
+      <x:c r="T149" s="20"/>
+      <x:c r="U149" s="20" t="str">
         <x:f>IF(A149="","",IF(OR(L149="Closed",L149="False positive"),"No",IF(N149="","No target set",IF(N149&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="150">
-      <x:c r="U150" t="str">
+      <x:c r="A150" s="20"/>
+      <x:c r="B150" s="20"/>
+      <x:c r="C150" s="20"/>
+      <x:c r="D150" s="20"/>
+      <x:c r="E150" s="20"/>
+      <x:c r="F150" s="20"/>
+      <x:c r="G150" s="20"/>
+      <x:c r="H150" s="20"/>
+      <x:c r="I150" s="20"/>
+      <x:c r="J150" s="20"/>
+      <x:c r="K150" s="20"/>
+      <x:c r="L150" s="20"/>
+      <x:c r="M150" s="20"/>
+      <x:c r="N150" s="20"/>
+      <x:c r="O150" s="20"/>
+      <x:c r="P150" s="20"/>
+      <x:c r="Q150" s="20"/>
+      <x:c r="R150" s="20"/>
+      <x:c r="S150" s="20"/>
+      <x:c r="T150" s="20"/>
+      <x:c r="U150" s="20" t="str">
         <x:f>IF(A150="","",IF(OR(L150="Closed",L150="False positive"),"No",IF(N150="","No target set",IF(N150&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="151">
-      <x:c r="U151" t="str">
+      <x:c r="A151" s="20"/>
+      <x:c r="B151" s="20"/>
+      <x:c r="C151" s="20"/>
+      <x:c r="D151" s="20"/>
+      <x:c r="E151" s="20"/>
+      <x:c r="F151" s="20"/>
+      <x:c r="G151" s="20"/>
+      <x:c r="H151" s="20"/>
+      <x:c r="I151" s="20"/>
+      <x:c r="J151" s="20"/>
+      <x:c r="K151" s="20"/>
+      <x:c r="L151" s="20"/>
+      <x:c r="M151" s="20"/>
+      <x:c r="N151" s="20"/>
+      <x:c r="O151" s="20"/>
+      <x:c r="P151" s="20"/>
+      <x:c r="Q151" s="20"/>
+      <x:c r="R151" s="20"/>
+      <x:c r="S151" s="20"/>
+      <x:c r="T151" s="20"/>
+      <x:c r="U151" s="20" t="str">
         <x:f>IF(A151="","",IF(OR(L151="Closed",L151="False positive"),"No",IF(N151="","No target set",IF(N151&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="152">
-      <x:c r="U152" t="str">
+      <x:c r="A152" s="20"/>
+      <x:c r="B152" s="20"/>
+      <x:c r="C152" s="20"/>
+      <x:c r="D152" s="20"/>
+      <x:c r="E152" s="20"/>
+      <x:c r="F152" s="20"/>
+      <x:c r="G152" s="20"/>
+      <x:c r="H152" s="20"/>
+      <x:c r="I152" s="20"/>
+      <x:c r="J152" s="20"/>
+      <x:c r="K152" s="20"/>
+      <x:c r="L152" s="20"/>
+      <x:c r="M152" s="20"/>
+      <x:c r="N152" s="20"/>
+      <x:c r="O152" s="20"/>
+      <x:c r="P152" s="20"/>
+      <x:c r="Q152" s="20"/>
+      <x:c r="R152" s="20"/>
+      <x:c r="S152" s="20"/>
+      <x:c r="T152" s="20"/>
+      <x:c r="U152" s="20" t="str">
         <x:f>IF(A152="","",IF(OR(L152="Closed",L152="False positive"),"No",IF(N152="","No target set",IF(N152&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="153">
-      <x:c r="U153" t="str">
+      <x:c r="A153" s="20"/>
+      <x:c r="B153" s="20"/>
+      <x:c r="C153" s="20"/>
+      <x:c r="D153" s="20"/>
+      <x:c r="E153" s="20"/>
+      <x:c r="F153" s="20"/>
+      <x:c r="G153" s="20"/>
+      <x:c r="H153" s="20"/>
+      <x:c r="I153" s="20"/>
+      <x:c r="J153" s="20"/>
+      <x:c r="K153" s="20"/>
+      <x:c r="L153" s="20"/>
+      <x:c r="M153" s="20"/>
+      <x:c r="N153" s="20"/>
+      <x:c r="O153" s="20"/>
+      <x:c r="P153" s="20"/>
+      <x:c r="Q153" s="20"/>
+      <x:c r="R153" s="20"/>
+      <x:c r="S153" s="20"/>
+      <x:c r="T153" s="20"/>
+      <x:c r="U153" s="20" t="str">
         <x:f>IF(A153="","",IF(OR(L153="Closed",L153="False positive"),"No",IF(N153="","No target set",IF(N153&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="154">
-      <x:c r="U154" t="str">
+      <x:c r="A154" s="20"/>
+      <x:c r="B154" s="20"/>
+      <x:c r="C154" s="20"/>
+      <x:c r="D154" s="20"/>
+      <x:c r="E154" s="20"/>
+      <x:c r="F154" s="20"/>
+      <x:c r="G154" s="20"/>
+      <x:c r="H154" s="20"/>
+      <x:c r="I154" s="20"/>
+      <x:c r="J154" s="20"/>
+      <x:c r="K154" s="20"/>
+      <x:c r="L154" s="20"/>
+      <x:c r="M154" s="20"/>
+      <x:c r="N154" s="20"/>
+      <x:c r="O154" s="20"/>
+      <x:c r="P154" s="20"/>
+      <x:c r="Q154" s="20"/>
+      <x:c r="R154" s="20"/>
+      <x:c r="S154" s="20"/>
+      <x:c r="T154" s="20"/>
+      <x:c r="U154" s="20" t="str">
         <x:f>IF(A154="","",IF(OR(L154="Closed",L154="False positive"),"No",IF(N154="","No target set",IF(N154&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="155">
-      <x:c r="U155" t="str">
+      <x:c r="A155" s="20"/>
+      <x:c r="B155" s="20"/>
+      <x:c r="C155" s="20"/>
+      <x:c r="D155" s="20"/>
+      <x:c r="E155" s="20"/>
+      <x:c r="F155" s="20"/>
+      <x:c r="G155" s="20"/>
+      <x:c r="H155" s="20"/>
+      <x:c r="I155" s="20"/>
+      <x:c r="J155" s="20"/>
+      <x:c r="K155" s="20"/>
+      <x:c r="L155" s="20"/>
+      <x:c r="M155" s="20"/>
+      <x:c r="N155" s="20"/>
+      <x:c r="O155" s="20"/>
+      <x:c r="P155" s="20"/>
+      <x:c r="Q155" s="20"/>
+      <x:c r="R155" s="20"/>
+      <x:c r="S155" s="20"/>
+      <x:c r="T155" s="20"/>
+      <x:c r="U155" s="20" t="str">
         <x:f>IF(A155="","",IF(OR(L155="Closed",L155="False positive"),"No",IF(N155="","No target set",IF(N155&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="156">
-      <x:c r="U156" t="str">
+      <x:c r="A156" s="20"/>
+      <x:c r="B156" s="20"/>
+      <x:c r="C156" s="20"/>
+      <x:c r="D156" s="20"/>
+      <x:c r="E156" s="20"/>
+      <x:c r="F156" s="20"/>
+      <x:c r="G156" s="20"/>
+      <x:c r="H156" s="20"/>
+      <x:c r="I156" s="20"/>
+      <x:c r="J156" s="20"/>
+      <x:c r="K156" s="20"/>
+      <x:c r="L156" s="20"/>
+      <x:c r="M156" s="20"/>
+      <x:c r="N156" s="20"/>
+      <x:c r="O156" s="20"/>
+      <x:c r="P156" s="20"/>
+      <x:c r="Q156" s="20"/>
+      <x:c r="R156" s="20"/>
+      <x:c r="S156" s="20"/>
+      <x:c r="T156" s="20"/>
+      <x:c r="U156" s="20" t="str">
         <x:f>IF(A156="","",IF(OR(L156="Closed",L156="False positive"),"No",IF(N156="","No target set",IF(N156&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="157">
-      <x:c r="U157" t="str">
+      <x:c r="A157" s="20"/>
+      <x:c r="B157" s="20"/>
+      <x:c r="C157" s="20"/>
+      <x:c r="D157" s="20"/>
+      <x:c r="E157" s="20"/>
+      <x:c r="F157" s="20"/>
+      <x:c r="G157" s="20"/>
+      <x:c r="H157" s="20"/>
+      <x:c r="I157" s="20"/>
+      <x:c r="J157" s="20"/>
+      <x:c r="K157" s="20"/>
+      <x:c r="L157" s="20"/>
+      <x:c r="M157" s="20"/>
+      <x:c r="N157" s="20"/>
+      <x:c r="O157" s="20"/>
+      <x:c r="P157" s="20"/>
+      <x:c r="Q157" s="20"/>
+      <x:c r="R157" s="20"/>
+      <x:c r="S157" s="20"/>
+      <x:c r="T157" s="20"/>
+      <x:c r="U157" s="20" t="str">
         <x:f>IF(A157="","",IF(OR(L157="Closed",L157="False positive"),"No",IF(N157="","No target set",IF(N157&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="158">
-      <x:c r="U158" t="str">
+      <x:c r="A158" s="20"/>
+      <x:c r="B158" s="20"/>
+      <x:c r="C158" s="20"/>
+      <x:c r="D158" s="20"/>
+      <x:c r="E158" s="20"/>
+      <x:c r="F158" s="20"/>
+      <x:c r="G158" s="20"/>
+      <x:c r="H158" s="20"/>
+      <x:c r="I158" s="20"/>
+      <x:c r="J158" s="20"/>
+      <x:c r="K158" s="20"/>
+      <x:c r="L158" s="20"/>
+      <x:c r="M158" s="20"/>
+      <x:c r="N158" s="20"/>
+      <x:c r="O158" s="20"/>
+      <x:c r="P158" s="20"/>
+      <x:c r="Q158" s="20"/>
+      <x:c r="R158" s="20"/>
+      <x:c r="S158" s="20"/>
+      <x:c r="T158" s="20"/>
+      <x:c r="U158" s="20" t="str">
         <x:f>IF(A158="","",IF(OR(L158="Closed",L158="False positive"),"No",IF(N158="","No target set",IF(N158&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="159">
-      <x:c r="U159" t="str">
+      <x:c r="A159" s="20"/>
+      <x:c r="B159" s="20"/>
+      <x:c r="C159" s="20"/>
+      <x:c r="D159" s="20"/>
+      <x:c r="E159" s="20"/>
+      <x:c r="F159" s="20"/>
+      <x:c r="G159" s="20"/>
+      <x:c r="H159" s="20"/>
+      <x:c r="I159" s="20"/>
+      <x:c r="J159" s="20"/>
+      <x:c r="K159" s="20"/>
+      <x:c r="L159" s="20"/>
+      <x:c r="M159" s="20"/>
+      <x:c r="N159" s="20"/>
+      <x:c r="O159" s="20"/>
+      <x:c r="P159" s="20"/>
+      <x:c r="Q159" s="20"/>
+      <x:c r="R159" s="20"/>
+      <x:c r="S159" s="20"/>
+      <x:c r="T159" s="20"/>
+      <x:c r="U159" s="20" t="str">
         <x:f>IF(A159="","",IF(OR(L159="Closed",L159="False positive"),"No",IF(N159="","No target set",IF(N159&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="160">
-      <x:c r="U160" t="str">
+      <x:c r="A160" s="20"/>
+      <x:c r="B160" s="20"/>
+      <x:c r="C160" s="20"/>
+      <x:c r="D160" s="20"/>
+      <x:c r="E160" s="20"/>
+      <x:c r="F160" s="20"/>
+      <x:c r="G160" s="20"/>
+      <x:c r="H160" s="20"/>
+      <x:c r="I160" s="20"/>
+      <x:c r="J160" s="20"/>
+      <x:c r="K160" s="20"/>
+      <x:c r="L160" s="20"/>
+      <x:c r="M160" s="20"/>
+      <x:c r="N160" s="20"/>
+      <x:c r="O160" s="20"/>
+      <x:c r="P160" s="20"/>
+      <x:c r="Q160" s="20"/>
+      <x:c r="R160" s="20"/>
+      <x:c r="S160" s="20"/>
+      <x:c r="T160" s="20"/>
+      <x:c r="U160" s="20" t="str">
         <x:f>IF(A160="","",IF(OR(L160="Closed",L160="False positive"),"No",IF(N160="","No target set",IF(N160&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="161">
-      <x:c r="U161" t="str">
+      <x:c r="A161" s="20"/>
+      <x:c r="B161" s="20"/>
+      <x:c r="C161" s="20"/>
+      <x:c r="D161" s="20"/>
+      <x:c r="E161" s="20"/>
+      <x:c r="F161" s="20"/>
+      <x:c r="G161" s="20"/>
+      <x:c r="H161" s="20"/>
+      <x:c r="I161" s="20"/>
+      <x:c r="J161" s="20"/>
+      <x:c r="K161" s="20"/>
+      <x:c r="L161" s="20"/>
+      <x:c r="M161" s="20"/>
+      <x:c r="N161" s="20"/>
+      <x:c r="O161" s="20"/>
+      <x:c r="P161" s="20"/>
+      <x:c r="Q161" s="20"/>
+      <x:c r="R161" s="20"/>
+      <x:c r="S161" s="20"/>
+      <x:c r="T161" s="20"/>
+      <x:c r="U161" s="20" t="str">
         <x:f>IF(A161="","",IF(OR(L161="Closed",L161="False positive"),"No",IF(N161="","No target set",IF(N161&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="162">
-      <x:c r="U162" t="str">
+      <x:c r="A162" s="20"/>
+      <x:c r="B162" s="20"/>
+      <x:c r="C162" s="20"/>
+      <x:c r="D162" s="20"/>
+      <x:c r="E162" s="20"/>
+      <x:c r="F162" s="20"/>
+      <x:c r="G162" s="20"/>
+      <x:c r="H162" s="20"/>
+      <x:c r="I162" s="20"/>
+      <x:c r="J162" s="20"/>
+      <x:c r="K162" s="20"/>
+      <x:c r="L162" s="20"/>
+      <x:c r="M162" s="20"/>
+      <x:c r="N162" s="20"/>
+      <x:c r="O162" s="20"/>
+      <x:c r="P162" s="20"/>
+      <x:c r="Q162" s="20"/>
+      <x:c r="R162" s="20"/>
+      <x:c r="S162" s="20"/>
+      <x:c r="T162" s="20"/>
+      <x:c r="U162" s="20" t="str">
         <x:f>IF(A162="","",IF(OR(L162="Closed",L162="False positive"),"No",IF(N162="","No target set",IF(N162&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="163">
-      <x:c r="U163" t="str">
+      <x:c r="A163" s="20"/>
+      <x:c r="B163" s="20"/>
+      <x:c r="C163" s="20"/>
+      <x:c r="D163" s="20"/>
+      <x:c r="E163" s="20"/>
+      <x:c r="F163" s="20"/>
+      <x:c r="G163" s="20"/>
+      <x:c r="H163" s="20"/>
+      <x:c r="I163" s="20"/>
+      <x:c r="J163" s="20"/>
+      <x:c r="K163" s="20"/>
+      <x:c r="L163" s="20"/>
+      <x:c r="M163" s="20"/>
+      <x:c r="N163" s="20"/>
+      <x:c r="O163" s="20"/>
+      <x:c r="P163" s="20"/>
+      <x:c r="Q163" s="20"/>
+      <x:c r="R163" s="20"/>
+      <x:c r="S163" s="20"/>
+      <x:c r="T163" s="20"/>
+      <x:c r="U163" s="20" t="str">
         <x:f>IF(A163="","",IF(OR(L163="Closed",L163="False positive"),"No",IF(N163="","No target set",IF(N163&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="164">
-      <x:c r="U164" t="str">
+      <x:c r="A164" s="20"/>
+      <x:c r="B164" s="20"/>
+      <x:c r="C164" s="20"/>
+      <x:c r="D164" s="20"/>
+      <x:c r="E164" s="20"/>
+      <x:c r="F164" s="20"/>
+      <x:c r="G164" s="20"/>
+      <x:c r="H164" s="20"/>
+      <x:c r="I164" s="20"/>
+      <x:c r="J164" s="20"/>
+      <x:c r="K164" s="20"/>
+      <x:c r="L164" s="20"/>
+      <x:c r="M164" s="20"/>
+      <x:c r="N164" s="20"/>
+      <x:c r="O164" s="20"/>
+      <x:c r="P164" s="20"/>
+      <x:c r="Q164" s="20"/>
+      <x:c r="R164" s="20"/>
+      <x:c r="S164" s="20"/>
+      <x:c r="T164" s="20"/>
+      <x:c r="U164" s="20" t="str">
         <x:f>IF(A164="","",IF(OR(L164="Closed",L164="False positive"),"No",IF(N164="","No target set",IF(N164&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="165">
-      <x:c r="U165" t="str">
+      <x:c r="A165" s="20"/>
+      <x:c r="B165" s="20"/>
+      <x:c r="C165" s="20"/>
+      <x:c r="D165" s="20"/>
+      <x:c r="E165" s="20"/>
+      <x:c r="F165" s="20"/>
+      <x:c r="G165" s="20"/>
+      <x:c r="H165" s="20"/>
+      <x:c r="I165" s="20"/>
+      <x:c r="J165" s="20"/>
+      <x:c r="K165" s="20"/>
+      <x:c r="L165" s="20"/>
+      <x:c r="M165" s="20"/>
+      <x:c r="N165" s="20"/>
+      <x:c r="O165" s="20"/>
+      <x:c r="P165" s="20"/>
+      <x:c r="Q165" s="20"/>
+      <x:c r="R165" s="20"/>
+      <x:c r="S165" s="20"/>
+      <x:c r="T165" s="20"/>
+      <x:c r="U165" s="20" t="str">
         <x:f>IF(A165="","",IF(OR(L165="Closed",L165="False positive"),"No",IF(N165="","No target set",IF(N165&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="166">
-      <x:c r="U166" t="str">
+      <x:c r="A166" s="20"/>
+      <x:c r="B166" s="20"/>
+      <x:c r="C166" s="20"/>
+      <x:c r="D166" s="20"/>
+      <x:c r="E166" s="20"/>
+      <x:c r="F166" s="20"/>
+      <x:c r="G166" s="20"/>
+      <x:c r="H166" s="20"/>
+      <x:c r="I166" s="20"/>
+      <x:c r="J166" s="20"/>
+      <x:c r="K166" s="20"/>
+      <x:c r="L166" s="20"/>
+      <x:c r="M166" s="20"/>
+      <x:c r="N166" s="20"/>
+      <x:c r="O166" s="20"/>
+      <x:c r="P166" s="20"/>
+      <x:c r="Q166" s="20"/>
+      <x:c r="R166" s="20"/>
+      <x:c r="S166" s="20"/>
+      <x:c r="T166" s="20"/>
+      <x:c r="U166" s="20" t="str">
         <x:f>IF(A166="","",IF(OR(L166="Closed",L166="False positive"),"No",IF(N166="","No target set",IF(N166&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="167">
-      <x:c r="U167" t="str">
+      <x:c r="A167" s="20"/>
+      <x:c r="B167" s="20"/>
+      <x:c r="C167" s="20"/>
+      <x:c r="D167" s="20"/>
+      <x:c r="E167" s="20"/>
+      <x:c r="F167" s="20"/>
+      <x:c r="G167" s="20"/>
+      <x:c r="H167" s="20"/>
+      <x:c r="I167" s="20"/>
+      <x:c r="J167" s="20"/>
+      <x:c r="K167" s="20"/>
+      <x:c r="L167" s="20"/>
+      <x:c r="M167" s="20"/>
+      <x:c r="N167" s="20"/>
+      <x:c r="O167" s="20"/>
+      <x:c r="P167" s="20"/>
+      <x:c r="Q167" s="20"/>
+      <x:c r="R167" s="20"/>
+      <x:c r="S167" s="20"/>
+      <x:c r="T167" s="20"/>
+      <x:c r="U167" s="20" t="str">
         <x:f>IF(A167="","",IF(OR(L167="Closed",L167="False positive"),"No",IF(N167="","No target set",IF(N167&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="168">
-      <x:c r="U168" t="str">
+      <x:c r="A168" s="20"/>
+      <x:c r="B168" s="20"/>
+      <x:c r="C168" s="20"/>
+      <x:c r="D168" s="20"/>
+      <x:c r="E168" s="20"/>
+      <x:c r="F168" s="20"/>
+      <x:c r="G168" s="20"/>
+      <x:c r="H168" s="20"/>
+      <x:c r="I168" s="20"/>
+      <x:c r="J168" s="20"/>
+      <x:c r="K168" s="20"/>
+      <x:c r="L168" s="20"/>
+      <x:c r="M168" s="20"/>
+      <x:c r="N168" s="20"/>
+      <x:c r="O168" s="20"/>
+      <x:c r="P168" s="20"/>
+      <x:c r="Q168" s="20"/>
+      <x:c r="R168" s="20"/>
+      <x:c r="S168" s="20"/>
+      <x:c r="T168" s="20"/>
+      <x:c r="U168" s="20" t="str">
         <x:f>IF(A168="","",IF(OR(L168="Closed",L168="False positive"),"No",IF(N168="","No target set",IF(N168&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="169">
-      <x:c r="U169" t="str">
+      <x:c r="A169" s="20"/>
+      <x:c r="B169" s="20"/>
+      <x:c r="C169" s="20"/>
+      <x:c r="D169" s="20"/>
+      <x:c r="E169" s="20"/>
+      <x:c r="F169" s="20"/>
+      <x:c r="G169" s="20"/>
+      <x:c r="H169" s="20"/>
+      <x:c r="I169" s="20"/>
+      <x:c r="J169" s="20"/>
+      <x:c r="K169" s="20"/>
+      <x:c r="L169" s="20"/>
+      <x:c r="M169" s="20"/>
+      <x:c r="N169" s="20"/>
+      <x:c r="O169" s="20"/>
+      <x:c r="P169" s="20"/>
+      <x:c r="Q169" s="20"/>
+      <x:c r="R169" s="20"/>
+      <x:c r="S169" s="20"/>
+      <x:c r="T169" s="20"/>
+      <x:c r="U169" s="20" t="str">
         <x:f>IF(A169="","",IF(OR(L169="Closed",L169="False positive"),"No",IF(N169="","No target set",IF(N169&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="170">
-      <x:c r="U170" t="str">
+      <x:c r="A170" s="20"/>
+      <x:c r="B170" s="20"/>
+      <x:c r="C170" s="20"/>
+      <x:c r="D170" s="20"/>
+      <x:c r="E170" s="20"/>
+      <x:c r="F170" s="20"/>
+      <x:c r="G170" s="20"/>
+      <x:c r="H170" s="20"/>
+      <x:c r="I170" s="20"/>
+      <x:c r="J170" s="20"/>
+      <x:c r="K170" s="20"/>
+      <x:c r="L170" s="20"/>
+      <x:c r="M170" s="20"/>
+      <x:c r="N170" s="20"/>
+      <x:c r="O170" s="20"/>
+      <x:c r="P170" s="20"/>
+      <x:c r="Q170" s="20"/>
+      <x:c r="R170" s="20"/>
+      <x:c r="S170" s="20"/>
+      <x:c r="T170" s="20"/>
+      <x:c r="U170" s="20" t="str">
         <x:f>IF(A170="","",IF(OR(L170="Closed",L170="False positive"),"No",IF(N170="","No target set",IF(N170&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="171">
-      <x:c r="U171" t="str">
+      <x:c r="A171" s="20"/>
+      <x:c r="B171" s="20"/>
+      <x:c r="C171" s="20"/>
+      <x:c r="D171" s="20"/>
+      <x:c r="E171" s="20"/>
+      <x:c r="F171" s="20"/>
+      <x:c r="G171" s="20"/>
+      <x:c r="H171" s="20"/>
+      <x:c r="I171" s="20"/>
+      <x:c r="J171" s="20"/>
+      <x:c r="K171" s="20"/>
+      <x:c r="L171" s="20"/>
+      <x:c r="M171" s="20"/>
+      <x:c r="N171" s="20"/>
+      <x:c r="O171" s="20"/>
+      <x:c r="P171" s="20"/>
+      <x:c r="Q171" s="20"/>
+      <x:c r="R171" s="20"/>
+      <x:c r="S171" s="20"/>
+      <x:c r="T171" s="20"/>
+      <x:c r="U171" s="20" t="str">
         <x:f>IF(A171="","",IF(OR(L171="Closed",L171="False positive"),"No",IF(N171="","No target set",IF(N171&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="172">
-      <x:c r="U172" t="str">
+      <x:c r="A172" s="20"/>
+      <x:c r="B172" s="20"/>
+      <x:c r="C172" s="20"/>
+      <x:c r="D172" s="20"/>
+      <x:c r="E172" s="20"/>
+      <x:c r="F172" s="20"/>
+      <x:c r="G172" s="20"/>
+      <x:c r="H172" s="20"/>
+      <x:c r="I172" s="20"/>
+      <x:c r="J172" s="20"/>
+      <x:c r="K172" s="20"/>
+      <x:c r="L172" s="20"/>
+      <x:c r="M172" s="20"/>
+      <x:c r="N172" s="20"/>
+      <x:c r="O172" s="20"/>
+      <x:c r="P172" s="20"/>
+      <x:c r="Q172" s="20"/>
+      <x:c r="R172" s="20"/>
+      <x:c r="S172" s="20"/>
+      <x:c r="T172" s="20"/>
+      <x:c r="U172" s="20" t="str">
         <x:f>IF(A172="","",IF(OR(L172="Closed",L172="False positive"),"No",IF(N172="","No target set",IF(N172&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="173">
-      <x:c r="U173" t="str">
+      <x:c r="A173" s="20"/>
+      <x:c r="B173" s="20"/>
+      <x:c r="C173" s="20"/>
+      <x:c r="D173" s="20"/>
+      <x:c r="E173" s="20"/>
+      <x:c r="F173" s="20"/>
+      <x:c r="G173" s="20"/>
+      <x:c r="H173" s="20"/>
+      <x:c r="I173" s="20"/>
+      <x:c r="J173" s="20"/>
+      <x:c r="K173" s="20"/>
+      <x:c r="L173" s="20"/>
+      <x:c r="M173" s="20"/>
+      <x:c r="N173" s="20"/>
+      <x:c r="O173" s="20"/>
+      <x:c r="P173" s="20"/>
+      <x:c r="Q173" s="20"/>
+      <x:c r="R173" s="20"/>
+      <x:c r="S173" s="20"/>
+      <x:c r="T173" s="20"/>
+      <x:c r="U173" s="20" t="str">
         <x:f>IF(A173="","",IF(OR(L173="Closed",L173="False positive"),"No",IF(N173="","No target set",IF(N173&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="174">
-      <x:c r="U174" t="str">
+      <x:c r="A174" s="20"/>
+      <x:c r="B174" s="20"/>
+      <x:c r="C174" s="20"/>
+      <x:c r="D174" s="20"/>
+      <x:c r="E174" s="20"/>
+      <x:c r="F174" s="20"/>
+      <x:c r="G174" s="20"/>
+      <x:c r="H174" s="20"/>
+      <x:c r="I174" s="20"/>
+      <x:c r="J174" s="20"/>
+      <x:c r="K174" s="20"/>
+      <x:c r="L174" s="20"/>
+      <x:c r="M174" s="20"/>
+      <x:c r="N174" s="20"/>
+      <x:c r="O174" s="20"/>
+      <x:c r="P174" s="20"/>
+      <x:c r="Q174" s="20"/>
+      <x:c r="R174" s="20"/>
+      <x:c r="S174" s="20"/>
+      <x:c r="T174" s="20"/>
+      <x:c r="U174" s="20" t="str">
         <x:f>IF(A174="","",IF(OR(L174="Closed",L174="False positive"),"No",IF(N174="","No target set",IF(N174&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="175">
-      <x:c r="U175" t="str">
+      <x:c r="A175" s="20"/>
+      <x:c r="B175" s="20"/>
+      <x:c r="C175" s="20"/>
+      <x:c r="D175" s="20"/>
+      <x:c r="E175" s="20"/>
+      <x:c r="F175" s="20"/>
+      <x:c r="G175" s="20"/>
+      <x:c r="H175" s="20"/>
+      <x:c r="I175" s="20"/>
+      <x:c r="J175" s="20"/>
+      <x:c r="K175" s="20"/>
+      <x:c r="L175" s="20"/>
+      <x:c r="M175" s="20"/>
+      <x:c r="N175" s="20"/>
+      <x:c r="O175" s="20"/>
+      <x:c r="P175" s="20"/>
+      <x:c r="Q175" s="20"/>
+      <x:c r="R175" s="20"/>
+      <x:c r="S175" s="20"/>
+      <x:c r="T175" s="20"/>
+      <x:c r="U175" s="20" t="str">
         <x:f>IF(A175="","",IF(OR(L175="Closed",L175="False positive"),"No",IF(N175="","No target set",IF(N175&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="176">
-      <x:c r="U176" t="str">
+      <x:c r="A176" s="20"/>
+      <x:c r="B176" s="20"/>
+      <x:c r="C176" s="20"/>
+      <x:c r="D176" s="20"/>
+      <x:c r="E176" s="20"/>
+      <x:c r="F176" s="20"/>
+      <x:c r="G176" s="20"/>
+      <x:c r="H176" s="20"/>
+      <x:c r="I176" s="20"/>
+      <x:c r="J176" s="20"/>
+      <x:c r="K176" s="20"/>
+      <x:c r="L176" s="20"/>
+      <x:c r="M176" s="20"/>
+      <x:c r="N176" s="20"/>
+      <x:c r="O176" s="20"/>
+      <x:c r="P176" s="20"/>
+      <x:c r="Q176" s="20"/>
+      <x:c r="R176" s="20"/>
+      <x:c r="S176" s="20"/>
+      <x:c r="T176" s="20"/>
+      <x:c r="U176" s="20" t="str">
         <x:f>IF(A176="","",IF(OR(L176="Closed",L176="False positive"),"No",IF(N176="","No target set",IF(N176&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="177">
-      <x:c r="U177" t="str">
+      <x:c r="A177" s="20"/>
+      <x:c r="B177" s="20"/>
+      <x:c r="C177" s="20"/>
+      <x:c r="D177" s="20"/>
+      <x:c r="E177" s="20"/>
+      <x:c r="F177" s="20"/>
+      <x:c r="G177" s="20"/>
+      <x:c r="H177" s="20"/>
+      <x:c r="I177" s="20"/>
+      <x:c r="J177" s="20"/>
+      <x:c r="K177" s="20"/>
+      <x:c r="L177" s="20"/>
+      <x:c r="M177" s="20"/>
+      <x:c r="N177" s="20"/>
+      <x:c r="O177" s="20"/>
+      <x:c r="P177" s="20"/>
+      <x:c r="Q177" s="20"/>
+      <x:c r="R177" s="20"/>
+      <x:c r="S177" s="20"/>
+      <x:c r="T177" s="20"/>
+      <x:c r="U177" s="20" t="str">
         <x:f>IF(A177="","",IF(OR(L177="Closed",L177="False positive"),"No",IF(N177="","No target set",IF(N177&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="178">
-      <x:c r="U178" t="str">
+      <x:c r="A178" s="20"/>
+      <x:c r="B178" s="20"/>
+      <x:c r="C178" s="20"/>
+      <x:c r="D178" s="20"/>
+      <x:c r="E178" s="20"/>
+      <x:c r="F178" s="20"/>
+      <x:c r="G178" s="20"/>
+      <x:c r="H178" s="20"/>
+      <x:c r="I178" s="20"/>
+      <x:c r="J178" s="20"/>
+      <x:c r="K178" s="20"/>
+      <x:c r="L178" s="20"/>
+      <x:c r="M178" s="20"/>
+      <x:c r="N178" s="20"/>
+      <x:c r="O178" s="20"/>
+      <x:c r="P178" s="20"/>
+      <x:c r="Q178" s="20"/>
+      <x:c r="R178" s="20"/>
+      <x:c r="S178" s="20"/>
+      <x:c r="T178" s="20"/>
+      <x:c r="U178" s="20" t="str">
         <x:f>IF(A178="","",IF(OR(L178="Closed",L178="False positive"),"No",IF(N178="","No target set",IF(N178&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="179">
-      <x:c r="U179" t="str">
+      <x:c r="A179" s="20"/>
+      <x:c r="B179" s="20"/>
+      <x:c r="C179" s="20"/>
+      <x:c r="D179" s="20"/>
+      <x:c r="E179" s="20"/>
+      <x:c r="F179" s="20"/>
+      <x:c r="G179" s="20"/>
+      <x:c r="H179" s="20"/>
+      <x:c r="I179" s="20"/>
+      <x:c r="J179" s="20"/>
+      <x:c r="K179" s="20"/>
+      <x:c r="L179" s="20"/>
+      <x:c r="M179" s="20"/>
+      <x:c r="N179" s="20"/>
+      <x:c r="O179" s="20"/>
+      <x:c r="P179" s="20"/>
+      <x:c r="Q179" s="20"/>
+      <x:c r="R179" s="20"/>
+      <x:c r="S179" s="20"/>
+      <x:c r="T179" s="20"/>
+      <x:c r="U179" s="20" t="str">
         <x:f>IF(A179="","",IF(OR(L179="Closed",L179="False positive"),"No",IF(N179="","No target set",IF(N179&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="180">
-      <x:c r="U180" t="str">
+      <x:c r="A180" s="20"/>
+      <x:c r="B180" s="20"/>
+      <x:c r="C180" s="20"/>
+      <x:c r="D180" s="20"/>
+      <x:c r="E180" s="20"/>
+      <x:c r="F180" s="20"/>
+      <x:c r="G180" s="20"/>
+      <x:c r="H180" s="20"/>
+      <x:c r="I180" s="20"/>
+      <x:c r="J180" s="20"/>
+      <x:c r="K180" s="20"/>
+      <x:c r="L180" s="20"/>
+      <x:c r="M180" s="20"/>
+      <x:c r="N180" s="20"/>
+      <x:c r="O180" s="20"/>
+      <x:c r="P180" s="20"/>
+      <x:c r="Q180" s="20"/>
+      <x:c r="R180" s="20"/>
+      <x:c r="S180" s="20"/>
+      <x:c r="T180" s="20"/>
+      <x:c r="U180" s="20" t="str">
         <x:f>IF(A180="","",IF(OR(L180="Closed",L180="False positive"),"No",IF(N180="","No target set",IF(N180&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="181">
-      <x:c r="U181" t="str">
+      <x:c r="A181" s="20"/>
+      <x:c r="B181" s="20"/>
+      <x:c r="C181" s="20"/>
+      <x:c r="D181" s="20"/>
+      <x:c r="E181" s="20"/>
+      <x:c r="F181" s="20"/>
+      <x:c r="G181" s="20"/>
+      <x:c r="H181" s="20"/>
+      <x:c r="I181" s="20"/>
+      <x:c r="J181" s="20"/>
+      <x:c r="K181" s="20"/>
+      <x:c r="L181" s="20"/>
+      <x:c r="M181" s="20"/>
+      <x:c r="N181" s="20"/>
+      <x:c r="O181" s="20"/>
+      <x:c r="P181" s="20"/>
+      <x:c r="Q181" s="20"/>
+      <x:c r="R181" s="20"/>
+      <x:c r="S181" s="20"/>
+      <x:c r="T181" s="20"/>
+      <x:c r="U181" s="20" t="str">
         <x:f>IF(A181="","",IF(OR(L181="Closed",L181="False positive"),"No",IF(N181="","No target set",IF(N181&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="182">
-      <x:c r="U182" t="str">
+      <x:c r="A182" s="20"/>
+      <x:c r="B182" s="20"/>
+      <x:c r="C182" s="20"/>
+      <x:c r="D182" s="20"/>
+      <x:c r="E182" s="20"/>
+      <x:c r="F182" s="20"/>
+      <x:c r="G182" s="20"/>
+      <x:c r="H182" s="20"/>
+      <x:c r="I182" s="20"/>
+      <x:c r="J182" s="20"/>
+      <x:c r="K182" s="20"/>
+      <x:c r="L182" s="20"/>
+      <x:c r="M182" s="20"/>
+      <x:c r="N182" s="20"/>
+      <x:c r="O182" s="20"/>
+      <x:c r="P182" s="20"/>
+      <x:c r="Q182" s="20"/>
+      <x:c r="R182" s="20"/>
+      <x:c r="S182" s="20"/>
+      <x:c r="T182" s="20"/>
+      <x:c r="U182" s="20" t="str">
         <x:f>IF(A182="","",IF(OR(L182="Closed",L182="False positive"),"No",IF(N182="","No target set",IF(N182&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="183">
-      <x:c r="U183" t="str">
+      <x:c r="A183" s="20"/>
+      <x:c r="B183" s="20"/>
+      <x:c r="C183" s="20"/>
+      <x:c r="D183" s="20"/>
+      <x:c r="E183" s="20"/>
+      <x:c r="F183" s="20"/>
+      <x:c r="G183" s="20"/>
+      <x:c r="H183" s="20"/>
+      <x:c r="I183" s="20"/>
+      <x:c r="J183" s="20"/>
+      <x:c r="K183" s="20"/>
+      <x:c r="L183" s="20"/>
+      <x:c r="M183" s="20"/>
+      <x:c r="N183" s="20"/>
+      <x:c r="O183" s="20"/>
+      <x:c r="P183" s="20"/>
+      <x:c r="Q183" s="20"/>
+      <x:c r="R183" s="20"/>
+      <x:c r="S183" s="20"/>
+      <x:c r="T183" s="20"/>
+      <x:c r="U183" s="20" t="str">
         <x:f>IF(A183="","",IF(OR(L183="Closed",L183="False positive"),"No",IF(N183="","No target set",IF(N183&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="184">
-      <x:c r="U184" t="str">
+      <x:c r="A184" s="20"/>
+      <x:c r="B184" s="20"/>
+      <x:c r="C184" s="20"/>
+      <x:c r="D184" s="20"/>
+      <x:c r="E184" s="20"/>
+      <x:c r="F184" s="20"/>
+      <x:c r="G184" s="20"/>
+      <x:c r="H184" s="20"/>
+      <x:c r="I184" s="20"/>
+      <x:c r="J184" s="20"/>
+      <x:c r="K184" s="20"/>
+      <x:c r="L184" s="20"/>
+      <x:c r="M184" s="20"/>
+      <x:c r="N184" s="20"/>
+      <x:c r="O184" s="20"/>
+      <x:c r="P184" s="20"/>
+      <x:c r="Q184" s="20"/>
+      <x:c r="R184" s="20"/>
+      <x:c r="S184" s="20"/>
+      <x:c r="T184" s="20"/>
+      <x:c r="U184" s="20" t="str">
         <x:f>IF(A184="","",IF(OR(L184="Closed",L184="False positive"),"No",IF(N184="","No target set",IF(N184&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="185">
-      <x:c r="U185" t="str">
+      <x:c r="A185" s="20"/>
+      <x:c r="B185" s="20"/>
+      <x:c r="C185" s="20"/>
+      <x:c r="D185" s="20"/>
+      <x:c r="E185" s="20"/>
+      <x:c r="F185" s="20"/>
+      <x:c r="G185" s="20"/>
+      <x:c r="H185" s="20"/>
+      <x:c r="I185" s="20"/>
+      <x:c r="J185" s="20"/>
+      <x:c r="K185" s="20"/>
+      <x:c r="L185" s="20"/>
+      <x:c r="M185" s="20"/>
+      <x:c r="N185" s="20"/>
+      <x:c r="O185" s="20"/>
+      <x:c r="P185" s="20"/>
+      <x:c r="Q185" s="20"/>
+      <x:c r="R185" s="20"/>
+      <x:c r="S185" s="20"/>
+      <x:c r="T185" s="20"/>
+      <x:c r="U185" s="20" t="str">
         <x:f>IF(A185="","",IF(OR(L185="Closed",L185="False positive"),"No",IF(N185="","No target set",IF(N185&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="186">
-      <x:c r="U186" t="str">
+      <x:c r="A186" s="20"/>
+      <x:c r="B186" s="20"/>
+      <x:c r="C186" s="20"/>
+      <x:c r="D186" s="20"/>
+      <x:c r="E186" s="20"/>
+      <x:c r="F186" s="20"/>
+      <x:c r="G186" s="20"/>
+      <x:c r="H186" s="20"/>
+      <x:c r="I186" s="20"/>
+      <x:c r="J186" s="20"/>
+      <x:c r="K186" s="20"/>
+      <x:c r="L186" s="20"/>
+      <x:c r="M186" s="20"/>
+      <x:c r="N186" s="20"/>
+      <x:c r="O186" s="20"/>
+      <x:c r="P186" s="20"/>
+      <x:c r="Q186" s="20"/>
+      <x:c r="R186" s="20"/>
+      <x:c r="S186" s="20"/>
+      <x:c r="T186" s="20"/>
+      <x:c r="U186" s="20" t="str">
         <x:f>IF(A186="","",IF(OR(L186="Closed",L186="False positive"),"No",IF(N186="","No target set",IF(N186&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="187">
-      <x:c r="U187" t="str">
+      <x:c r="A187" s="20"/>
+      <x:c r="B187" s="20"/>
+      <x:c r="C187" s="20"/>
+      <x:c r="D187" s="20"/>
+      <x:c r="E187" s="20"/>
+      <x:c r="F187" s="20"/>
+      <x:c r="G187" s="20"/>
+      <x:c r="H187" s="20"/>
+      <x:c r="I187" s="20"/>
+      <x:c r="J187" s="20"/>
+      <x:c r="K187" s="20"/>
+      <x:c r="L187" s="20"/>
+      <x:c r="M187" s="20"/>
+      <x:c r="N187" s="20"/>
+      <x:c r="O187" s="20"/>
+      <x:c r="P187" s="20"/>
+      <x:c r="Q187" s="20"/>
+      <x:c r="R187" s="20"/>
+      <x:c r="S187" s="20"/>
+      <x:c r="T187" s="20"/>
+      <x:c r="U187" s="20" t="str">
         <x:f>IF(A187="","",IF(OR(L187="Closed",L187="False positive"),"No",IF(N187="","No target set",IF(N187&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="188">
-      <x:c r="U188" t="str">
+      <x:c r="A188" s="20"/>
+      <x:c r="B188" s="20"/>
+      <x:c r="C188" s="20"/>
+      <x:c r="D188" s="20"/>
+      <x:c r="E188" s="20"/>
+      <x:c r="F188" s="20"/>
+      <x:c r="G188" s="20"/>
+      <x:c r="H188" s="20"/>
+      <x:c r="I188" s="20"/>
+      <x:c r="J188" s="20"/>
+      <x:c r="K188" s="20"/>
+      <x:c r="L188" s="20"/>
+      <x:c r="M188" s="20"/>
+      <x:c r="N188" s="20"/>
+      <x:c r="O188" s="20"/>
+      <x:c r="P188" s="20"/>
+      <x:c r="Q188" s="20"/>
+      <x:c r="R188" s="20"/>
+      <x:c r="S188" s="20"/>
+      <x:c r="T188" s="20"/>
+      <x:c r="U188" s="20" t="str">
         <x:f>IF(A188="","",IF(OR(L188="Closed",L188="False positive"),"No",IF(N188="","No target set",IF(N188&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="189">
-      <x:c r="U189" t="str">
+      <x:c r="A189" s="20"/>
+      <x:c r="B189" s="20"/>
+      <x:c r="C189" s="20"/>
+      <x:c r="D189" s="20"/>
+      <x:c r="E189" s="20"/>
+      <x:c r="F189" s="20"/>
+      <x:c r="G189" s="20"/>
+      <x:c r="H189" s="20"/>
+      <x:c r="I189" s="20"/>
+      <x:c r="J189" s="20"/>
+      <x:c r="K189" s="20"/>
+      <x:c r="L189" s="20"/>
+      <x:c r="M189" s="20"/>
+      <x:c r="N189" s="20"/>
+      <x:c r="O189" s="20"/>
+      <x:c r="P189" s="20"/>
+      <x:c r="Q189" s="20"/>
+      <x:c r="R189" s="20"/>
+      <x:c r="S189" s="20"/>
+      <x:c r="T189" s="20"/>
+      <x:c r="U189" s="20" t="str">
         <x:f>IF(A189="","",IF(OR(L189="Closed",L189="False positive"),"No",IF(N189="","No target set",IF(N189&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="190">
-      <x:c r="U190" t="str">
+      <x:c r="A190" s="20"/>
+      <x:c r="B190" s="20"/>
+      <x:c r="C190" s="20"/>
+      <x:c r="D190" s="20"/>
+      <x:c r="E190" s="20"/>
+      <x:c r="F190" s="20"/>
+      <x:c r="G190" s="20"/>
+      <x:c r="H190" s="20"/>
+      <x:c r="I190" s="20"/>
+      <x:c r="J190" s="20"/>
+      <x:c r="K190" s="20"/>
+      <x:c r="L190" s="20"/>
+      <x:c r="M190" s="20"/>
+      <x:c r="N190" s="20"/>
+      <x:c r="O190" s="20"/>
+      <x:c r="P190" s="20"/>
+      <x:c r="Q190" s="20"/>
+      <x:c r="R190" s="20"/>
+      <x:c r="S190" s="20"/>
+      <x:c r="T190" s="20"/>
+      <x:c r="U190" s="20" t="str">
         <x:f>IF(A190="","",IF(OR(L190="Closed",L190="False positive"),"No",IF(N190="","No target set",IF(N190&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="191">
-      <x:c r="U191" t="str">
+      <x:c r="A191" s="20"/>
+      <x:c r="B191" s="20"/>
+      <x:c r="C191" s="20"/>
+      <x:c r="D191" s="20"/>
+      <x:c r="E191" s="20"/>
+      <x:c r="F191" s="20"/>
+      <x:c r="G191" s="20"/>
+      <x:c r="H191" s="20"/>
+      <x:c r="I191" s="20"/>
+      <x:c r="J191" s="20"/>
+      <x:c r="K191" s="20"/>
+      <x:c r="L191" s="20"/>
+      <x:c r="M191" s="20"/>
+      <x:c r="N191" s="20"/>
+      <x:c r="O191" s="20"/>
+      <x:c r="P191" s="20"/>
+      <x:c r="Q191" s="20"/>
+      <x:c r="R191" s="20"/>
+      <x:c r="S191" s="20"/>
+      <x:c r="T191" s="20"/>
+      <x:c r="U191" s="20" t="str">
         <x:f>IF(A191="","",IF(OR(L191="Closed",L191="False positive"),"No",IF(N191="","No target set",IF(N191&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="192">
-      <x:c r="U192" t="str">
+      <x:c r="A192" s="20"/>
+      <x:c r="B192" s="20"/>
+      <x:c r="C192" s="20"/>
+      <x:c r="D192" s="20"/>
+      <x:c r="E192" s="20"/>
+      <x:c r="F192" s="20"/>
+      <x:c r="G192" s="20"/>
+      <x:c r="H192" s="20"/>
+      <x:c r="I192" s="20"/>
+      <x:c r="J192" s="20"/>
+      <x:c r="K192" s="20"/>
+      <x:c r="L192" s="20"/>
+      <x:c r="M192" s="20"/>
+      <x:c r="N192" s="20"/>
+      <x:c r="O192" s="20"/>
+      <x:c r="P192" s="20"/>
+      <x:c r="Q192" s="20"/>
+      <x:c r="R192" s="20"/>
+      <x:c r="S192" s="20"/>
+      <x:c r="T192" s="20"/>
+      <x:c r="U192" s="20" t="str">
         <x:f>IF(A192="","",IF(OR(L192="Closed",L192="False positive"),"No",IF(N192="","No target set",IF(N192&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="193">
-      <x:c r="U193" t="str">
+      <x:c r="A193" s="20"/>
+      <x:c r="B193" s="20"/>
+      <x:c r="C193" s="20"/>
+      <x:c r="D193" s="20"/>
+      <x:c r="E193" s="20"/>
+      <x:c r="F193" s="20"/>
+      <x:c r="G193" s="20"/>
+      <x:c r="H193" s="20"/>
+      <x:c r="I193" s="20"/>
+      <x:c r="J193" s="20"/>
+      <x:c r="K193" s="20"/>
+      <x:c r="L193" s="20"/>
+      <x:c r="M193" s="20"/>
+      <x:c r="N193" s="20"/>
+      <x:c r="O193" s="20"/>
+      <x:c r="P193" s="20"/>
+      <x:c r="Q193" s="20"/>
+      <x:c r="R193" s="20"/>
+      <x:c r="S193" s="20"/>
+      <x:c r="T193" s="20"/>
+      <x:c r="U193" s="20" t="str">
         <x:f>IF(A193="","",IF(OR(L193="Closed",L193="False positive"),"No",IF(N193="","No target set",IF(N193&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="194">
-      <x:c r="U194" t="str">
+      <x:c r="A194" s="20"/>
+      <x:c r="B194" s="20"/>
+      <x:c r="C194" s="20"/>
+      <x:c r="D194" s="20"/>
+      <x:c r="E194" s="20"/>
+      <x:c r="F194" s="20"/>
+      <x:c r="G194" s="20"/>
+      <x:c r="H194" s="20"/>
+      <x:c r="I194" s="20"/>
+      <x:c r="J194" s="20"/>
+      <x:c r="K194" s="20"/>
+      <x:c r="L194" s="20"/>
+      <x:c r="M194" s="20"/>
+      <x:c r="N194" s="20"/>
+      <x:c r="O194" s="20"/>
+      <x:c r="P194" s="20"/>
+      <x:c r="Q194" s="20"/>
+      <x:c r="R194" s="20"/>
+      <x:c r="S194" s="20"/>
+      <x:c r="T194" s="20"/>
+      <x:c r="U194" s="20" t="str">
         <x:f>IF(A194="","",IF(OR(L194="Closed",L194="False positive"),"No",IF(N194="","No target set",IF(N194&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="195">
-      <x:c r="U195" t="str">
+      <x:c r="A195" s="20"/>
+      <x:c r="B195" s="20"/>
+      <x:c r="C195" s="20"/>
+      <x:c r="D195" s="20"/>
+      <x:c r="E195" s="20"/>
+      <x:c r="F195" s="20"/>
+      <x:c r="G195" s="20"/>
+      <x:c r="H195" s="20"/>
+      <x:c r="I195" s="20"/>
+      <x:c r="J195" s="20"/>
+      <x:c r="K195" s="20"/>
+      <x:c r="L195" s="20"/>
+      <x:c r="M195" s="20"/>
+      <x:c r="N195" s="20"/>
+      <x:c r="O195" s="20"/>
+      <x:c r="P195" s="20"/>
+      <x:c r="Q195" s="20"/>
+      <x:c r="R195" s="20"/>
+      <x:c r="S195" s="20"/>
+      <x:c r="T195" s="20"/>
+      <x:c r="U195" s="20" t="str">
         <x:f>IF(A195="","",IF(OR(L195="Closed",L195="False positive"),"No",IF(N195="","No target set",IF(N195&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="196">
-      <x:c r="U196" t="str">
+      <x:c r="A196" s="20"/>
+      <x:c r="B196" s="20"/>
+      <x:c r="C196" s="20"/>
+      <x:c r="D196" s="20"/>
+      <x:c r="E196" s="20"/>
+      <x:c r="F196" s="20"/>
+      <x:c r="G196" s="20"/>
+      <x:c r="H196" s="20"/>
+      <x:c r="I196" s="20"/>
+      <x:c r="J196" s="20"/>
+      <x:c r="K196" s="20"/>
+      <x:c r="L196" s="20"/>
+      <x:c r="M196" s="20"/>
+      <x:c r="N196" s="20"/>
+      <x:c r="O196" s="20"/>
+      <x:c r="P196" s="20"/>
+      <x:c r="Q196" s="20"/>
+      <x:c r="R196" s="20"/>
+      <x:c r="S196" s="20"/>
+      <x:c r="T196" s="20"/>
+      <x:c r="U196" s="20" t="str">
         <x:f>IF(A196="","",IF(OR(L196="Closed",L196="False positive"),"No",IF(N196="","No target set",IF(N196&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="197">
-      <x:c r="U197" t="str">
+      <x:c r="A197" s="20"/>
+      <x:c r="B197" s="20"/>
+      <x:c r="C197" s="20"/>
+      <x:c r="D197" s="20"/>
+      <x:c r="E197" s="20"/>
+      <x:c r="F197" s="20"/>
+      <x:c r="G197" s="20"/>
+      <x:c r="H197" s="20"/>
+      <x:c r="I197" s="20"/>
+      <x:c r="J197" s="20"/>
+      <x:c r="K197" s="20"/>
+      <x:c r="L197" s="20"/>
+      <x:c r="M197" s="20"/>
+      <x:c r="N197" s="20"/>
+      <x:c r="O197" s="20"/>
+      <x:c r="P197" s="20"/>
+      <x:c r="Q197" s="20"/>
+      <x:c r="R197" s="20"/>
+      <x:c r="S197" s="20"/>
+      <x:c r="T197" s="20"/>
+      <x:c r="U197" s="20" t="str">
         <x:f>IF(A197="","",IF(OR(L197="Closed",L197="False positive"),"No",IF(N197="","No target set",IF(N197&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="198">
-      <x:c r="U198" t="str">
+      <x:c r="A198" s="20"/>
+      <x:c r="B198" s="20"/>
+      <x:c r="C198" s="20"/>
+      <x:c r="D198" s="20"/>
+      <x:c r="E198" s="20"/>
+      <x:c r="F198" s="20"/>
+      <x:c r="G198" s="20"/>
+      <x:c r="H198" s="20"/>
+      <x:c r="I198" s="20"/>
+      <x:c r="J198" s="20"/>
+      <x:c r="K198" s="20"/>
+      <x:c r="L198" s="20"/>
+      <x:c r="M198" s="20"/>
+      <x:c r="N198" s="20"/>
+      <x:c r="O198" s="20"/>
+      <x:c r="P198" s="20"/>
+      <x:c r="Q198" s="20"/>
+      <x:c r="R198" s="20"/>
+      <x:c r="S198" s="20"/>
+      <x:c r="T198" s="20"/>
+      <x:c r="U198" s="20" t="str">
         <x:f>IF(A198="","",IF(OR(L198="Closed",L198="False positive"),"No",IF(N198="","No target set",IF(N198&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="199">
-      <x:c r="U199" t="str">
+      <x:c r="A199" s="20"/>
+      <x:c r="B199" s="20"/>
+      <x:c r="C199" s="20"/>
+      <x:c r="D199" s="20"/>
+      <x:c r="E199" s="20"/>
+      <x:c r="F199" s="20"/>
+      <x:c r="G199" s="20"/>
+      <x:c r="H199" s="20"/>
+      <x:c r="I199" s="20"/>
+      <x:c r="J199" s="20"/>
+      <x:c r="K199" s="20"/>
+      <x:c r="L199" s="20"/>
+      <x:c r="M199" s="20"/>
+      <x:c r="N199" s="20"/>
+      <x:c r="O199" s="20"/>
+      <x:c r="P199" s="20"/>
+      <x:c r="Q199" s="20"/>
+      <x:c r="R199" s="20"/>
+      <x:c r="S199" s="20"/>
+      <x:c r="T199" s="20"/>
+      <x:c r="U199" s="20" t="str">
         <x:f>IF(A199="","",IF(OR(L199="Closed",L199="False positive"),"No",IF(N199="","No target set",IF(N199&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="200">
-      <x:c r="U200" t="str">
+      <x:c r="A200" s="20"/>
+      <x:c r="B200" s="20"/>
+      <x:c r="C200" s="20"/>
+      <x:c r="D200" s="20"/>
+      <x:c r="E200" s="20"/>
+      <x:c r="F200" s="20"/>
+      <x:c r="G200" s="20"/>
+      <x:c r="H200" s="20"/>
+      <x:c r="I200" s="20"/>
+      <x:c r="J200" s="20"/>
+      <x:c r="K200" s="20"/>
+      <x:c r="L200" s="20"/>
+      <x:c r="M200" s="20"/>
+      <x:c r="N200" s="20"/>
+      <x:c r="O200" s="20"/>
+      <x:c r="P200" s="20"/>
+      <x:c r="Q200" s="20"/>
+      <x:c r="R200" s="20"/>
+      <x:c r="S200" s="20"/>
+      <x:c r="T200" s="20"/>
+      <x:c r="U200" s="20" t="str">
         <x:f>IF(A200="","",IF(OR(L200="Closed",L200="False positive"),"No",IF(N200="","No target set",IF(N200&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="201">
-      <x:c r="U201" t="str">
+      <x:c r="A201" s="20"/>
+      <x:c r="B201" s="20"/>
+      <x:c r="C201" s="20"/>
+      <x:c r="D201" s="20"/>
+      <x:c r="E201" s="20"/>
+      <x:c r="F201" s="20"/>
+      <x:c r="G201" s="20"/>
+      <x:c r="H201" s="20"/>
+      <x:c r="I201" s="20"/>
+      <x:c r="J201" s="20"/>
+      <x:c r="K201" s="20"/>
+      <x:c r="L201" s="20"/>
+      <x:c r="M201" s="20"/>
+      <x:c r="N201" s="20"/>
+      <x:c r="O201" s="20"/>
+      <x:c r="P201" s="20"/>
+      <x:c r="Q201" s="20"/>
+      <x:c r="R201" s="20"/>
+      <x:c r="S201" s="20"/>
+      <x:c r="T201" s="20"/>
+      <x:c r="U201" s="20" t="str">
         <x:f>IF(A201="","",IF(OR(L201="Closed",L201="False positive"),"No",IF(N201="","No target set",IF(N201&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="202">
-      <x:c r="U202" t="str">
+      <x:c r="A202" s="20"/>
+      <x:c r="B202" s="20"/>
+      <x:c r="C202" s="20"/>
+      <x:c r="D202" s="20"/>
+      <x:c r="E202" s="20"/>
+      <x:c r="F202" s="20"/>
+      <x:c r="G202" s="20"/>
+      <x:c r="H202" s="20"/>
+      <x:c r="I202" s="20"/>
+      <x:c r="J202" s="20"/>
+      <x:c r="K202" s="20"/>
+      <x:c r="L202" s="20"/>
+      <x:c r="M202" s="20"/>
+      <x:c r="N202" s="20"/>
+      <x:c r="O202" s="20"/>
+      <x:c r="P202" s="20"/>
+      <x:c r="Q202" s="20"/>
+      <x:c r="R202" s="20"/>
+      <x:c r="S202" s="20"/>
+      <x:c r="T202" s="20"/>
+      <x:c r="U202" s="20" t="str">
         <x:f>IF(A202="","",IF(OR(L202="Closed",L202="False positive"),"No",IF(N202="","No target set",IF(N202&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="203">
-      <x:c r="U203" t="str">
+      <x:c r="A203" s="20"/>
+      <x:c r="B203" s="20"/>
+      <x:c r="C203" s="20"/>
+      <x:c r="D203" s="20"/>
+      <x:c r="E203" s="20"/>
+      <x:c r="F203" s="20"/>
+      <x:c r="G203" s="20"/>
+      <x:c r="H203" s="20"/>
+      <x:c r="I203" s="20"/>
+      <x:c r="J203" s="20"/>
+      <x:c r="K203" s="20"/>
+      <x:c r="L203" s="20"/>
+      <x:c r="M203" s="20"/>
+      <x:c r="N203" s="20"/>
+      <x:c r="O203" s="20"/>
+      <x:c r="P203" s="20"/>
+      <x:c r="Q203" s="20"/>
+      <x:c r="R203" s="20"/>
+      <x:c r="S203" s="20"/>
+      <x:c r="T203" s="20"/>
+      <x:c r="U203" s="20" t="str">
         <x:f>IF(A203="","",IF(OR(L203="Closed",L203="False positive"),"No",IF(N203="","No target set",IF(N203&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="204">
-      <x:c r="U204" t="str">
+      <x:c r="A204" s="20"/>
+      <x:c r="B204" s="20"/>
+      <x:c r="C204" s="20"/>
+      <x:c r="D204" s="20"/>
+      <x:c r="E204" s="20"/>
+      <x:c r="F204" s="20"/>
+      <x:c r="G204" s="20"/>
+      <x:c r="H204" s="20"/>
+      <x:c r="I204" s="20"/>
+      <x:c r="J204" s="20"/>
+      <x:c r="K204" s="20"/>
+      <x:c r="L204" s="20"/>
+      <x:c r="M204" s="20"/>
+      <x:c r="N204" s="20"/>
+      <x:c r="O204" s="20"/>
+      <x:c r="P204" s="20"/>
+      <x:c r="Q204" s="20"/>
+      <x:c r="R204" s="20"/>
+      <x:c r="S204" s="20"/>
+      <x:c r="T204" s="20"/>
+      <x:c r="U204" s="20" t="str">
         <x:f>IF(A204="","",IF(OR(L204="Closed",L204="False positive"),"No",IF(N204="","No target set",IF(N204&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
     <x:row r="205">
-      <x:c r="U205" t="str">
+      <x:c r="A205" s="20"/>
+      <x:c r="B205" s="20"/>
+      <x:c r="C205" s="20"/>
+      <x:c r="D205" s="20"/>
+      <x:c r="E205" s="20"/>
+      <x:c r="F205" s="20"/>
+      <x:c r="G205" s="20"/>
+      <x:c r="H205" s="20"/>
+      <x:c r="I205" s="20"/>
+      <x:c r="J205" s="20"/>
+      <x:c r="K205" s="20"/>
+      <x:c r="L205" s="20"/>
+      <x:c r="M205" s="20"/>
+      <x:c r="N205" s="20"/>
+      <x:c r="O205" s="20"/>
+      <x:c r="P205" s="20"/>
+      <x:c r="Q205" s="20"/>
+      <x:c r="R205" s="20"/>
+      <x:c r="S205" s="20"/>
+      <x:c r="T205" s="20"/>
+      <x:c r="U205" s="20" t="str">
         <x:f>IF(A205="","",IF(OR(L205="Closed",L205="False positive"),"No",IF(N205="","No target set",IF(N205&lt;'Dashboard'!B4,"Overdue","Within target"))))</x:f>
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+    <x:mergeCell ref="A3:K3"/>
+  </x:mergeCells>
   <x:conditionalFormatting sqref="L6:L205">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Closed"/>
   </x:conditionalFormatting>
@@ -2047,13 +6402,16 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ea21927c6e5431b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R701d46a02ad64092"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF5A7890"/>
+  </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="21" hidden="0" customWidth="1"/>
@@ -2068,148 +6426,154 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="1"/>
-      <x:c r="B1" s="1"/>
-      <x:c r="C1" s="1"/>
-      <x:c r="D1" s="1"/>
-      <x:c r="E1" s="1"/>
-      <x:c r="F1" s="1"/>
-      <x:c r="G1" s="1"/>
-      <x:c r="H1" s="1"/>
-      <x:c r="I1" s="1"/>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="2" t="str">
+      <x:c r="A1" s="20"/>
+      <x:c r="B1" s="20"/>
+      <x:c r="C1" s="20"/>
+      <x:c r="D1" s="20"/>
+      <x:c r="E1" s="20"/>
+      <x:c r="F1" s="20"/>
+      <x:c r="G1" s="20"/>
+      <x:c r="H1" s="20"/>
+      <x:c r="I1" s="20"/>
+    </x:row>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="24" t="str">
         <x:v>DC01 | Change and validation log</x:v>
       </x:c>
-      <x:c r="B2" s="1"/>
-      <x:c r="C2" s="1"/>
-      <x:c r="D2" s="1"/>
-      <x:c r="E2" s="1"/>
-      <x:c r="F2" s="1"/>
-      <x:c r="G2" s="1"/>
-      <x:c r="H2" s="1"/>
-      <x:c r="I2" s="1"/>
+      <x:c r="B2" s="20"/>
+      <x:c r="C2" s="20"/>
+      <x:c r="D2" s="20"/>
+      <x:c r="E2" s="20"/>
+      <x:c r="F2" s="20"/>
+      <x:c r="G2" s="20"/>
+      <x:c r="H2" s="20"/>
+      <x:c r="I2" s="20"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="1"/>
-      <x:c r="B3" s="1"/>
-      <x:c r="C3" s="1"/>
-      <x:c r="D3" s="1"/>
-      <x:c r="E3" s="1"/>
-      <x:c r="F3" s="1"/>
-      <x:c r="G3" s="1"/>
-      <x:c r="H3" s="1"/>
-      <x:c r="I3" s="1"/>
+      <x:c r="A3" s="20"/>
+      <x:c r="B3" s="20"/>
+      <x:c r="C3" s="20"/>
+      <x:c r="D3" s="20"/>
+      <x:c r="E3" s="20"/>
+      <x:c r="F3" s="20"/>
+      <x:c r="G3" s="20"/>
+      <x:c r="H3" s="20"/>
+      <x:c r="I3" s="20"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="1"/>
-      <x:c r="B4" s="1"/>
-      <x:c r="C4" s="1"/>
-      <x:c r="D4" s="1"/>
-      <x:c r="E4" s="1"/>
-      <x:c r="F4" s="1"/>
-      <x:c r="G4" s="1"/>
-      <x:c r="H4" s="1"/>
-      <x:c r="I4" s="1"/>
-    </x:row>
-    <x:row r="5" ht="34" customHeight="1">
-      <x:c r="A5" s="7" t="str">
+      <x:c r="A4" s="20"/>
+      <x:c r="B4" s="20"/>
+      <x:c r="C4" s="20"/>
+      <x:c r="D4" s="20"/>
+      <x:c r="E4" s="20"/>
+      <x:c r="F4" s="20"/>
+      <x:c r="G4" s="20"/>
+      <x:c r="H4" s="20"/>
+      <x:c r="I4" s="20"/>
+    </x:row>
+    <x:row r="5" ht="42" customHeight="1">
+      <x:c r="A5" s="33" t="str">
         <x:v>Change ID</x:v>
       </x:c>
-      <x:c r="B5" s="7" t="str">
+      <x:c r="B5" s="33" t="str">
         <x:v>Finding ID</x:v>
       </x:c>
-      <x:c r="C5" s="7" t="str">
+      <x:c r="C5" s="33" t="str">
         <x:v>Date</x:v>
       </x:c>
-      <x:c r="D5" s="7" t="str">
+      <x:c r="D5" s="33" t="str">
         <x:v>Implementation</x:v>
       </x:c>
-      <x:c r="E5" s="7" t="str">
+      <x:c r="E5" s="33" t="str">
         <x:v>Prior state / rollback</x:v>
       </x:c>
-      <x:c r="F5" s="7" t="str">
+      <x:c r="F5" s="33" t="str">
         <x:v>Verification</x:v>
       </x:c>
-      <x:c r="G5" s="7" t="str">
+      <x:c r="G5" s="33" t="str">
         <x:v>Status</x:v>
       </x:c>
-      <x:c r="H5" s="7" t="str">
+      <x:c r="H5" s="33" t="str">
         <x:v>Implementer / reviewer</x:v>
       </x:c>
-      <x:c r="I5" s="7" t="str">
+      <x:c r="I5" s="33" t="str">
         <x:v>Evidence IDs</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="145" customHeight="1">
-      <x:c r="A6" s="8" t="str">
+    <x:row r="6" ht="125" customHeight="1">
+      <x:c r="A6" s="34" t="str">
         <x:v>LAB-CHG-012</x:v>
       </x:c>
-      <x:c r="B6" s="8" t="str">
+      <x:c r="B6" s="34" t="str">
         <x:v>DC01-VULN-001</x:v>
       </x:c>
-      <x:c r="C6" s="9" t="d">
+      <x:c r="C6" s="37" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D6" s="8" t="str">
+      <x:c r="D6" s="34" t="str">
         <x:v>LAB - DC01 Security Hardening; Registry Preferences Update; HKLM native and WOW6432Node Wintrust\Config: EnableCertPaddingCheck DWORD 1. Linked Domain Controllers OU, DC01$ filter, not enforced.</x:v>
       </x:c>
-      <x:c r="E6" s="8" t="str">
+      <x:c r="E6" s="34" t="str">
         <x:v>Both values absent before. Rollback requires explicit removal of newly introduced values after preventing GPP reapplication. Unlink alone does not remove values. Rollback not exercised.</x:v>
       </x:c>
-      <x:c r="F6" s="8" t="str">
+      <x:c r="F6" s="34" t="str">
         <x:v>gpupdate success; gpresult applied; both values 0x1; restart and service checks operator-reported; credentialed rescan no WinVerifyTrust finding.</x:v>
       </x:c>
-      <x:c r="G6" s="8" t="str">
+      <x:c r="G6" s="34" t="str">
         <x:v>Verified implemented</x:v>
       </x:c>
-      <x:c r="H6" s="8" t="str">
+      <x:c r="H6" s="34" t="str">
         <x:v>Lab operator performed implementation and review; no independent approval claimed.</x:v>
       </x:c>
-      <x:c r="I6" s="8" t="str">
+      <x:c r="I6" s="34" t="str">
         <x:v>EV-003; EV-005; EV-006; EV-007; EV-008</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="145" customHeight="1">
-      <x:c r="A7" s="8" t="str">
+    <x:row r="7" ht="125" customHeight="1">
+      <x:c r="A7" s="38" t="str">
         <x:v>LAB-CHG-013</x:v>
       </x:c>
-      <x:c r="B7" s="8" t="str">
+      <x:c r="B7" s="38" t="str">
         <x:v>DC01-VULN-002</x:v>
       </x:c>
-      <x:c r="C7" s="9" t="d">
+      <x:c r="C7" s="41" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="D7" s="8" t="str">
+      <x:c r="D7" s="38" t="str">
         <x:v>Same DC01-only GPO: HKLM SYSTEM\CurrentControlSet\Control\Session Manager\Memory Management; FeatureSettingsOverride DWORD 8388608; FeatureSettingsOverrideMask DWORD 3.</x:v>
       </x:c>
-      <x:c r="E7" s="8" t="str">
+      <x:c r="E7" s="38" t="str">
         <x:v>Both values absent before. Explicitly remove introduced values after preventing reapplication if rollback needed; restart; validate. Rollback not exercised.</x:v>
       </x:c>
-      <x:c r="F7" s="8" t="str">
+      <x:c r="F7" s="38" t="str">
         <x:v>gpupdate success; values 0x800000 and 0x3; restart/service checks operator-reported; final authenticated scan all Info; Windows group Info.</x:v>
       </x:c>
-      <x:c r="G7" s="8" t="str">
+      <x:c r="G7" s="38" t="str">
         <x:v>Verified implemented</x:v>
       </x:c>
-      <x:c r="H7" s="8" t="str">
+      <x:c r="H7" s="38" t="str">
         <x:v>Lab operator performed implementation and review; no independent approval claimed.</x:v>
       </x:c>
-      <x:c r="I7" s="8" t="str">
+      <x:c r="I7" s="38" t="str">
         <x:v>EV-009; EV-010; EV-011; EV-012; EV-013</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86948319ec4542e8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf24da322758a4ff6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF5A7890"/>
+  </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
@@ -2224,468 +6588,480 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="1"/>
-      <x:c r="B1" s="1"/>
-      <x:c r="C1" s="1"/>
-      <x:c r="D1" s="1"/>
-      <x:c r="E1" s="1"/>
-      <x:c r="F1" s="1"/>
-      <x:c r="G1" s="1"/>
-      <x:c r="H1" s="1"/>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="2" t="str">
+      <x:c r="A1" s="20"/>
+      <x:c r="B1" s="20"/>
+      <x:c r="C1" s="20"/>
+      <x:c r="D1" s="20"/>
+      <x:c r="E1" s="20"/>
+      <x:c r="F1" s="20"/>
+      <x:c r="G1" s="20"/>
+      <x:c r="H1" s="20"/>
+      <x:c r="I1" s="20"/>
+    </x:row>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="24" t="str">
         <x:v>DC01 | Evidence index</x:v>
       </x:c>
-      <x:c r="B2" s="1"/>
-      <x:c r="C2" s="1"/>
-      <x:c r="D2" s="1"/>
-      <x:c r="E2" s="1"/>
-      <x:c r="F2" s="1"/>
-      <x:c r="G2" s="1"/>
-      <x:c r="H2" s="1"/>
+      <x:c r="B2" s="20"/>
+      <x:c r="C2" s="20"/>
+      <x:c r="D2" s="20"/>
+      <x:c r="E2" s="20"/>
+      <x:c r="F2" s="20"/>
+      <x:c r="G2" s="20"/>
+      <x:c r="H2" s="20"/>
+      <x:c r="I2" s="20"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="1"/>
-      <x:c r="B3" s="1"/>
-      <x:c r="C3" s="1"/>
-      <x:c r="D3" s="1"/>
-      <x:c r="E3" s="1"/>
-      <x:c r="F3" s="1"/>
-      <x:c r="G3" s="1"/>
-      <x:c r="H3" s="1"/>
+      <x:c r="A3" s="20"/>
+      <x:c r="B3" s="20"/>
+      <x:c r="C3" s="20"/>
+      <x:c r="D3" s="20"/>
+      <x:c r="E3" s="20"/>
+      <x:c r="F3" s="20"/>
+      <x:c r="G3" s="20"/>
+      <x:c r="H3" s="20"/>
+      <x:c r="I3" s="20"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="1"/>
-      <x:c r="B4" s="1"/>
-      <x:c r="C4" s="1"/>
-      <x:c r="D4" s="1"/>
-      <x:c r="E4" s="1"/>
-      <x:c r="F4" s="1"/>
-      <x:c r="G4" s="1"/>
-      <x:c r="H4" s="1"/>
-    </x:row>
-    <x:row r="5" ht="34" customHeight="1">
-      <x:c r="A5" s="7" t="str">
+      <x:c r="A4" s="20"/>
+      <x:c r="B4" s="20"/>
+      <x:c r="C4" s="20"/>
+      <x:c r="D4" s="20"/>
+      <x:c r="E4" s="20"/>
+      <x:c r="F4" s="20"/>
+      <x:c r="G4" s="20"/>
+      <x:c r="H4" s="20"/>
+      <x:c r="I4" s="20"/>
+    </x:row>
+    <x:row r="5" ht="42" customHeight="1">
+      <x:c r="A5" s="33" t="str">
         <x:v>Evidence ID</x:v>
       </x:c>
-      <x:c r="B5" s="7" t="str">
+      <x:c r="B5" s="33" t="str">
         <x:v>Related record</x:v>
       </x:c>
-      <x:c r="C5" s="7" t="str">
+      <x:c r="C5" s="33" t="str">
         <x:v>Evidence title</x:v>
       </x:c>
-      <x:c r="D5" s="7" t="str">
+      <x:c r="D5" s="33" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="E5" s="7" t="str">
+      <x:c r="E5" s="33" t="str">
         <x:v>What it demonstrates</x:v>
       </x:c>
-      <x:c r="F5" s="7" t="str">
+      <x:c r="F5" s="33" t="str">
         <x:v>Source locator</x:v>
       </x:c>
-      <x:c r="G5" s="7" t="str">
+      <x:c r="G5" s="33" t="str">
         <x:v>Observed date</x:v>
       </x:c>
-      <x:c r="H5" s="7" t="str">
+      <x:c r="H5" s="33" t="str">
         <x:v>Retention status</x:v>
       </x:c>
-      <x:c r="I5" s="13" t="str">
+      <x:c r="I5" s="33" t="str">
         <x:v>Evidence link</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="72" customHeight="1">
-      <x:c r="A6" s="8" t="str">
+    <x:row r="6" ht="90" customHeight="1">
+      <x:c r="A6" s="34" t="str">
         <x:v>EV-001</x:v>
       </x:c>
-      <x:c r="B6" s="8" t="str">
+      <x:c r="B6" s="34" t="str">
         <x:v>DC01-SCAN-001</x:v>
       </x:c>
-      <x:c r="C6" s="8" t="str">
+      <x:c r="C6" s="34" t="str">
         <x:v>Initial limited scan / valid SMB login / WMI denied</x:v>
       </x:c>
-      <x:c r="D6" s="8" t="str">
+      <x:c r="D6" s="34" t="str">
         <x:v>Screenshots</x:v>
       </x:c>
-      <x:c r="E6" s="8" t="str">
+      <x:c r="E6" s="34" t="str">
         <x:v>Initial Auth Fail; 19506 credentialed checks no; 141118 valid svc_nessus SMB login; 135860 WMI unavailable; direct WMI access denied.</x:v>
       </x:c>
-      <x:c r="F6" s="8" t="str">
+      <x:c r="F6" s="34" t="str">
         <x:v>DC01-Initial-Scan-Auth-Fail.png; DC01-Initial-Credentialed-Checks-No.png; DC01-Initial-SMB-Valid-Credentials-Output.png; DC01-Initial-WMI-Not-Available.png; DC01-Scanner-WMI-Access-Denied-01.png</x:v>
       </x:c>
-      <x:c r="G6" s="9" t="d">
+      <x:c r="G6" s="37" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H6" s="8" t="str">
+      <x:c r="H6" s="34" t="str">
         <x:v>Retained in repository evidence folder; linked to first capture. See evidence README for full inventory.</x:v>
       </x:c>
-      <x:c r="I6" t="e">
+      <x:c r="I6" s="54" t="e">
         <x:f>HYPERLINK("../06-Evidence/Phase-4-Vulnerability-Assessment/DC01/DC01-Initial-Scan-Auth-Fail.png","Open evidence")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=../06-Evidence/Phase-4-Vulnerability-Assessment/DC01/DC01-Initial-Scan-Auth-Fail.png, friendlyName=Open evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="72" customHeight="1">
-      <x:c r="A7" s="8" t="str">
+    <x:row r="7" ht="90" customHeight="1">
+      <x:c r="A7" s="38" t="str">
         <x:v>EV-002</x:v>
       </x:c>
-      <x:c r="B7" s="8" t="str">
+      <x:c r="B7" s="38" t="str">
         <x:v>DC01-SCAN-001</x:v>
       </x:c>
-      <x:c r="C7" s="8" t="str">
+      <x:c r="C7" s="38" t="str">
         <x:v>Privileged scan coverage</x:v>
       </x:c>
-      <x:c r="D7" s="8" t="str">
+      <x:c r="D7" s="38" t="str">
         <x:v>Screenshots</x:v>
       </x:c>
-      <x:c r="E7" s="8" t="str">
+      <x:c r="E7" s="38" t="str">
         <x:v>19506 yes as NORTHSTAR\Administrator; 110095 no privilege/access problems via SMB.</x:v>
       </x:c>
-      <x:c r="F7" s="8" t="str">
+      <x:c r="F7" s="38" t="str">
         <x:v>DC01-Privileged-Baseline-Credentialed-Checks.png; DC01-Privileged-No-Credential-Issues-Output.png</x:v>
       </x:c>
-      <x:c r="G7" s="9" t="d">
+      <x:c r="G7" s="41" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H7" s="8" t="str">
+      <x:c r="H7" s="38" t="str">
         <x:v>Retained in repository evidence folder; linked to first capture. See evidence README for full inventory.</x:v>
       </x:c>
-      <x:c r="I7" t="e">
+      <x:c r="I7" s="55" t="e">
         <x:f>HYPERLINK("../06-Evidence/Phase-4-Vulnerability-Assessment/DC01/DC01-Privileged-Baseline-Credentialed-Checks.png","Open evidence")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=../06-Evidence/Phase-4-Vulnerability-Assessment/DC01/DC01-Privileged-Baseline-Credentialed-Checks.png, friendlyName=Open evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="72" customHeight="1">
-      <x:c r="A8" s="8" t="str">
+    <x:row r="8" ht="90" customHeight="1">
+      <x:c r="A8" s="34" t="str">
         <x:v>EV-003</x:v>
       </x:c>
-      <x:c r="B8" s="8" t="str">
+      <x:c r="B8" s="34" t="str">
         <x:v>DC01-VULN-001</x:v>
       </x:c>
-      <x:c r="C8" s="8" t="str">
+      <x:c r="C8" s="34" t="str">
         <x:v>WinVerifyTrust baseline details and scores</x:v>
       </x:c>
-      <x:c r="D8" s="8" t="str">
+      <x:c r="D8" s="34" t="str">
         <x:v>Screenshots</x:v>
       </x:c>
-      <x:c r="E8" s="8" t="str">
+      <x:c r="E8" s="34" t="str">
         <x:v>Both values absent; CVSS 8.8 / VPR 9.5 / EPSS .4465.</x:v>
       </x:c>
-      <x:c r="F8" s="8" t="str">
+      <x:c r="F8" s="34" t="str">
         <x:v>DC01-WinVerifyTrust-Baseline-Details.png; DC01-WinVerifyTrust-Baseline-Output-Scores.png</x:v>
       </x:c>
-      <x:c r="G8" s="9" t="d">
+      <x:c r="G8" s="37" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H8" s="8" t="str">
+      <x:c r="H8" s="34" t="str">
         <x:v>Retained in repository evidence folder; linked to first capture. See evidence README for full inventory.</x:v>
       </x:c>
-      <x:c r="I8" t="e">
+      <x:c r="I8" s="54" t="e">
         <x:f>HYPERLINK("../06-Evidence/Phase-4-Vulnerability-Assessment/DC01/DC01-WinVerifyTrust-Baseline-Details.png","Open evidence")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=../06-Evidence/Phase-4-Vulnerability-Assessment/DC01/DC01-WinVerifyTrust-Baseline-Details.png, friendlyName=Open evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="72" customHeight="1">
-      <x:c r="A9" s="8" t="str">
+    <x:row r="9" ht="90" customHeight="1">
+      <x:c r="A9" s="38" t="str">
         <x:v>EV-004</x:v>
       </x:c>
-      <x:c r="B9" s="8" t="str">
+      <x:c r="B9" s="38" t="str">
         <x:v>DC01-VULN-002</x:v>
       </x:c>
-      <x:c r="C9" s="8" t="str">
+      <x:c r="C9" s="38" t="str">
         <x:v>Intel BHI baseline details and scores</x:v>
       </x:c>
-      <x:c r="D9" s="8" t="str">
+      <x:c r="D9" s="38" t="str">
         <x:v>Screenshots</x:v>
       </x:c>
-      <x:c r="E9" s="8" t="str">
+      <x:c r="E9" s="38" t="str">
         <x:v>Override and mask Not Set; Low / CVSS 6.5 / VPR 3.3 / EPSS .0046.</x:v>
       </x:c>
-      <x:c r="F9" s="8" t="str">
+      <x:c r="F9" s="38" t="str">
         <x:v>DC01-Intel-BHI-Baseline-Details.png; DC01-Intel-BHI-Baseline-Recommendations-Scores.png</x:v>
       </x:c>
-      <x:c r="G9" s="9" t="d">
+      <x:c r="G9" s="41" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H9" s="8" t="str">
+      <x:c r="H9" s="38" t="str">
         <x:v>Retained in repository evidence folder; linked to first capture. See evidence README for full inventory.</x:v>
       </x:c>
-      <x:c r="I9" t="e">
+      <x:c r="I9" s="55" t="e">
         <x:f>HYPERLINK("../06-Evidence/Phase-4-Vulnerability-Assessment/DC01/DC01-Intel-BHI-Baseline-Details.png","Open evidence")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=../06-Evidence/Phase-4-Vulnerability-Assessment/DC01/DC01-Intel-BHI-Baseline-Details.png, friendlyName=Open evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="72" customHeight="1">
-      <x:c r="A10" s="8" t="str">
+    <x:row r="10" ht="90" customHeight="1">
+      <x:c r="A10" s="34" t="str">
         <x:v>EV-005</x:v>
       </x:c>
-      <x:c r="B10" s="8" t="str">
+      <x:c r="B10" s="34" t="str">
         <x:v>LAB-CHG-012</x:v>
       </x:c>
-      <x:c r="C10" s="8" t="str">
+      <x:c r="C10" s="34" t="str">
         <x:v>GPO scope and application</x:v>
       </x:c>
-      <x:c r="D10" s="8" t="str">
+      <x:c r="D10" s="34" t="str">
         <x:v>Screenshots</x:v>
       </x:c>
-      <x:c r="E10" s="8" t="str">
+      <x:c r="E10" s="34" t="str">
         <x:v>Domain Controllers link enabled, not enforced; DC01$ only; gpresult applied.</x:v>
       </x:c>
-      <x:c r="F10" s="8" t="str">
+      <x:c r="F10" s="34" t="str">
         <x:v>DC01-Hardening-GPO-Security-Filtering.png; DC01-Hardening-GPO-Domain-Controllers-Link.png; DC01-Hardening-GPO-Applied.png</x:v>
       </x:c>
-      <x:c r="G10" s="9" t="d">
+      <x:c r="G10" s="37" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H10" s="8" t="str">
+      <x:c r="H10" s="34" t="str">
         <x:v>Retained in repository evidence folder; linked to first capture. See evidence README for full inventory.</x:v>
       </x:c>
-      <x:c r="I10" t="e">
+      <x:c r="I10" s="54" t="e">
         <x:f>HYPERLINK("../06-Evidence/Phase-4-Vulnerability-Assessment/DC01/DC01-Hardening-GPO-Security-Filtering.png","Open evidence")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=../06-Evidence/Phase-4-Vulnerability-Assessment/DC01/DC01-Hardening-GPO-Security-Filtering.png, friendlyName=Open evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="72" customHeight="1">
-      <x:c r="A11" s="8" t="str">
+    <x:row r="11" ht="90" customHeight="1">
+      <x:c r="A11" s="38" t="str">
         <x:v>EV-006</x:v>
       </x:c>
-      <x:c r="B11" s="8" t="str">
+      <x:c r="B11" s="38" t="str">
         <x:v>LAB-CHG-012</x:v>
       </x:c>
-      <x:c r="C11" s="8" t="str">
+      <x:c r="C11" s="38" t="str">
         <x:v>Native and WOW6432Node values after</x:v>
       </x:c>
-      <x:c r="D11" s="8" t="str">
+      <x:c r="D11" s="38" t="str">
         <x:v>Screenshot</x:v>
       </x:c>
-      <x:c r="E11" s="8" t="str">
+      <x:c r="E11" s="38" t="str">
         <x:v>Both EnableCertPaddingCheck values REG_DWORD 0x1.</x:v>
       </x:c>
-      <x:c r="F11" s="8" t="str">
+      <x:c r="F11" s="38" t="str">
         <x:v>DC01-WinVerifyTrust-Registry-After.png</x:v>
       </x:c>
-      <x:c r="G11" s="9" t="d">
+      <x:c r="G11" s="41" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H11" s="8" t="str">
+      <x:c r="H11" s="38" t="str">
         <x:v>Retained in repository evidence folder; linked to first capture. See evidence README for full inventory.</x:v>
       </x:c>
-      <x:c r="I11" t="e">
+      <x:c r="I11" s="55" t="e">
         <x:f>HYPERLINK("../06-Evidence/Phase-4-Vulnerability-Assessment/DC01/DC01-WinVerifyTrust-Registry-After.png","Open evidence")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=../06-Evidence/Phase-4-Vulnerability-Assessment/DC01/DC01-WinVerifyTrust-Registry-After.png, friendlyName=Open evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="72" customHeight="1">
-      <x:c r="A12" s="8" t="str">
+    <x:row r="12" ht="90" customHeight="1">
+      <x:c r="A12" s="34" t="str">
         <x:v>EV-007</x:v>
       </x:c>
-      <x:c r="B12" s="8" t="str">
+      <x:c r="B12" s="34" t="str">
         <x:v>LAB-CHG-012</x:v>
       </x:c>
-      <x:c r="C12" s="8" t="str">
+      <x:c r="C12" s="34" t="str">
         <x:v>Post-restart health</x:v>
       </x:c>
-      <x:c r="D12" s="8" t="str">
+      <x:c r="D12" s="34" t="str">
         <x:v>Operator report</x:v>
       </x:c>
-      <x:c r="E12" s="8" t="str">
+      <x:c r="E12" s="34" t="str">
         <x:v>AD DS, DNS, Netlogon, KDC running; ADUC displays ad.northstar.test.</x:v>
       </x:c>
-      <x:c r="F12" s="8" t="str">
+      <x:c r="F12" s="34" t="str">
         <x:v>User confirmation in chat; no screenshot claimed.</x:v>
       </x:c>
-      <x:c r="G12" s="9" t="d">
+      <x:c r="G12" s="37" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H12" s="8" t="str">
+      <x:c r="H12" s="34" t="str">
         <x:v>Operator-confirmed in conversation; no screenshot claimed.</x:v>
       </x:c>
-    </x:row>
-    <x:row r="13" ht="72" customHeight="1">
-      <x:c r="A13" s="8" t="str">
+      <x:c r="I12" s="54"/>
+    </x:row>
+    <x:row r="13" ht="90" customHeight="1">
+      <x:c r="A13" s="38" t="str">
         <x:v>EV-008</x:v>
       </x:c>
-      <x:c r="B13" s="8" t="str">
+      <x:c r="B13" s="38" t="str">
         <x:v>DC01-VULN-001</x:v>
       </x:c>
-      <x:c r="C13" s="8" t="str">
+      <x:c r="C13" s="38" t="str">
         <x:v>WinVerifyTrust verification</x:v>
       </x:c>
-      <x:c r="D13" s="8" t="str">
+      <x:c r="D13" s="38" t="str">
         <x:v>Screenshots</x:v>
       </x:c>
-      <x:c r="E13" s="8" t="str">
+      <x:c r="E13" s="38" t="str">
         <x:v>Auth Pass / 19506 yes / same feed; no records for WinVerifyTrust; overview no High segment.</x:v>
       </x:c>
-      <x:c r="F13" s="8" t="str">
+      <x:c r="F13" s="38" t="str">
         <x:v>DC01-WinVerifyTrust-Rescan-Credentialed-Checks.png; DC01-WinVerifyTrust-Verification-Not-Detected.png</x:v>
       </x:c>
-      <x:c r="G13" s="9" t="d">
+      <x:c r="G13" s="41" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H13" s="8" t="str">
+      <x:c r="H13" s="38" t="str">
         <x:v>Retained in repository evidence folder; linked to first capture. See evidence README for full inventory.</x:v>
       </x:c>
-      <x:c r="I13" t="e">
+      <x:c r="I13" s="55" t="e">
         <x:f>HYPERLINK("../06-Evidence/Phase-4-Vulnerability-Assessment/DC01/DC01-WinVerifyTrust-Rescan-Credentialed-Checks.png","Open evidence")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=../06-Evidence/Phase-4-Vulnerability-Assessment/DC01/DC01-WinVerifyTrust-Rescan-Credentialed-Checks.png, friendlyName=Open evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="72" customHeight="1">
-      <x:c r="A14" s="8" t="str">
+    <x:row r="14" ht="90" customHeight="1">
+      <x:c r="A14" s="34" t="str">
         <x:v>EV-009</x:v>
       </x:c>
-      <x:c r="B14" s="8" t="str">
+      <x:c r="B14" s="34" t="str">
         <x:v>LAB-CHG-013</x:v>
       </x:c>
-      <x:c r="C14" s="8" t="str">
+      <x:c r="C14" s="34" t="str">
         <x:v>BHI local values before</x:v>
       </x:c>
-      <x:c r="D14" s="8" t="str">
+      <x:c r="D14" s="34" t="str">
         <x:v>Screenshot</x:v>
       </x:c>
-      <x:c r="E14" s="8" t="str">
+      <x:c r="E14" s="34" t="str">
         <x:v>Both registry queries report value/key not found.</x:v>
       </x:c>
-      <x:c r="F14" s="8" t="str">
+      <x:c r="F14" s="34" t="str">
         <x:v>DC01-BHI-Registry-Before.png</x:v>
       </x:c>
-      <x:c r="G14" s="9" t="d">
+      <x:c r="G14" s="37" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H14" s="8" t="str">
+      <x:c r="H14" s="34" t="str">
         <x:v>Retained in repository evidence folder; linked to first capture. See evidence README for full inventory.</x:v>
       </x:c>
-      <x:c r="I14" t="e">
+      <x:c r="I14" s="54" t="e">
         <x:f>HYPERLINK("../06-Evidence/Phase-4-Vulnerability-Assessment/DC01/DC01-BHI-Registry-Before.png","Open evidence")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=../06-Evidence/Phase-4-Vulnerability-Assessment/DC01/DC01-BHI-Registry-Before.png, friendlyName=Open evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="72" customHeight="1">
-      <x:c r="A15" s="8" t="str">
+    <x:row r="15" ht="90" customHeight="1">
+      <x:c r="A15" s="38" t="str">
         <x:v>EV-010</x:v>
       </x:c>
-      <x:c r="B15" s="8" t="str">
+      <x:c r="B15" s="38" t="str">
         <x:v>LAB-CHG-013</x:v>
       </x:c>
-      <x:c r="C15" s="8" t="str">
+      <x:c r="C15" s="38" t="str">
         <x:v>Four GPO registry items</x:v>
       </x:c>
-      <x:c r="D15" s="8" t="str">
+      <x:c r="D15" s="38" t="str">
         <x:v>Screenshot</x:v>
       </x:c>
-      <x:c r="E15" s="8" t="str">
+      <x:c r="E15" s="38" t="str">
         <x:v>Two cert-padding values retained; BHI data 00800000 and 00000003.</x:v>
       </x:c>
-      <x:c r="F15" s="8" t="str">
+      <x:c r="F15" s="38" t="str">
         <x:v>DC01-Hardening-GPO-Four-Registry-Items.png</x:v>
       </x:c>
-      <x:c r="G15" s="9" t="d">
+      <x:c r="G15" s="41" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H15" s="8" t="str">
+      <x:c r="H15" s="38" t="str">
         <x:v>Retained in repository evidence folder; linked to first capture. See evidence README for full inventory.</x:v>
       </x:c>
-      <x:c r="I15" t="e">
+      <x:c r="I15" s="55" t="e">
         <x:f>HYPERLINK("../06-Evidence/Phase-4-Vulnerability-Assessment/DC01/DC01-Hardening-GPO-Four-Registry-Items.png","Open evidence")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=../06-Evidence/Phase-4-Vulnerability-Assessment/DC01/DC01-Hardening-GPO-Four-Registry-Items.png, friendlyName=Open evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="72" customHeight="1">
-      <x:c r="A16" s="8" t="str">
+    <x:row r="16" ht="90" customHeight="1">
+      <x:c r="A16" s="34" t="str">
         <x:v>EV-011</x:v>
       </x:c>
-      <x:c r="B16" s="8" t="str">
+      <x:c r="B16" s="34" t="str">
         <x:v>LAB-CHG-013</x:v>
       </x:c>
-      <x:c r="C16" s="8" t="str">
+      <x:c r="C16" s="34" t="str">
         <x:v>BHI local values after</x:v>
       </x:c>
-      <x:c r="D16" s="8" t="str">
+      <x:c r="D16" s="34" t="str">
         <x:v>Screenshot</x:v>
       </x:c>
-      <x:c r="E16" s="8" t="str">
+      <x:c r="E16" s="34" t="str">
         <x:v>Policy refreshed; override 0x800000 and mask 0x3.</x:v>
       </x:c>
-      <x:c r="F16" s="8" t="str">
+      <x:c r="F16" s="34" t="str">
         <x:v>DC01-BHI-Registry-After.png</x:v>
       </x:c>
-      <x:c r="G16" s="9" t="d">
+      <x:c r="G16" s="37" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H16" s="8" t="str">
+      <x:c r="H16" s="34" t="str">
         <x:v>Retained in repository evidence folder; linked to first capture. See evidence README for full inventory.</x:v>
       </x:c>
-      <x:c r="I16" t="e">
+      <x:c r="I16" s="54" t="e">
         <x:f>HYPERLINK("../06-Evidence/Phase-4-Vulnerability-Assessment/DC01/DC01-BHI-Registry-After.png","Open evidence")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=../06-Evidence/Phase-4-Vulnerability-Assessment/DC01/DC01-BHI-Registry-After.png, friendlyName=Open evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="72" customHeight="1">
-      <x:c r="A17" s="8" t="str">
+    <x:row r="17" ht="90" customHeight="1">
+      <x:c r="A17" s="38" t="str">
         <x:v>EV-012</x:v>
       </x:c>
-      <x:c r="B17" s="8" t="str">
+      <x:c r="B17" s="38" t="str">
         <x:v>DC01-VULN-002</x:v>
       </x:c>
-      <x:c r="C17" s="8" t="str">
+      <x:c r="C17" s="38" t="str">
         <x:v>Final credentialed rescan and Windows group</x:v>
       </x:c>
-      <x:c r="D17" s="8" t="str">
+      <x:c r="D17" s="38" t="str">
         <x:v>Screenshots</x:v>
       </x:c>
-      <x:c r="E17" s="8" t="str">
+      <x:c r="E17" s="38" t="str">
         <x:v>Auth Pass; credentialed checks yes; same feed; all Info; Windows group Info.</x:v>
       </x:c>
-      <x:c r="F17" s="8" t="str">
+      <x:c r="F17" s="38" t="str">
         <x:v>DC01-Final-Rescan-Overview.png; DC01-Final-Rescan-Credentialed-Checks.png; DC01-Final-Rescan-Windows-Group-Info.png</x:v>
       </x:c>
-      <x:c r="G17" s="9" t="d">
+      <x:c r="G17" s="41" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H17" s="8" t="str">
+      <x:c r="H17" s="38" t="str">
         <x:v>Retained in repository evidence folder; linked to first capture. See evidence README for full inventory.</x:v>
       </x:c>
-      <x:c r="I17" t="e">
+      <x:c r="I17" s="55" t="e">
         <x:f>HYPERLINK("../06-Evidence/Phase-4-Vulnerability-Assessment/DC01/DC01-Final-Rescan-Overview.png","Open evidence")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=../06-Evidence/Phase-4-Vulnerability-Assessment/DC01/DC01-Final-Rescan-Overview.png, friendlyName=Open evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="72" customHeight="1">
-      <x:c r="A18" s="8" t="str">
+    <x:row r="18" ht="90" customHeight="1">
+      <x:c r="A18" s="34" t="str">
         <x:v>EV-013</x:v>
       </x:c>
-      <x:c r="B18" s="8" t="str">
+      <x:c r="B18" s="34" t="str">
         <x:v>LAB-CHG-013</x:v>
       </x:c>
-      <x:c r="C18" s="8" t="str">
+      <x:c r="C18" s="34" t="str">
         <x:v>Post-restart health</x:v>
       </x:c>
-      <x:c r="D18" s="8" t="str">
+      <x:c r="D18" s="34" t="str">
         <x:v>Operator report</x:v>
       </x:c>
-      <x:c r="E18" s="8" t="str">
+      <x:c r="E18" s="34" t="str">
         <x:v>User stated all listed service and ADUC checks passed.</x:v>
       </x:c>
-      <x:c r="F18" s="8" t="str">
+      <x:c r="F18" s="34" t="str">
         <x:v>User confirmation: They all passed; no screenshot claimed.</x:v>
       </x:c>
-      <x:c r="G18" s="9" t="d">
+      <x:c r="G18" s="37" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="H18" s="8" t="str">
+      <x:c r="H18" s="34" t="str">
         <x:v>Operator-confirmed in conversation; no screenshot claimed.</x:v>
       </x:c>
+      <x:c r="I18" s="54"/>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4db1269b7caa4d3e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re183d83402a34f78"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF5A7890"/>
+  </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
@@ -2697,314 +7073,323 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="1"/>
-      <x:c r="B1" s="1"/>
-      <x:c r="C1" s="1"/>
-      <x:c r="D1" s="1"/>
-      <x:c r="E1" s="1"/>
-      <x:c r="F1" s="1"/>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="2" t="str">
+      <x:c r="A1" s="20"/>
+      <x:c r="B1" s="20"/>
+      <x:c r="C1" s="20"/>
+      <x:c r="D1" s="20"/>
+      <x:c r="E1" s="20"/>
+      <x:c r="F1" s="20"/>
+    </x:row>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="24" t="str">
         <x:v>DC01 | Coverage and exceptions</x:v>
       </x:c>
-      <x:c r="B2" s="1"/>
-      <x:c r="C2" s="1"/>
-      <x:c r="D2" s="1"/>
-      <x:c r="E2" s="1"/>
-      <x:c r="F2" s="1"/>
+      <x:c r="B2" s="20"/>
+      <x:c r="C2" s="20"/>
+      <x:c r="D2" s="20"/>
+      <x:c r="E2" s="20"/>
+      <x:c r="F2" s="20"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="1"/>
-      <x:c r="B3" s="1"/>
-      <x:c r="C3" s="1"/>
-      <x:c r="D3" s="1"/>
-      <x:c r="E3" s="1"/>
-      <x:c r="F3" s="1"/>
+      <x:c r="A3" s="20"/>
+      <x:c r="B3" s="20"/>
+      <x:c r="C3" s="20"/>
+      <x:c r="D3" s="20"/>
+      <x:c r="E3" s="20"/>
+      <x:c r="F3" s="20"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="1"/>
-      <x:c r="B4" s="1"/>
-      <x:c r="C4" s="1"/>
-      <x:c r="D4" s="1"/>
-      <x:c r="E4" s="1"/>
-      <x:c r="F4" s="1"/>
-    </x:row>
-    <x:row r="5" ht="34" customHeight="1">
-      <x:c r="A5" s="7" t="str">
+      <x:c r="A4" s="20"/>
+      <x:c r="B4" s="20"/>
+      <x:c r="C4" s="20"/>
+      <x:c r="D4" s="20"/>
+      <x:c r="E4" s="20"/>
+      <x:c r="F4" s="20"/>
+    </x:row>
+    <x:row r="5" ht="42" customHeight="1">
+      <x:c r="A5" s="33" t="str">
         <x:v>Record ID</x:v>
       </x:c>
-      <x:c r="B5" s="7" t="str">
+      <x:c r="B5" s="33" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="C5" s="7" t="str">
+      <x:c r="C5" s="33" t="str">
         <x:v>Status</x:v>
       </x:c>
-      <x:c r="D5" s="7" t="str">
+      <x:c r="D5" s="33" t="str">
         <x:v>Observation</x:v>
       </x:c>
-      <x:c r="E5" s="7" t="str">
+      <x:c r="E5" s="33" t="str">
         <x:v>Disposition / remaining action</x:v>
       </x:c>
-      <x:c r="F5" s="7" t="str">
+      <x:c r="F5" s="33" t="str">
         <x:v>Evidence</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="110" customHeight="1">
-      <x:c r="A6" s="8" t="str">
+      <x:c r="A6" s="34" t="str">
         <x:v>DC01-SCAN-001</x:v>
       </x:c>
-      <x:c r="B6" s="8" t="str">
+      <x:c r="B6" s="34" t="str">
         <x:v>Scan quality</x:v>
       </x:c>
-      <x:c r="C6" s="8" t="str">
+      <x:c r="C6" s="34" t="str">
         <x:v>Resolved</x:v>
       </x:c>
-      <x:c r="D6" s="8" t="str">
+      <x:c r="D6" s="34" t="str">
         <x:v>svc_nessus authenticated to SMB but credentialed checks no; WMI access denied.</x:v>
       </x:c>
-      <x:c r="E6" s="8" t="str">
+      <x:c r="E6" s="34" t="str">
         <x:v>Resolved for this scan by replacing scan credentials with existing Administrator. svc_nessus privileges unchanged.</x:v>
       </x:c>
-      <x:c r="F6" s="8" t="str">
+      <x:c r="F6" s="34" t="str">
         <x:v>EV-001; EV-002</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="110" customHeight="1">
-      <x:c r="A7" s="8" t="str">
+      <x:c r="A7" s="38" t="str">
         <x:v>DC01-OBS-001</x:v>
       </x:c>
-      <x:c r="B7" s="8" t="str">
+      <x:c r="B7" s="38" t="str">
         <x:v>Historical discrepancy</x:v>
       </x:c>
-      <x:c r="C7" s="8" t="str">
+      <x:c r="C7" s="38" t="str">
         <x:v>Unverified</x:v>
       </x:c>
-      <x:c r="D7" s="8" t="str">
+      <x:c r="D7" s="38" t="str">
         <x:v>Initial limited scan showed truncated High Microsoft Windows SMB Shares finding. Not observed in later privileged scan.</x:v>
       </x:c>
-      <x:c r="E7" s="8" t="str">
+      <x:c r="E7" s="38" t="str">
         <x:v>Do not label remediated or false positive. Full initial plugin identity/output and reproduction not established. Retain as historical discrepancy.</x:v>
       </x:c>
-      <x:c r="F7" s="8" t="str">
+      <x:c r="F7" s="38" t="str">
         <x:v>Initial limited-scan screenshot in chat</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="110" customHeight="1">
-      <x:c r="A8" s="8" t="str">
+      <x:c r="A8" s="34" t="str">
         <x:v>DC01-ADMIN-001</x:v>
       </x:c>
-      <x:c r="B8" s="8" t="str">
+      <x:c r="B8" s="34" t="str">
         <x:v>Credential cleanup</x:v>
       </x:c>
-      <x:c r="C8" s="8" t="str">
+      <x:c r="C8" s="34" t="str">
         <x:v>Completed — operator confirmed</x:v>
       </x:c>
-      <x:c r="D8" s="8" t="str">
+      <x:c r="D8" s="34" t="str">
         <x:v>User confirmed removal of the saved Windows Administrator credential and saving the scan configuration.</x:v>
       </x:c>
-      <x:c r="E8" s="8" t="str">
+      <x:c r="E8" s="34" t="str">
         <x:v>Completion based on user confirmation, not independent configuration inspection. Historical results retained; no passwords recorded here.</x:v>
       </x:c>
-      <x:c r="F8" s="8" t="str">
+      <x:c r="F8" s="34" t="str">
         <x:v>User confirmation in conversation, October 23, 2026</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="110" customHeight="1">
-      <x:c r="A9" s="8" t="str">
+      <x:c r="A9" s="38" t="str">
         <x:v>DC01-SCOPE-001</x:v>
       </x:c>
-      <x:c r="B9" s="8" t="str">
+      <x:c r="B9" s="38" t="str">
         <x:v>Assessment limitation</x:v>
       </x:c>
-      <x:c r="C9" s="8" t="str">
+      <x:c r="C9" s="38" t="str">
         <x:v>Recorded</x:v>
       </x:c>
-      <x:c r="D9" s="8" t="str">
+      <x:c r="D9" s="38" t="str">
         <x:v>Final scan has 51 displayed groups and 235 Info instances; Basic Network Scan, default ports, safe checks, delayed feed 202609232334.</x:v>
       </x:c>
-      <x:c r="E9" s="8" t="str">
+      <x:c r="E9" s="38" t="str">
         <x:v>Closure applies to two tracked configuration findings. No assertion of zero vulnerabilities, full compliance, independent approval, or physical host protection.</x:v>
       </x:c>
-      <x:c r="F9" s="8" t="str">
+      <x:c r="F9" s="38" t="str">
         <x:v>EV-012</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9ba25b7d3364b7b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R586514181fbf4016"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF8B9AA7"/>
+  </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="29" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="110" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="100" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="90" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="78" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="1"/>
-      <x:c r="B1" s="1"/>
-      <x:c r="C1" s="1"/>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="2" t="str">
+      <x:c r="A1" s="20"/>
+      <x:c r="B1" s="20"/>
+      <x:c r="C1" s="20"/>
+    </x:row>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="24" t="str">
         <x:v>Using this lab tracker</x:v>
       </x:c>
-      <x:c r="B2" s="1"/>
-      <x:c r="C2" s="1"/>
+      <x:c r="B2" s="20"/>
+      <x:c r="C2" s="20"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="1"/>
-      <x:c r="B3" s="1"/>
-      <x:c r="C3" s="1"/>
+      <x:c r="A3" s="20"/>
+      <x:c r="B3" s="20"/>
+      <x:c r="C3" s="20"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="1"/>
-      <x:c r="B4" s="1"/>
-      <x:c r="C4" s="1"/>
-    </x:row>
-    <x:row r="5" ht="34" customHeight="1">
-      <x:c r="A5" s="7" t="str">
+      <x:c r="A4" s="20"/>
+      <x:c r="B4" s="20"/>
+      <x:c r="C4" s="20"/>
+    </x:row>
+    <x:row r="5" ht="42" customHeight="1">
+      <x:c r="A5" s="33" t="str">
         <x:v>Topic</x:v>
       </x:c>
-      <x:c r="B5" s="7" t="str">
+      <x:c r="B5" s="33" t="str">
         <x:v>How to interpret / maintain</x:v>
       </x:c>
-      <x:c r="C5" s="7" t="str">
+      <x:c r="C5" s="33" t="str">
         <x:v>Source</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="110" customHeight="1">
-      <x:c r="A6" s="8" t="str">
+    <x:row r="6" ht="75" customHeight="1">
+      <x:c r="A6" s="34" t="str">
         <x:v>CVSS</x:v>
       </x:c>
-      <x:c r="B6" s="8" t="str">
+      <x:c r="B6" s="34" t="str">
         <x:v>Technical severity; retain score version and vector in supporting evidence. CVSS 6.5 and Nessus Low may differ; preserve both. Baseline scores stay unchanged when status closes.</x:v>
       </x:c>
-      <x:c r="C6" s="8" t="str">
+      <x:c r="C6" s="34" t="str">
         <x:v>User-provided Nessus plugin 166555 and 302873 screenshots</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="110" customHeight="1">
-      <x:c r="A7" s="8" t="str">
+    <x:row r="7" ht="75" customHeight="1">
+      <x:c r="A7" s="38" t="str">
         <x:v>VPR</x:v>
       </x:c>
-      <x:c r="B7" s="8" t="str">
+      <x:c r="B7" s="38" t="str">
         <x:v>Tenable prioritization score (0-10) changes with threat assessment; preserve baseline and observation date. Not a probability.</x:v>
       </x:c>
-      <x:c r="C7" s="8" t="str">
+      <x:c r="C7" s="38" t="str">
         <x:v>https://www.tenable.com/plugins/nessus/166555</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="110" customHeight="1">
-      <x:c r="A8" s="8" t="str">
+    <x:row r="8" ht="75" customHeight="1">
+      <x:c r="A8" s="34" t="str">
         <x:v>EPSS</x:v>
       </x:c>
-      <x:c r="B8" s="8" t="str">
+      <x:c r="B8" s="34" t="str">
         <x:v>Probability of CVE exploitation in the wild within the next 30 days; .4465 = 44.65%. Not probability this specific DC is compromised. Store as numeric percentage and date it.</x:v>
       </x:c>
-      <x:c r="C8" s="8" t="str">
+      <x:c r="C8" s="34" t="str">
         <x:v>https://www.first.org/epss/</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="110" customHeight="1">
-      <x:c r="A9" s="8" t="str">
+    <x:row r="9" ht="75" customHeight="1">
+      <x:c r="A9" s="38" t="str">
         <x:v>Workflow</x:v>
       </x:c>
-      <x:c r="B9" s="8" t="str">
+      <x:c r="B9" s="38" t="str">
         <x:v>Validate scan coverage &gt; record finding/evidence &gt; assign owner and target &gt; plan change/rollback &gt; implement &gt; operational checks &gt; authenticated rescan &gt; verify closure.</x:v>
       </x:c>
-      <x:c r="C9" s="8" t="str">
+      <x:c r="C9" s="38" t="str">
         <x:v>Lab workflow agreed in this conversation</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="110" customHeight="1">
-      <x:c r="A10" s="8" t="str">
+    <x:row r="10" ht="75" customHeight="1">
+      <x:c r="A10" s="34" t="str">
         <x:v>Updating</x:v>
       </x:c>
-      <x:c r="B10" s="8" t="str">
+      <x:c r="B10" s="34" t="str">
         <x:v>Add findings in rows 8-205 of Findings; copy row structure, keep stable IDs, and extend table. Dashboard formulas cover rows 6-205. Overdue uses Dashboard as-of date; change that date for later reviews.</x:v>
       </x:c>
-      <x:c r="C10" s="8" t="str">
+      <x:c r="C10" s="34" t="str">
         <x:v>Workbook design</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="110" customHeight="1">
-      <x:c r="A11" s="8" t="str">
+    <x:row r="11" ht="75" customHeight="1">
+      <x:c r="A11" s="38" t="str">
         <x:v>Targets and approvals</x:v>
       </x:c>
-      <x:c r="B11" s="8" t="str">
+      <x:c r="B11" s="38" t="str">
         <x:v>Target dates blank because no policy/SLA was supplied. Set an agreed date for future open findings; no retrospective SLA or independent approval invented. Lab operator fills owner role; name not asserted.</x:v>
       </x:c>
-      <x:c r="C11" s="8" t="str">
+      <x:c r="C11" s="38" t="str">
         <x:v>Conversation scope</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="110" customHeight="1">
-      <x:c r="A12" s="8" t="str">
+    <x:row r="12" ht="75" customHeight="1">
+      <x:c r="A12" s="34" t="str">
         <x:v>Evidence retention</x:v>
       </x:c>
-      <x:c r="B12" s="8" t="str">
+      <x:c r="B12" s="34" t="str">
         <x:v>50 original screenshots retained in source archive; descriptive publication copies in 06-Evidence/Phase-4-Vulnerability-Assessment/DC01. Evidence links resolve relative to this workbook in 04-Vulnerability-Remediation. Download the repository together to preserve local links. No raw .nessus exports claimed.</x:v>
       </x:c>
-      <x:c r="C12" s="8" t="str">
+      <x:c r="C12" s="34" t="str">
         <x:v>User-provided screenshots and operator statements, October 23, 2026</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="110" customHeight="1">
-      <x:c r="A13" s="8" t="str">
+    <x:row r="13" ht="75" customHeight="1">
+      <x:c r="A13" s="38" t="str">
         <x:v>Closure</x:v>
       </x:c>
-      <x:c r="B13" s="8" t="str">
+      <x:c r="B13" s="38" t="str">
         <x:v>Close only with finding-specific evidence, correct settings, operational validation and successful authenticated verification. Risk acceptance requires a separate documented decision and review date.</x:v>
       </x:c>
-      <x:c r="C13" s="8" t="str">
+      <x:c r="C13" s="38" t="str">
         <x:v>Lab workflow</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="110" customHeight="1">
-      <x:c r="A14" s="8" t="str">
+    <x:row r="14" ht="75" customHeight="1">
+      <x:c r="A14" s="34" t="str">
         <x:v>Scope limits</x:v>
       </x:c>
-      <x:c r="B14" s="8" t="str">
+      <x:c r="B14" s="34" t="str">
         <x:v>This workbook covers DC01 only, two confirmed findings, two changes and scan-access exceptions. Previous member-server assessments remain separately documented on GitHub.</x:v>
       </x:c>
-      <x:c r="C14" s="8" t="str">
+      <x:c r="C14" s="34" t="str">
         <x:v>https://github.com/MusahIssah/Windows-Server-Patching-Security-Lab</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="110" customHeight="1">
-      <x:c r="A15" s="8" t="str">
+    <x:row r="15" ht="75" customHeight="1">
+      <x:c r="A15" s="38" t="str">
         <x:v>BHI guidance</x:v>
       </x:c>
-      <x:c r="B15" s="8" t="str">
+      <x:c r="B15" s="38" t="str">
         <x:v>Guest configuration: override 8388608 and mask 3; targeted BHI mitigation. Host/firmware protection and full speculative-execution coverage not established.</x:v>
       </x:c>
-      <x:c r="C15" s="8" t="str">
+      <x:c r="C15" s="38" t="str">
         <x:v>https://support.microsoft.com/en-us/servicing/os/windows-server/2019/12/kb4072698-windows-server-and-azure-stack-hci-guidance-to-protect-against-silicon-based-microarchitec</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="110" customHeight="1">
-      <x:c r="A16" s="8" t="str">
+    <x:row r="16" ht="75" customHeight="1">
+      <x:c r="A16" s="34" t="str">
         <x:v>WinVerifyTrust guidance</x:v>
       </x:c>
-      <x:c r="B16" s="8" t="str">
+      <x:c r="B16" s="34" t="str">
         <x:v>Native and WOW6432Node EnableCertPaddingCheck DWORD 1; retain baseline and verification evidence.</x:v>
       </x:c>
-      <x:c r="C16" s="8" t="str">
+      <x:c r="C16" s="34" t="str">
         <x:v>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2013-3900</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A2:C2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8bc103e6e37247cb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f30a02311584c52"/>
   </x:tableParts>
 </x:worksheet>
 </file>